--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41500F4C-5720-48A5-8D97-6A7CA55972E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AE3014-9031-4CCE-8C0F-D90EDA8FA2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -18,8 +18,8 @@
     <sheet name="Last activity" sheetId="10" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last activity'!$A$1:$C$83</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last activity'!$A$1:$C$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last activity'!$A$1:$D$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last activity'!$A$1:$D$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="229">
   <si>
     <t>Activity Name</t>
   </si>
@@ -682,9 +682,6 @@
 otherwise Positive, type = 'Reached voicemail'</t>
   </si>
   <si>
-    <t>Person filling</t>
-  </si>
-  <si>
     <t>Krish</t>
   </si>
   <si>
@@ -694,10 +691,46 @@
     <t>Callers are spending time on this activity, but not sure what are they doing, ask Mark</t>
   </si>
   <si>
-    <t>Verified by</t>
-  </si>
-  <si>
     <t>EDA team 1 / 2</t>
+  </si>
+  <si>
+    <t>Last activity menu</t>
+  </si>
+  <si>
+    <t>Legal Menu</t>
+  </si>
+  <si>
+    <t>Pre-legal seniors menu, legal menu, Family, Housing, Benefits, Employment, Immigration</t>
+  </si>
+  <si>
+    <t>Immigration menu</t>
+  </si>
+  <si>
+    <t>Benefits menu</t>
+  </si>
+  <si>
+    <t>Family menu</t>
+  </si>
+  <si>
+    <t>Housing menu</t>
+  </si>
+  <si>
+    <t>HIV menu</t>
+  </si>
+  <si>
+    <t>Legal menu</t>
+  </si>
+  <si>
+    <t>Employment menu</t>
+  </si>
+  <si>
+    <t>Pre-legal seniors menu</t>
+  </si>
+  <si>
+    <t>Tagging Initiated by</t>
+  </si>
+  <si>
+    <t>Tagging Verified by</t>
   </si>
 </sst>
 </file>
@@ -769,7 +802,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -782,9 +815,6 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3693,1105 +3723,1163 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
-  <dimension ref="A1:J83"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="31.47265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="11.3671875" customWidth="1"/>
-    <col min="4" max="4" width="9.62890625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="15.20703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.89453125" customWidth="1"/>
-    <col min="7" max="7" width="44.734375" customWidth="1"/>
+    <col min="2" max="2" width="22.26171875" customWidth="1"/>
+    <col min="3" max="3" width="17.1015625" customWidth="1"/>
+    <col min="4" max="4" width="6.9453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.89453125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.41796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.26171875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
         <v>195</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="I1" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="2">
         <v>39892</v>
       </c>
-      <c r="C2" s="6">
-        <f>B2/SUM(($B$2:$B$83))</f>
+      <c r="D2" s="6">
+        <f>C2/SUM(($C$2:$C$83))</f>
         <v>0.16056866391350899</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>204</v>
       </c>
-      <c r="H2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="I2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="2">
+      <c r="C3" s="2">
         <v>28035</v>
       </c>
-      <c r="C3" s="6">
-        <f t="shared" ref="C3:C66" si="0">B3/SUM(($B$2:$B$83))</f>
+      <c r="D3" s="6">
+        <f t="shared" ref="D3:D66" si="0">C3/SUM(($C$2:$C$83))</f>
         <v>0.11284323906585843</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>202</v>
       </c>
-      <c r="H3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="I3" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="2">
+      <c r="C4" s="2">
         <v>27545</v>
       </c>
-      <c r="C4" s="6">
+      <c r="D4" s="6">
         <f t="shared" si="0"/>
         <v>0.11087094774635528</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>205</v>
       </c>
-      <c r="H4" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="I4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="2">
+      <c r="C5" s="2">
         <v>25721</v>
       </c>
-      <c r="C5" s="6">
+      <c r="D5" s="6">
         <f t="shared" si="0"/>
         <v>0.10352919393661297</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="H5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="I5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2">
+      <c r="C6" s="2">
         <v>13075</v>
       </c>
-      <c r="C6" s="6">
+      <c r="D6" s="6">
         <f t="shared" si="0"/>
         <v>5.2627977556129801E-2</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>205</v>
       </c>
-      <c r="H6" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="I6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2">
+      <c r="C7" s="2">
         <v>12010</v>
       </c>
-      <c r="C7" s="6">
+      <c r="D7" s="6">
         <f t="shared" si="0"/>
         <v>4.8341262749454599E-2</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H7" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="I7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="2">
         <v>11987</v>
       </c>
-      <c r="C8" s="6">
+      <c r="D8" s="6">
         <f t="shared" si="0"/>
         <v>4.8248685809967717E-2</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>205</v>
       </c>
-      <c r="H8" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="I8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="2">
+      <c r="C9" s="2">
         <v>9640</v>
       </c>
-      <c r="C9" s="6">
+      <c r="D9" s="6">
         <f t="shared" si="0"/>
         <v>3.8801812897980216E-2</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>202</v>
       </c>
-      <c r="G9" t="s">
-        <v>215</v>
-      </c>
-      <c r="H9" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="H9" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="2">
+      <c r="C10" s="2">
         <v>9358</v>
       </c>
-      <c r="C10" s="6">
+      <c r="D10" s="6">
         <f t="shared" si="0"/>
         <v>3.7666739118184529E-2</v>
       </c>
-      <c r="G10" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="H10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2">
+      <c r="C11" s="2">
         <v>8939</v>
       </c>
-      <c r="C11" s="6">
+      <c r="D11" s="6">
         <f t="shared" si="0"/>
         <v>3.5980228785793066E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="2">
+      <c r="C12" s="2">
         <v>7890</v>
       </c>
-      <c r="C12" s="6">
+      <c r="D12" s="6">
         <f t="shared" si="0"/>
         <v>3.1757915328326128E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="C13" s="2">
         <v>7765</v>
       </c>
-      <c r="C13" s="6">
+      <c r="D13" s="6">
         <f t="shared" si="0"/>
         <v>3.125477978763655E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="2">
+      <c r="C14" s="2">
         <v>6895</v>
       </c>
-      <c r="C14" s="6">
+      <c r="D14" s="6">
         <f t="shared" si="0"/>
         <v>2.7752956424437092E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>67</v>
       </c>
-      <c r="B15" s="2">
+      <c r="C15" s="2">
         <v>6863</v>
       </c>
-      <c r="C15" s="6">
+      <c r="D15" s="6">
         <f t="shared" si="0"/>
         <v>2.7624153726020562E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>78</v>
       </c>
-      <c r="B16" s="2">
+      <c r="C16" s="2">
         <v>3959</v>
       </c>
-      <c r="C16" s="6">
+      <c r="D16" s="6">
         <f t="shared" si="0"/>
         <v>1.5935308844720296E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="2">
+      <c r="C17" s="2">
         <v>2545</v>
       </c>
-      <c r="C17" s="6">
+      <c r="D17" s="6">
         <f t="shared" si="0"/>
         <v>1.0243839608439796E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="2">
         <v>2394</v>
       </c>
-      <c r="C18" s="6">
+      <c r="D18" s="6">
         <f t="shared" si="0"/>
         <v>9.6360518752867871E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="2">
+      <c r="C19" s="2">
         <v>2267</v>
       </c>
-      <c r="C19" s="6">
+      <c r="D19" s="6">
         <f t="shared" si="0"/>
         <v>9.1248661659461758E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="2">
+      <c r="C20" s="2">
         <v>2136</v>
       </c>
-      <c r="C20" s="6">
+      <c r="D20" s="6">
         <f t="shared" si="0"/>
         <v>8.5975801193034999E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" t="s">
+        <v>221</v>
+      </c>
+      <c r="C21" s="2">
         <v>1462</v>
       </c>
-      <c r="C21" s="6">
+      <c r="D21" s="6">
         <f t="shared" si="0"/>
         <v>5.8846732839052977E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="2">
+      <c r="C22" s="2">
         <v>1287</v>
       </c>
-      <c r="C22" s="6">
+      <c r="D22" s="6">
         <f t="shared" si="0"/>
         <v>5.1802835269398892E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>5</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23" s="2">
         <v>1267</v>
       </c>
-      <c r="C23" s="6">
+      <c r="D23" s="6">
         <f t="shared" si="0"/>
         <v>5.099781840429557E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" t="s">
+        <v>226</v>
+      </c>
+      <c r="C24" s="2">
         <v>1209</v>
       </c>
-      <c r="C24" s="6">
+      <c r="D24" s="6">
         <f t="shared" si="0"/>
         <v>4.8663269495495933E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" t="s">
+        <v>222</v>
+      </c>
+      <c r="C25" s="2">
         <v>870</v>
       </c>
-      <c r="C25" s="6">
+      <c r="D25" s="6">
         <f t="shared" si="0"/>
         <v>3.5018233631994591E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" t="s">
+        <v>222</v>
+      </c>
+      <c r="C26" s="2">
         <v>837</v>
       </c>
-      <c r="C26" s="6">
+      <c r="D26" s="6">
         <f t="shared" si="0"/>
         <v>3.3689955804574105E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="2">
+      <c r="C27" s="2">
         <v>836</v>
       </c>
-      <c r="C27" s="6">
+      <c r="D27" s="6">
         <f t="shared" si="0"/>
         <v>3.3649704961318939E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>25</v>
       </c>
-      <c r="B28" s="2">
+      <c r="C28" s="2">
         <v>785</v>
       </c>
-      <c r="C28" s="6">
+      <c r="D28" s="6">
         <f t="shared" si="0"/>
         <v>3.1596911955305462E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" t="s">
+        <v>223</v>
+      </c>
+      <c r="C29" s="2">
         <v>771</v>
       </c>
-      <c r="C29" s="6">
+      <c r="D29" s="6">
         <f t="shared" si="0"/>
         <v>3.1033400149733138E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>97</v>
       </c>
-      <c r="B30" s="2">
+      <c r="C30" s="2">
         <v>694</v>
       </c>
-      <c r="C30" s="6">
+      <c r="D30" s="6">
         <f t="shared" si="0"/>
         <v>2.793408521908534E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>77</v>
       </c>
-      <c r="B31" s="2">
+      <c r="C31" s="2">
         <v>672</v>
       </c>
-      <c r="C31" s="6">
+      <c r="D31" s="6">
         <f t="shared" si="0"/>
         <v>2.7048566667471682E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" t="s">
+        <v>222</v>
+      </c>
+      <c r="C32" s="2">
         <v>604</v>
       </c>
-      <c r="C32" s="6">
+      <c r="D32" s="6">
         <f t="shared" si="0"/>
         <v>2.4311509326120384E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="2">
         <v>543</v>
       </c>
-      <c r="C33" s="6">
+      <c r="D33" s="6">
         <f t="shared" si="0"/>
         <v>2.1856207887555245E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>107</v>
       </c>
-      <c r="B34" s="2">
+      <c r="C34" s="2">
         <v>541</v>
       </c>
-      <c r="C34" s="6">
+      <c r="D34" s="6">
         <f t="shared" si="0"/>
         <v>2.1775706201044914E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" s="2">
         <v>540</v>
       </c>
-      <c r="C35" s="6">
+      <c r="D35" s="6">
         <f t="shared" si="0"/>
         <v>2.1735455357789744E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>74</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="2">
         <v>527</v>
       </c>
-      <c r="C36" s="6">
+      <c r="D36" s="6">
         <f t="shared" si="0"/>
         <v>2.1212194395472585E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>42</v>
       </c>
-      <c r="B37" s="2">
+      <c r="C37" s="2">
         <v>502</v>
       </c>
-      <c r="C37" s="6">
+      <c r="D37" s="6">
         <f t="shared" si="0"/>
         <v>2.020592331409343E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>83</v>
       </c>
-      <c r="B38" s="2">
+      <c r="C38" s="2">
         <v>479</v>
       </c>
-      <c r="C38" s="6">
+      <c r="D38" s="6">
         <f t="shared" si="0"/>
         <v>1.9280153919224608E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>80</v>
       </c>
-      <c r="B39" s="2">
+      <c r="C39" s="2">
         <v>454</v>
       </c>
-      <c r="C39" s="6">
+      <c r="D39" s="6">
         <f t="shared" si="0"/>
         <v>1.8273882837845452E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" t="s">
+        <v>226</v>
+      </c>
+      <c r="C40" s="2">
         <v>444</v>
       </c>
-      <c r="C40" s="6">
+      <c r="D40" s="6">
         <f t="shared" si="0"/>
         <v>1.7871374405293791E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>71</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" t="s">
+        <v>226</v>
+      </c>
+      <c r="C41" s="2">
         <v>442</v>
       </c>
-      <c r="C41" s="6">
+      <c r="D41" s="6">
         <f t="shared" si="0"/>
         <v>1.779087271878346E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>113</v>
       </c>
-      <c r="B42" s="2">
+      <c r="C42" s="2">
         <v>412</v>
       </c>
-      <c r="C42" s="6">
+      <c r="D42" s="6">
         <f t="shared" si="0"/>
         <v>1.6583347421128473E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>44</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" t="s">
+        <v>221</v>
+      </c>
+      <c r="C43" s="2">
         <v>353</v>
       </c>
-      <c r="C43" s="6">
+      <c r="D43" s="6">
         <f t="shared" si="0"/>
         <v>1.4208547669073666E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>72</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" t="s">
+        <v>220</v>
+      </c>
+      <c r="C44" s="2">
         <v>298</v>
       </c>
-      <c r="C44" s="6">
+      <c r="D44" s="6">
         <f t="shared" si="0"/>
         <v>1.1994751290039527E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>76</v>
       </c>
-      <c r="B45" s="2">
+      <c r="C45" s="2">
         <v>278</v>
       </c>
-      <c r="C45" s="6">
+      <c r="D45" s="6">
         <f t="shared" si="0"/>
         <v>1.1189734424936202E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>17</v>
       </c>
-      <c r="B46" s="2">
+      <c r="C46" s="2">
         <v>228</v>
       </c>
-      <c r="C46" s="6">
+      <c r="D46" s="6">
         <f t="shared" si="0"/>
         <v>9.1771922621778929E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>22</v>
       </c>
-      <c r="B47" s="2">
+      <c r="C47" s="2">
         <v>219</v>
       </c>
-      <c r="C47" s="6">
+      <c r="D47" s="6">
         <f t="shared" si="0"/>
         <v>8.8149346728813973E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>14</v>
       </c>
-      <c r="B48" s="2">
+      <c r="C48" s="2">
         <v>212</v>
       </c>
-      <c r="C48" s="6">
+      <c r="D48" s="6">
         <f t="shared" si="0"/>
         <v>8.533178770095233E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>122</v>
       </c>
-      <c r="B49" s="2">
+      <c r="C49" s="2">
         <v>185</v>
       </c>
-      <c r="C49" s="6">
+      <c r="D49" s="6">
         <f t="shared" si="0"/>
         <v>7.446406002205746E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>75</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" t="s">
+        <v>225</v>
+      </c>
+      <c r="C50" s="2">
         <v>183</v>
       </c>
-      <c r="C50" s="6">
+      <c r="D50" s="6">
         <f t="shared" si="0"/>
         <v>7.3659043156954135E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>198</v>
       </c>
-      <c r="B51" s="2">
+      <c r="C51" s="2">
         <v>177</v>
       </c>
-      <c r="C51" s="6">
+      <c r="D51" s="6">
         <f t="shared" si="0"/>
         <v>7.1243992561644172E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="2">
+      <c r="C52" s="2">
         <v>158</v>
       </c>
-      <c r="C52" s="6">
+      <c r="D52" s="6">
         <f t="shared" si="0"/>
         <v>6.3596332343162591E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>129</v>
       </c>
-      <c r="B53" s="2">
+      <c r="C53" s="2">
         <v>139</v>
       </c>
-      <c r="C53" s="6">
+      <c r="D53" s="6">
         <f t="shared" si="0"/>
         <v>5.594867212468101E-4</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>68</v>
       </c>
-      <c r="B54" s="2">
+      <c r="C54" s="2">
         <v>138</v>
       </c>
-      <c r="C54" s="6">
+      <c r="D54" s="6">
         <f t="shared" si="0"/>
         <v>5.5546163692129352E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>16</v>
       </c>
-      <c r="B55" s="2">
+      <c r="C55" s="2">
         <v>127</v>
       </c>
-      <c r="C55" s="6">
+      <c r="D55" s="6">
         <f t="shared" si="0"/>
         <v>5.1118570934061071E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>92</v>
       </c>
-      <c r="B56" s="2">
+      <c r="C56" s="2">
         <v>116</v>
       </c>
-      <c r="C56" s="6">
+      <c r="D56" s="6">
         <f t="shared" si="0"/>
         <v>4.669097817599279E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>84</v>
       </c>
-      <c r="B57" s="2">
+      <c r="C57" s="2">
         <v>85</v>
       </c>
-      <c r="C57" s="6">
+      <c r="D57" s="6">
         <f t="shared" si="0"/>
         <v>3.4213216766891265E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>139</v>
       </c>
-      <c r="B58" s="2">
+      <c r="C58" s="2">
         <v>70</v>
       </c>
-      <c r="C58" s="6">
+      <c r="D58" s="6">
         <f t="shared" si="0"/>
         <v>2.8175590278616339E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>141</v>
       </c>
-      <c r="B59" s="2">
+      <c r="C59" s="2">
         <v>67</v>
       </c>
-      <c r="C59" s="6">
+      <c r="D59" s="6">
         <f t="shared" si="0"/>
         <v>2.6968064980961351E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>89</v>
       </c>
-      <c r="B60" s="2">
+      <c r="C60" s="2">
         <v>58</v>
       </c>
-      <c r="C60" s="6">
+      <c r="D60" s="6">
         <f t="shared" si="0"/>
         <v>2.3345489087996395E-4</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>24</v>
       </c>
-      <c r="B61" s="2">
+      <c r="C61" s="2">
         <v>37</v>
       </c>
-      <c r="C61" s="6">
+      <c r="D61" s="6">
         <f t="shared" si="0"/>
         <v>1.4892812004411492E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>36</v>
       </c>
-      <c r="B62" s="2">
+      <c r="C62" s="2">
         <v>34</v>
       </c>
-      <c r="C62" s="6">
+      <c r="D62" s="6">
         <f t="shared" si="0"/>
         <v>1.3685286706756507E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>9</v>
       </c>
-      <c r="B63" s="2">
+      <c r="C63" s="2">
         <v>32</v>
       </c>
-      <c r="C63" s="6">
+      <c r="D63" s="6">
         <f t="shared" si="0"/>
         <v>1.2880269841653182E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>120</v>
       </c>
-      <c r="B64" s="2">
+      <c r="C64" s="2">
         <v>31</v>
       </c>
-      <c r="C64" s="6">
+      <c r="D64" s="6">
         <f t="shared" si="0"/>
         <v>1.247776140910152E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>96</v>
       </c>
-      <c r="B65" s="2">
+      <c r="C65" s="2">
         <v>27</v>
       </c>
-      <c r="C65" s="6">
+      <c r="D65" s="6">
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>27</v>
       </c>
-      <c r="B66" s="2">
+      <c r="C66" s="2">
         <v>27</v>
       </c>
-      <c r="C66" s="6">
+      <c r="D66" s="6">
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>163</v>
       </c>
-      <c r="B67" s="2">
+      <c r="C67" s="2">
         <v>22</v>
       </c>
-      <c r="C67" s="6">
-        <f t="shared" ref="C67:C83" si="1">B67/SUM(($B$2:$B$83))</f>
+      <c r="D67" s="6">
+        <f t="shared" ref="D67:D83" si="1">C67/SUM(($C$2:$C$83))</f>
         <v>8.855185516136563E-5</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>34</v>
       </c>
-      <c r="B68" s="2">
+      <c r="C68" s="2">
         <v>13</v>
       </c>
-      <c r="C68" s="6">
+      <c r="D68" s="6">
         <f t="shared" si="1"/>
         <v>5.2326096231716057E-5</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>87</v>
       </c>
-      <c r="B69" s="2">
+      <c r="C69" s="2">
         <v>8</v>
       </c>
-      <c r="C69" s="6">
+      <c r="D69" s="6">
         <f t="shared" si="1"/>
         <v>3.2200674604132955E-5</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>86</v>
       </c>
-      <c r="B70" s="2">
+      <c r="C70" s="2">
         <v>5</v>
       </c>
-      <c r="C70" s="6">
+      <c r="D70" s="6">
         <f t="shared" si="1"/>
         <v>2.0125421627583099E-5</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>93</v>
       </c>
-      <c r="B71" s="2">
+      <c r="C71" s="2">
         <v>4</v>
       </c>
-      <c r="C71" s="6">
+      <c r="D71" s="6">
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>123</v>
       </c>
-      <c r="B72" s="2">
+      <c r="C72" s="2">
         <v>4</v>
       </c>
-      <c r="C72" s="6">
+      <c r="D72" s="6">
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>126</v>
       </c>
-      <c r="B73" s="2">
+      <c r="C73" s="2">
         <v>2</v>
       </c>
-      <c r="C73" s="6">
+      <c r="D73" s="6">
         <f t="shared" si="1"/>
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>91</v>
       </c>
-      <c r="B74" s="2">
+      <c r="C74" s="2">
         <v>2</v>
       </c>
-      <c r="C74" s="6">
+      <c r="D74" s="6">
         <f t="shared" si="1"/>
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>85</v>
       </c>
-      <c r="B75" s="2">
-        <v>1</v>
-      </c>
-      <c r="C75" s="6">
+      <c r="C75" s="2">
+        <v>1</v>
+      </c>
+      <c r="D75" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>124</v>
       </c>
-      <c r="B76" s="2">
-        <v>1</v>
-      </c>
-      <c r="C76" s="6">
+      <c r="C76" s="2">
+        <v>1</v>
+      </c>
+      <c r="D76" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>145</v>
       </c>
-      <c r="B77" s="2">
-        <v>1</v>
-      </c>
-      <c r="C77" s="6">
+      <c r="C77" s="2">
+        <v>1</v>
+      </c>
+      <c r="D77" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>101</v>
       </c>
-      <c r="B78" s="2">
-        <v>1</v>
-      </c>
-      <c r="C78" s="6">
+      <c r="C78" s="2">
+        <v>1</v>
+      </c>
+      <c r="D78" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>173</v>
       </c>
-      <c r="B79" s="2">
-        <v>1</v>
-      </c>
-      <c r="C79" s="6">
+      <c r="C79" s="2">
+        <v>1</v>
+      </c>
+      <c r="D79" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>29</v>
       </c>
-      <c r="B80" s="2">
-        <v>1</v>
-      </c>
-      <c r="C80" s="6">
+      <c r="C80" s="2">
+        <v>1</v>
+      </c>
+      <c r="D80" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>112</v>
       </c>
-      <c r="B81" s="2">
-        <v>1</v>
-      </c>
-      <c r="C81" s="6">
+      <c r="C81" s="2">
+        <v>1</v>
+      </c>
+      <c r="D81" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>109</v>
       </c>
-      <c r="B82" s="2">
-        <v>1</v>
-      </c>
-      <c r="C82" s="6">
+      <c r="C82" s="2">
+        <v>1</v>
+      </c>
+      <c r="D82" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>150</v>
       </c>
-      <c r="B83" s="2">
-        <v>1</v>
-      </c>
-      <c r="C83" s="6">
+      <c r="C83" s="2">
+        <v>1</v>
+      </c>
+      <c r="D83" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sana/Downloads/STAT390/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AE3014-9031-4CCE-8C0F-D90EDA8FA2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18E5027-0143-F24A-913F-E19BF016F93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23240" windowHeight="13880" tabRatio="799" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="230">
   <si>
     <t>Activity Name</t>
   </si>
@@ -731,6 +731,9 @@
   </si>
   <si>
     <t>Tagging Verified by</t>
+  </si>
+  <si>
+    <t>sana</t>
   </si>
 </sst>
 </file>
@@ -1154,13 +1157,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.89453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.89453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1184,7 +1187,7 @@
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1192,7 +1195,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1200,7 +1203,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1208,7 +1211,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1216,7 +1219,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1224,7 +1227,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1240,7 +1243,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -1248,7 +1251,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -1256,7 +1259,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -1264,7 +1267,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1280,7 +1283,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -1296,7 +1299,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -1304,7 +1307,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -1312,7 +1315,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1320,7 +1323,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1336,7 +1339,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1344,7 +1347,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -1352,7 +1355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1360,7 +1363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1368,7 +1371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -1384,17 +1387,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.89453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.15625" customWidth="1"/>
-    <col min="4" max="4" width="9.15625" customWidth="1"/>
-    <col min="5" max="5" width="11.62890625" customWidth="1"/>
-    <col min="6" max="6" width="31.47265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.3671875" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1408,7 +1411,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1422,7 +1425,7 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1436,7 +1439,7 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1450,7 +1453,7 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1464,7 +1467,7 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1478,7 +1481,7 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -1492,7 +1495,7 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1506,7 +1509,7 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1520,7 +1523,7 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1534,7 +1537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1548,7 +1551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1562,7 +1565,7 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1576,7 +1579,7 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1590,7 +1593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1604,7 +1607,7 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1618,7 +1621,7 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1632,7 +1635,7 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1646,7 +1649,7 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -1660,7 +1663,7 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1674,7 +1677,7 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1702,7 +1705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -1730,7 +1733,7 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -1744,7 +1747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1758,7 +1761,7 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -1772,7 +1775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1786,7 +1789,7 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -1800,7 +1803,7 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -1814,7 +1817,7 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1828,7 +1831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -1842,7 +1845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -1856,7 +1859,7 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -1870,7 +1873,7 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1884,7 +1887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -1898,7 +1901,7 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -1912,7 +1915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>73</v>
       </c>
@@ -1926,7 +1929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -1940,7 +1943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>75</v>
       </c>
@@ -1954,7 +1957,7 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -1968,7 +1971,7 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>78</v>
       </c>
@@ -1982,7 +1985,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>74</v>
       </c>
@@ -1996,7 +1999,7 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>77</v>
       </c>
@@ -2010,7 +2013,7 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -2024,7 +2027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>81</v>
       </c>
@@ -2038,7 +2041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>44</v>
       </c>
@@ -2052,7 +2055,7 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>84</v>
       </c>
@@ -2066,7 +2069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -2080,7 +2083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -2094,7 +2097,7 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -2108,7 +2111,7 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -2122,7 +2125,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2136,7 +2139,7 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -2150,7 +2153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2164,7 +2167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -2178,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -2192,7 +2195,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2206,7 +2209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -2220,7 +2223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2234,7 +2237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2248,7 +2251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>89</v>
       </c>
@@ -2262,7 +2265,7 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -2276,7 +2279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>86</v>
       </c>
@@ -2290,7 +2293,7 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>93</v>
       </c>
@@ -2304,7 +2307,7 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>92</v>
       </c>
@@ -2318,7 +2321,7 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>95</v>
       </c>
@@ -2332,7 +2335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>96</v>
       </c>
@@ -2346,7 +2349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>98</v>
       </c>
@@ -2360,7 +2363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>99</v>
       </c>
@@ -2374,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -2388,7 +2391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>97</v>
       </c>
@@ -2402,7 +2405,7 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -2416,7 +2419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>102</v>
       </c>
@@ -2430,7 +2433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -2444,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>103</v>
       </c>
@@ -2458,7 +2461,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>104</v>
       </c>
@@ -2472,7 +2475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>105</v>
       </c>
@@ -2486,7 +2489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>106</v>
       </c>
@@ -2500,7 +2503,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>107</v>
       </c>
@@ -2514,7 +2517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>108</v>
       </c>
@@ -2528,7 +2531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>109</v>
       </c>
@@ -2542,7 +2545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>110</v>
       </c>
@@ -2556,7 +2559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>111</v>
       </c>
@@ -2570,7 +2573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>112</v>
       </c>
@@ -2584,7 +2587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>113</v>
       </c>
@@ -2598,7 +2601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>114</v>
       </c>
@@ -2612,7 +2615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>115</v>
       </c>
@@ -2626,7 +2629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>116</v>
       </c>
@@ -2640,7 +2643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>117</v>
       </c>
@@ -2654,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>118</v>
       </c>
@@ -2668,7 +2671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>119</v>
       </c>
@@ -2682,7 +2685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>121</v>
       </c>
@@ -2696,7 +2699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -2710,7 +2713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>123</v>
       </c>
@@ -2724,7 +2727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>120</v>
       </c>
@@ -2738,7 +2741,7 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>124</v>
       </c>
@@ -2752,7 +2755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>125</v>
       </c>
@@ -2766,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>126</v>
       </c>
@@ -2780,7 +2783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>127</v>
       </c>
@@ -2794,7 +2797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>128</v>
       </c>
@@ -2808,7 +2811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>129</v>
       </c>
@@ -2822,7 +2825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>130</v>
       </c>
@@ -2836,7 +2839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>131</v>
       </c>
@@ -2850,7 +2853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>132</v>
       </c>
@@ -2864,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>133</v>
       </c>
@@ -2878,7 +2881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>134</v>
       </c>
@@ -2892,7 +2895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>135</v>
       </c>
@@ -2906,7 +2909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>136</v>
       </c>
@@ -2920,7 +2923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>137</v>
       </c>
@@ -2934,7 +2937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>138</v>
       </c>
@@ -2948,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>139</v>
       </c>
@@ -2962,7 +2965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>140</v>
       </c>
@@ -2976,7 +2979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>141</v>
       </c>
@@ -2990,7 +2993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>142</v>
       </c>
@@ -3004,7 +3007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>143</v>
       </c>
@@ -3018,7 +3021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>144</v>
       </c>
@@ -3032,7 +3035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>145</v>
       </c>
@@ -3046,7 +3049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>146</v>
       </c>
@@ -3060,7 +3063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>147</v>
       </c>
@@ -3074,7 +3077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>148</v>
       </c>
@@ -3088,7 +3091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>149</v>
       </c>
@@ -3102,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>150</v>
       </c>
@@ -3116,7 +3119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>151</v>
       </c>
@@ -3130,7 +3133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>152</v>
       </c>
@@ -3144,7 +3147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>153</v>
       </c>
@@ -3158,7 +3161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>154</v>
       </c>
@@ -3172,7 +3175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>155</v>
       </c>
@@ -3186,7 +3189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>156</v>
       </c>
@@ -3200,7 +3203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>157</v>
       </c>
@@ -3214,7 +3217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>158</v>
       </c>
@@ -3228,7 +3231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>159</v>
       </c>
@@ -3242,7 +3245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>160</v>
       </c>
@@ -3256,7 +3259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>161</v>
       </c>
@@ -3270,7 +3273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>162</v>
       </c>
@@ -3284,7 +3287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>163</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>164</v>
       </c>
@@ -3312,7 +3315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>165</v>
       </c>
@@ -3326,7 +3329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>166</v>
       </c>
@@ -3340,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>167</v>
       </c>
@@ -3354,7 +3357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>168</v>
       </c>
@@ -3368,7 +3371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>169</v>
       </c>
@@ -3382,7 +3385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>170</v>
       </c>
@@ -3396,7 +3399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>171</v>
       </c>
@@ -3410,7 +3413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>172</v>
       </c>
@@ -3424,7 +3427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>173</v>
       </c>
@@ -3438,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>174</v>
       </c>
@@ -3452,7 +3455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>175</v>
       </c>
@@ -3466,7 +3469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>176</v>
       </c>
@@ -3480,7 +3483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>177</v>
       </c>
@@ -3494,7 +3497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>178</v>
       </c>
@@ -3508,7 +3511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>179</v>
       </c>
@@ -3522,7 +3525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>180</v>
       </c>
@@ -3536,7 +3539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>181</v>
       </c>
@@ -3550,7 +3553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>182</v>
       </c>
@@ -3564,7 +3567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>183</v>
       </c>
@@ -3578,7 +3581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>184</v>
       </c>
@@ -3592,7 +3595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>186</v>
       </c>
@@ -3620,7 +3623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>187</v>
       </c>
@@ -3634,7 +3637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>188</v>
       </c>
@@ -3648,7 +3651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>189</v>
       </c>
@@ -3662,7 +3665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>190</v>
       </c>
@@ -3676,7 +3679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>191</v>
       </c>
@@ -3690,7 +3693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>192</v>
       </c>
@@ -3724,19 +3727,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="31.47265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.26171875" customWidth="1"/>
-    <col min="3" max="3" width="17.1015625" customWidth="1"/>
-    <col min="4" max="4" width="6.9453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.89453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.41796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.26171875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.3125" customWidth="1"/>
+    <col min="1" max="1" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>195</v>
       </c>
@@ -3771,7 +3774,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -3794,8 +3797,11 @@
       <c r="I2" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="J2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -3816,7 +3822,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3837,7 +3843,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -3858,7 +3864,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3879,7 +3885,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -3900,7 +3906,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3924,7 +3930,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -3945,7 +3951,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3960,7 +3966,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -3972,7 +3978,7 @@
         <v>3.5980228785793066E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -3984,7 +3990,7 @@
         <v>3.1757915328326128E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -3996,7 +4002,7 @@
         <v>3.125477978763655E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -4008,7 +4014,7 @@
         <v>2.7752956424437092E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -4020,7 +4026,7 @@
         <v>2.7624153726020562E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -4032,7 +4038,7 @@
         <v>1.5935308844720296E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>81</v>
       </c>
@@ -4044,7 +4050,7 @@
         <v>1.0243839608439796E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -4059,7 +4065,7 @@
         <v>9.6360518752867871E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -4071,7 +4077,7 @@
         <v>9.1248661659461758E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -4083,7 +4089,7 @@
         <v>8.5975801193034999E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -4098,7 +4104,7 @@
         <v>5.8846732839052977E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4110,7 +4116,7 @@
         <v>5.1802835269398892E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -4125,7 +4131,7 @@
         <v>5.099781840429557E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -4140,7 +4146,7 @@
         <v>4.8663269495495933E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -4155,7 +4161,7 @@
         <v>3.5018233631994591E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -4170,7 +4176,7 @@
         <v>3.3689955804574105E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>99</v>
       </c>
@@ -4182,7 +4188,7 @@
         <v>3.3649704961318939E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -4194,7 +4200,7 @@
         <v>3.1596911955305462E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -4209,7 +4215,7 @@
         <v>3.1033400149733138E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -4221,7 +4227,7 @@
         <v>2.793408521908534E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -4233,7 +4239,7 @@
         <v>2.7048566667471682E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -4248,7 +4254,7 @@
         <v>2.4311509326120384E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -4263,7 +4269,7 @@
         <v>2.1856207887555245E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -4275,7 +4281,7 @@
         <v>2.1775706201044914E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -4290,7 +4296,7 @@
         <v>2.1735455357789744E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -4305,7 +4311,7 @@
         <v>2.1212194395472585E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -4317,7 +4323,7 @@
         <v>2.020592331409343E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -4329,7 +4335,7 @@
         <v>1.9280153919224608E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>80</v>
       </c>
@@ -4341,7 +4347,7 @@
         <v>1.8273882837845452E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -4356,7 +4362,7 @@
         <v>1.7871374405293791E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>71</v>
       </c>
@@ -4371,7 +4377,7 @@
         <v>1.779087271878346E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -4383,7 +4389,7 @@
         <v>1.6583347421128473E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -4398,7 +4404,7 @@
         <v>1.4208547669073666E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -4413,7 +4419,7 @@
         <v>1.1994751290039527E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>76</v>
       </c>
@@ -4425,7 +4431,7 @@
         <v>1.1189734424936202E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -4437,7 +4443,7 @@
         <v>9.1771922621778929E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -4449,7 +4455,7 @@
         <v>8.8149346728813973E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -4461,7 +4467,7 @@
         <v>8.533178770095233E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>122</v>
       </c>
@@ -4473,7 +4479,7 @@
         <v>7.446406002205746E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -4488,7 +4494,7 @@
         <v>7.3659043156954135E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>198</v>
       </c>
@@ -4500,7 +4506,7 @@
         <v>7.1243992561644172E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>125</v>
       </c>
@@ -4512,7 +4518,7 @@
         <v>6.3596332343162591E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>129</v>
       </c>
@@ -4524,7 +4530,7 @@
         <v>5.594867212468101E-4</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -4536,7 +4542,7 @@
         <v>5.5546163692129352E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>16</v>
       </c>
@@ -4548,7 +4554,7 @@
         <v>5.1118570934061071E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -4560,7 +4566,7 @@
         <v>4.669097817599279E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -4572,7 +4578,7 @@
         <v>3.4213216766891265E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>139</v>
       </c>
@@ -4584,7 +4590,7 @@
         <v>2.8175590278616339E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>141</v>
       </c>
@@ -4596,7 +4602,7 @@
         <v>2.6968064980961351E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>89</v>
       </c>
@@ -4608,7 +4614,7 @@
         <v>2.3345489087996395E-4</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>24</v>
       </c>
@@ -4620,7 +4626,7 @@
         <v>1.4892812004411492E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>36</v>
       </c>
@@ -4632,7 +4638,7 @@
         <v>1.3685286706756507E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -4644,7 +4650,7 @@
         <v>1.2880269841653182E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>120</v>
       </c>
@@ -4656,7 +4662,7 @@
         <v>1.247776140910152E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>96</v>
       </c>
@@ -4668,7 +4674,7 @@
         <v>1.0867727678894872E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -4680,7 +4686,7 @@
         <v>1.0867727678894872E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>163</v>
       </c>
@@ -4692,7 +4698,7 @@
         <v>8.855185516136563E-5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>34</v>
       </c>
@@ -4704,7 +4710,7 @@
         <v>5.2326096231716057E-5</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>87</v>
       </c>
@@ -4716,7 +4722,7 @@
         <v>3.2200674604132955E-5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>86</v>
       </c>
@@ -4728,7 +4734,7 @@
         <v>2.0125421627583099E-5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -4740,7 +4746,7 @@
         <v>1.6100337302066478E-5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>123</v>
       </c>
@@ -4752,7 +4758,7 @@
         <v>1.6100337302066478E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>126</v>
       </c>
@@ -4764,7 +4770,7 @@
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -4776,7 +4782,7 @@
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -4788,7 +4794,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>124</v>
       </c>
@@ -4800,7 +4806,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>145</v>
       </c>
@@ -4812,7 +4818,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>101</v>
       </c>
@@ -4824,7 +4830,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>173</v>
       </c>
@@ -4836,7 +4842,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>29</v>
       </c>
@@ -4848,7 +4854,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>112</v>
       </c>
@@ -4860,7 +4866,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -4872,7 +4878,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>150</v>
       </c>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AE3014-9031-4CCE-8C0F-D90EDA8FA2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2461659-0460-40C9-96DD-5B60B3F84BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="229">
   <si>
     <t>Activity Name</t>
   </si>
@@ -3794,6 +3794,9 @@
       <c r="I2" t="s">
         <v>212</v>
       </c>
+      <c r="J2" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="3" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sana/Downloads/STAT390/STAT390_LegalAid_Fall2025/Clarifications/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18E5027-0143-F24A-913F-E19BF016F93E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9398651-4F37-4E20-9FE2-4FF084FD151C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="23240" windowHeight="13880" tabRatio="799" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="229">
   <si>
     <t>Activity Name</t>
   </si>
@@ -731,9 +731,6 @@
   </si>
   <si>
     <t>Tagging Verified by</t>
-  </si>
-  <si>
-    <t>sana</t>
   </si>
 </sst>
 </file>
@@ -1157,13 +1154,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.83984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1171,7 +1168,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1179,7 +1176,7 @@
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1187,7 +1184,7 @@
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -1195,7 +1192,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -1203,7 +1200,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1211,7 +1208,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1219,7 +1216,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -1227,7 +1224,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>47</v>
       </c>
@@ -1235,7 +1232,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -1243,7 +1240,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>48</v>
       </c>
@@ -1251,7 +1248,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>49</v>
       </c>
@@ -1259,7 +1256,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -1267,7 +1264,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -1275,7 +1272,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1283,7 +1280,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>53</v>
       </c>
@@ -1291,7 +1288,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>54</v>
       </c>
@@ -1299,7 +1296,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>55</v>
       </c>
@@ -1307,7 +1304,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>56</v>
       </c>
@@ -1315,7 +1312,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1323,7 +1320,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1331,7 +1328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -1339,7 +1336,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>60</v>
       </c>
@@ -1347,7 +1344,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -1355,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1363,7 +1360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1371,7 +1368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>64</v>
       </c>
@@ -1387,17 +1384,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.83984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.15625" customWidth="1"/>
+    <col min="4" max="4" width="9.15625" customWidth="1"/>
+    <col min="5" max="5" width="11.68359375" customWidth="1"/>
+    <col min="6" max="6" width="31.47265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1411,7 +1408,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1425,7 +1422,7 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1439,7 +1436,7 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1453,7 +1450,7 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1467,7 +1464,7 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1481,7 +1478,7 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -1495,7 +1492,7 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1509,7 +1506,7 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -1523,7 +1520,7 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1537,7 +1534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1551,7 +1548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1565,7 +1562,7 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1579,7 +1576,7 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -1593,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -1607,7 +1604,7 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -1621,7 +1618,7 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -1635,7 +1632,7 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1649,7 +1646,7 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -1663,7 +1660,7 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1677,7 +1674,7 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1691,7 +1688,7 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1705,7 +1702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>43</v>
       </c>
@@ -1719,7 +1716,7 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -1733,7 +1730,7 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>70</v>
       </c>
@@ -1747,7 +1744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -1761,7 +1758,7 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -1775,7 +1772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1789,7 +1786,7 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>27</v>
       </c>
@@ -1803,7 +1800,7 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>25</v>
       </c>
@@ -1817,7 +1814,7 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>29</v>
       </c>
@@ -1831,7 +1828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -1845,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>26</v>
       </c>
@@ -1859,7 +1856,7 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>71</v>
       </c>
@@ -1873,7 +1870,7 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -1887,7 +1884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>72</v>
       </c>
@@ -1901,7 +1898,7 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -1915,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>73</v>
       </c>
@@ -1929,7 +1926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>76</v>
       </c>
@@ -1943,7 +1940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>75</v>
       </c>
@@ -1957,7 +1954,7 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>41</v>
       </c>
@@ -1971,7 +1968,7 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>78</v>
       </c>
@@ -1985,7 +1982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>74</v>
       </c>
@@ -1999,7 +1996,7 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>77</v>
       </c>
@@ -2013,7 +2010,7 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>21</v>
       </c>
@@ -2027,7 +2024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>81</v>
       </c>
@@ -2041,7 +2038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>44</v>
       </c>
@@ -2055,7 +2052,7 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>84</v>
       </c>
@@ -2069,7 +2066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>7</v>
       </c>
@@ -2083,7 +2080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -2097,7 +2094,7 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>80</v>
       </c>
@@ -2111,7 +2108,7 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>79</v>
       </c>
@@ -2125,7 +2122,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2139,7 +2136,7 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>23</v>
       </c>
@@ -2153,7 +2150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2167,7 +2164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>87</v>
       </c>
@@ -2181,7 +2178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>34</v>
       </c>
@@ -2195,7 +2192,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2209,7 +2206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>16</v>
       </c>
@@ -2223,7 +2220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2237,7 +2234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2251,7 +2248,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>89</v>
       </c>
@@ -2265,7 +2262,7 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -2279,7 +2276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>86</v>
       </c>
@@ -2293,7 +2290,7 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>93</v>
       </c>
@@ -2307,7 +2304,7 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>92</v>
       </c>
@@ -2321,7 +2318,7 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>95</v>
       </c>
@@ -2335,7 +2332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>96</v>
       </c>
@@ -2349,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>98</v>
       </c>
@@ -2363,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>99</v>
       </c>
@@ -2377,7 +2374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>100</v>
       </c>
@@ -2391,7 +2388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>97</v>
       </c>
@@ -2405,7 +2402,7 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -2419,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>102</v>
       </c>
@@ -2433,7 +2430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>17</v>
       </c>
@@ -2447,7 +2444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>103</v>
       </c>
@@ -2461,7 +2458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>104</v>
       </c>
@@ -2475,7 +2472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>105</v>
       </c>
@@ -2489,7 +2486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>106</v>
       </c>
@@ -2503,7 +2500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>107</v>
       </c>
@@ -2517,7 +2514,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>108</v>
       </c>
@@ -2531,7 +2528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
         <v>109</v>
       </c>
@@ -2545,7 +2542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
         <v>110</v>
       </c>
@@ -2559,7 +2556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
         <v>111</v>
       </c>
@@ -2573,7 +2570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
         <v>112</v>
       </c>
@@ -2587,7 +2584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
         <v>113</v>
       </c>
@@ -2601,7 +2598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
         <v>114</v>
       </c>
@@ -2615,7 +2612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
         <v>115</v>
       </c>
@@ -2629,7 +2626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
         <v>116</v>
       </c>
@@ -2643,7 +2640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
         <v>117</v>
       </c>
@@ -2657,7 +2654,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
         <v>118</v>
       </c>
@@ -2671,7 +2668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
         <v>119</v>
       </c>
@@ -2685,7 +2682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
         <v>121</v>
       </c>
@@ -2699,7 +2696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
         <v>122</v>
       </c>
@@ -2713,7 +2710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
         <v>123</v>
       </c>
@@ -2727,7 +2724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
         <v>120</v>
       </c>
@@ -2741,7 +2738,7 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
         <v>124</v>
       </c>
@@ -2755,7 +2752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
         <v>125</v>
       </c>
@@ -2769,7 +2766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
         <v>126</v>
       </c>
@@ -2783,7 +2780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
         <v>127</v>
       </c>
@@ -2797,7 +2794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
         <v>128</v>
       </c>
@@ -2811,7 +2808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
         <v>129</v>
       </c>
@@ -2825,7 +2822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
         <v>130</v>
       </c>
@@ -2839,7 +2836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
         <v>131</v>
       </c>
@@ -2853,7 +2850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
         <v>132</v>
       </c>
@@ -2867,7 +2864,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
         <v>133</v>
       </c>
@@ -2881,7 +2878,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
         <v>134</v>
       </c>
@@ -2895,7 +2892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
         <v>135</v>
       </c>
@@ -2909,7 +2906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
         <v>136</v>
       </c>
@@ -2923,7 +2920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
         <v>137</v>
       </c>
@@ -2937,7 +2934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
         <v>138</v>
       </c>
@@ -2951,7 +2948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
         <v>139</v>
       </c>
@@ -2965,7 +2962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
         <v>140</v>
       </c>
@@ -2979,7 +2976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
         <v>141</v>
       </c>
@@ -2993,7 +2990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
         <v>142</v>
       </c>
@@ -3007,7 +3004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
         <v>143</v>
       </c>
@@ -3021,7 +3018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
         <v>144</v>
       </c>
@@ -3035,7 +3032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
         <v>145</v>
       </c>
@@ -3049,7 +3046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
         <v>146</v>
       </c>
@@ -3063,7 +3060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
         <v>147</v>
       </c>
@@ -3077,7 +3074,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
         <v>148</v>
       </c>
@@ -3091,7 +3088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
         <v>149</v>
       </c>
@@ -3105,7 +3102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
         <v>150</v>
       </c>
@@ -3119,7 +3116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
         <v>151</v>
       </c>
@@ -3133,7 +3130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
         <v>152</v>
       </c>
@@ -3147,7 +3144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
         <v>153</v>
       </c>
@@ -3161,7 +3158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
         <v>154</v>
       </c>
@@ -3175,7 +3172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>155</v>
       </c>
@@ -3189,7 +3186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
         <v>156</v>
       </c>
@@ -3203,7 +3200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
         <v>157</v>
       </c>
@@ -3217,7 +3214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
         <v>158</v>
       </c>
@@ -3231,7 +3228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
         <v>159</v>
       </c>
@@ -3245,7 +3242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
         <v>160</v>
       </c>
@@ -3259,7 +3256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
         <v>161</v>
       </c>
@@ -3273,7 +3270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
         <v>162</v>
       </c>
@@ -3287,7 +3284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
         <v>163</v>
       </c>
@@ -3301,7 +3298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
         <v>164</v>
       </c>
@@ -3315,7 +3312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
         <v>165</v>
       </c>
@@ -3329,7 +3326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
         <v>166</v>
       </c>
@@ -3343,7 +3340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
         <v>167</v>
       </c>
@@ -3357,7 +3354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
         <v>168</v>
       </c>
@@ -3371,7 +3368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
         <v>169</v>
       </c>
@@ -3385,7 +3382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
         <v>170</v>
       </c>
@@ -3399,7 +3396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" t="s">
         <v>171</v>
       </c>
@@ -3413,7 +3410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" t="s">
         <v>172</v>
       </c>
@@ -3427,7 +3424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" t="s">
         <v>173</v>
       </c>
@@ -3441,7 +3438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" t="s">
         <v>174</v>
       </c>
@@ -3455,7 +3452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" t="s">
         <v>175</v>
       </c>
@@ -3469,7 +3466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" t="s">
         <v>176</v>
       </c>
@@ -3483,7 +3480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" t="s">
         <v>177</v>
       </c>
@@ -3497,7 +3494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" t="s">
         <v>178</v>
       </c>
@@ -3511,7 +3508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" t="s">
         <v>179</v>
       </c>
@@ -3525,7 +3522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" t="s">
         <v>180</v>
       </c>
@@ -3539,7 +3536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" t="s">
         <v>181</v>
       </c>
@@ -3553,7 +3550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" t="s">
         <v>182</v>
       </c>
@@ -3567,7 +3564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" t="s">
         <v>183</v>
       </c>
@@ -3581,7 +3578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" t="s">
         <v>184</v>
       </c>
@@ -3595,7 +3592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>185</v>
       </c>
@@ -3609,7 +3606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" t="s">
         <v>186</v>
       </c>
@@ -3623,7 +3620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" t="s">
         <v>187</v>
       </c>
@@ -3637,7 +3634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>188</v>
       </c>
@@ -3651,7 +3648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" t="s">
         <v>189</v>
       </c>
@@ -3665,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" t="s">
         <v>190</v>
       </c>
@@ -3679,7 +3676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" t="s">
         <v>191</v>
       </c>
@@ -3693,7 +3690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" t="s">
         <v>192</v>
       </c>
@@ -3727,19 +3724,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="31.47265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.3125" customWidth="1"/>
+    <col min="3" max="3" width="17.15625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.33203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.47265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.3125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
         <v>195</v>
       </c>
@@ -3774,7 +3771,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>66</v>
       </c>
@@ -3798,10 +3795,10 @@
         <v>212</v>
       </c>
       <c r="J2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -3822,7 +3819,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -3843,7 +3840,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -3864,7 +3861,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -3885,7 +3882,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -3906,7 +3903,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -3930,7 +3927,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -3951,7 +3948,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -3966,7 +3963,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -3978,7 +3975,7 @@
         <v>3.5980228785793066E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -3990,7 +3987,7 @@
         <v>3.1757915328326128E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -4002,7 +3999,7 @@
         <v>3.125477978763655E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -4014,7 +4011,7 @@
         <v>2.7752956424437092E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -4026,7 +4023,7 @@
         <v>2.7624153726020562E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -4038,7 +4035,7 @@
         <v>1.5935308844720296E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>81</v>
       </c>
@@ -4050,7 +4047,7 @@
         <v>1.0243839608439796E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -4065,7 +4062,7 @@
         <v>9.6360518752867871E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -4077,7 +4074,7 @@
         <v>9.1248661659461758E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -4089,7 +4086,7 @@
         <v>8.5975801193034999E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -4104,7 +4101,7 @@
         <v>5.8846732839052977E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -4116,7 +4113,7 @@
         <v>5.1802835269398892E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -4131,7 +4128,7 @@
         <v>5.099781840429557E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -4146,7 +4143,7 @@
         <v>4.8663269495495933E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>41</v>
       </c>
@@ -4161,7 +4158,7 @@
         <v>3.5018233631994591E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -4176,7 +4173,7 @@
         <v>3.3689955804574105E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>99</v>
       </c>
@@ -4188,7 +4185,7 @@
         <v>3.3649704961318939E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -4200,7 +4197,7 @@
         <v>3.1596911955305462E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>79</v>
       </c>
@@ -4215,7 +4212,7 @@
         <v>3.1033400149733138E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -4227,7 +4224,7 @@
         <v>2.793408521908534E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>77</v>
       </c>
@@ -4239,7 +4236,7 @@
         <v>2.7048566667471682E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -4254,7 +4251,7 @@
         <v>2.4311509326120384E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -4269,7 +4266,7 @@
         <v>2.1856207887555245E-3</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -4281,7 +4278,7 @@
         <v>2.1775706201044914E-3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>82</v>
       </c>
@@ -4296,7 +4293,7 @@
         <v>2.1735455357789744E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
         <v>74</v>
       </c>
@@ -4311,7 +4308,7 @@
         <v>2.1212194395472585E-3</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>42</v>
       </c>
@@ -4323,7 +4320,7 @@
         <v>2.020592331409343E-3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -4335,7 +4332,7 @@
         <v>1.9280153919224608E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>80</v>
       </c>
@@ -4347,7 +4344,7 @@
         <v>1.8273882837845452E-3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
         <v>15</v>
       </c>
@@ -4362,7 +4359,7 @@
         <v>1.7871374405293791E-3</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>71</v>
       </c>
@@ -4377,7 +4374,7 @@
         <v>1.779087271878346E-3</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>113</v>
       </c>
@@ -4389,7 +4386,7 @@
         <v>1.6583347421128473E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -4404,7 +4401,7 @@
         <v>1.4208547669073666E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -4419,7 +4416,7 @@
         <v>1.1994751290039527E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>76</v>
       </c>
@@ -4431,7 +4428,7 @@
         <v>1.1189734424936202E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" t="s">
         <v>17</v>
       </c>
@@ -4443,7 +4440,7 @@
         <v>9.1771922621778929E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -4455,7 +4452,7 @@
         <v>8.8149346728813973E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -4467,7 +4464,7 @@
         <v>8.533178770095233E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" t="s">
         <v>122</v>
       </c>
@@ -4479,7 +4476,7 @@
         <v>7.446406002205746E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" t="s">
         <v>75</v>
       </c>
@@ -4494,7 +4491,7 @@
         <v>7.3659043156954135E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" t="s">
         <v>198</v>
       </c>
@@ -4506,7 +4503,7 @@
         <v>7.1243992561644172E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" t="s">
         <v>125</v>
       </c>
@@ -4518,7 +4515,7 @@
         <v>6.3596332343162591E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" t="s">
         <v>129</v>
       </c>
@@ -4530,7 +4527,7 @@
         <v>5.594867212468101E-4</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" t="s">
         <v>68</v>
       </c>
@@ -4542,7 +4539,7 @@
         <v>5.5546163692129352E-4</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" t="s">
         <v>16</v>
       </c>
@@ -4554,7 +4551,7 @@
         <v>5.1118570934061071E-4</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" t="s">
         <v>92</v>
       </c>
@@ -4566,7 +4563,7 @@
         <v>4.669097817599279E-4</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -4578,7 +4575,7 @@
         <v>3.4213216766891265E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" t="s">
         <v>139</v>
       </c>
@@ -4590,7 +4587,7 @@
         <v>2.8175590278616339E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" t="s">
         <v>141</v>
       </c>
@@ -4602,7 +4599,7 @@
         <v>2.6968064980961351E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" t="s">
         <v>89</v>
       </c>
@@ -4614,7 +4611,7 @@
         <v>2.3345489087996395E-4</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" t="s">
         <v>24</v>
       </c>
@@ -4626,7 +4623,7 @@
         <v>1.4892812004411492E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" t="s">
         <v>36</v>
       </c>
@@ -4638,7 +4635,7 @@
         <v>1.3685286706756507E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" t="s">
         <v>9</v>
       </c>
@@ -4650,7 +4647,7 @@
         <v>1.2880269841653182E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" t="s">
         <v>120</v>
       </c>
@@ -4662,7 +4659,7 @@
         <v>1.247776140910152E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" t="s">
         <v>96</v>
       </c>
@@ -4674,7 +4671,7 @@
         <v>1.0867727678894872E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" t="s">
         <v>27</v>
       </c>
@@ -4686,7 +4683,7 @@
         <v>1.0867727678894872E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" t="s">
         <v>163</v>
       </c>
@@ -4698,7 +4695,7 @@
         <v>8.855185516136563E-5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
         <v>34</v>
       </c>
@@ -4710,7 +4707,7 @@
         <v>5.2326096231716057E-5</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
         <v>87</v>
       </c>
@@ -4722,7 +4719,7 @@
         <v>3.2200674604132955E-5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
         <v>86</v>
       </c>
@@ -4734,7 +4731,7 @@
         <v>2.0125421627583099E-5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
         <v>93</v>
       </c>
@@ -4746,7 +4743,7 @@
         <v>1.6100337302066478E-5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
         <v>123</v>
       </c>
@@ -4758,7 +4755,7 @@
         <v>1.6100337302066478E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
         <v>126</v>
       </c>
@@ -4770,7 +4767,7 @@
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -4782,7 +4779,7 @@
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -4794,7 +4791,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
         <v>124</v>
       </c>
@@ -4806,7 +4803,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
         <v>145</v>
       </c>
@@ -4818,7 +4815,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
         <v>101</v>
       </c>
@@ -4830,7 +4827,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
         <v>173</v>
       </c>
@@ -4842,7 +4839,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
         <v>29</v>
       </c>
@@ -4854,7 +4851,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
         <v>112</v>
       </c>
@@ -4866,7 +4863,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
         <v>109</v>
       </c>
@@ -4878,7 +4875,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
         <v>150</v>
       </c>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9398651-4F37-4E20-9FE2-4FF084FD151C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99C9471B-EF4E-4FDE-9648-2B2FF6D3D5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Last activity'!$A$1:$D$83</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Last activity'!$A$1:$D$83</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,12 +42,102 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="254">
+  <si>
+    <t>Termination Reason</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>Customer Left</t>
+  </si>
+  <si>
+    <t>Agent Left</t>
+  </si>
+  <si>
+    <t>System disconnected the contact</t>
+  </si>
+  <si>
+    <t>NO_ANSWER_FROM_AGENT</t>
+  </si>
+  <si>
+    <t>RONA_TIMER_EXPIRED</t>
+  </si>
+  <si>
+    <t>Queue Timeout</t>
+  </si>
+  <si>
+    <t>NO_ANSWER_FROM_CUSTOMER</t>
+  </si>
+  <si>
+    <t>RONA Timer Expired</t>
+  </si>
+  <si>
+    <t>AGENT_ENDS</t>
+  </si>
+  <si>
+    <t>CUSTOMER_UNAVAILABLE</t>
+  </si>
+  <si>
+    <t>System Error</t>
+  </si>
+  <si>
+    <t>CUSTOMER_BUSY</t>
+  </si>
+  <si>
+    <t>USER_UNAVAILABLE</t>
+  </si>
+  <si>
+    <t>NO_ANSWER_USER</t>
+  </si>
+  <si>
+    <t>USER_BUSY</t>
+  </si>
+  <si>
+    <t>MEDIA_MANAGER_INTERNAL_ERROR</t>
+  </si>
+  <si>
+    <t>AGENT_UNAVAILABLE</t>
+  </si>
+  <si>
+    <t>MAX_CALLBACK_RETRY_LIMIT_REACHED</t>
+  </si>
+  <si>
+    <t>AGENT_BUSY</t>
+  </si>
+  <si>
+    <t>USER_DECLINED</t>
+  </si>
+  <si>
+    <t>Participant Invite timer expired</t>
+  </si>
+  <si>
+    <t>CONTACT_CALLBACK_IN_PROGRESS</t>
+  </si>
+  <si>
+    <t>OUTDIAL_FAILED</t>
+  </si>
+  <si>
+    <t>CHANNEL_FAILURE</t>
+  </si>
+  <si>
+    <t>NO_ANSWER_CUSTOMER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total: </t>
+  </si>
   <si>
     <t>Activity Name</t>
   </si>
   <si>
-    <t>Termination Reason</t>
+    <t>Number of rows</t>
+  </si>
+  <si>
+    <t>#Calls (distinct contact session IDs)</t>
+  </si>
+  <si>
+    <t>Ratio</t>
   </si>
   <si>
     <t>LanguageSelectionMenu</t>
@@ -65,294 +155,213 @@
     <t>LegalMenu2</t>
   </si>
   <si>
+    <t>ClosedQueueMenu</t>
+  </si>
+  <si>
+    <t>SeniorsConfirmationMenu</t>
+  </si>
+  <si>
+    <t>SuburbsOrCityMenu</t>
+  </si>
+  <si>
+    <t>StaffDirectoryEnglishTransfer</t>
+  </si>
+  <si>
+    <t>ClinicVoicemailTransfer</t>
+  </si>
+  <si>
+    <t>FamilyMenu</t>
+  </si>
+  <si>
+    <t>ClosedMenu</t>
+  </si>
+  <si>
+    <t>DisconnectContact1</t>
+  </si>
+  <si>
+    <t>HousingMenu</t>
+  </si>
+  <si>
+    <t>SeniorsADAPTMenu</t>
+  </si>
+  <si>
+    <t>PreTenantMenu</t>
+  </si>
+  <si>
+    <t>OtherLegalMenu</t>
+  </si>
+  <si>
+    <t>AppointmentMenu</t>
+  </si>
+  <si>
+    <t>TenantMenu</t>
+  </si>
+  <si>
+    <t>HelpWithLegalorOtherReasonMenu</t>
+  </si>
+  <si>
+    <t>PreQueueMessage2</t>
+  </si>
+  <si>
+    <t>DivorceOrParentingMenu</t>
+  </si>
+  <si>
+    <t>OtherLegalOtherMenu</t>
+  </si>
+  <si>
+    <t>FarmworkerMainMenu</t>
+  </si>
+  <si>
+    <t>LegalServerScreenPop</t>
+  </si>
+  <si>
+    <t>DisconnectContact</t>
+  </si>
+  <si>
+    <t>SetCallerID</t>
+  </si>
+  <si>
+    <t>ReadANI</t>
+  </si>
+  <si>
+    <t>PlayMOH300s</t>
+  </si>
+  <si>
+    <t>PlayCCBConfirmation</t>
+  </si>
+  <si>
+    <t>CCB</t>
+  </si>
+  <si>
+    <t>QueueMenu1</t>
+  </si>
+  <si>
+    <t>SuburbanSeniorsMenu</t>
+  </si>
+  <si>
+    <t>FrontDeskTransfer1</t>
+  </si>
+  <si>
+    <t>BenefitsMenu</t>
+  </si>
+  <si>
+    <t>IntakePreQueueMessage1</t>
+  </si>
+  <si>
+    <t>FrontDeskTransfer2</t>
+  </si>
+  <si>
+    <t>SubSeniorPreQueueMessage1_1</t>
+  </si>
+  <si>
+    <t>EmploymentMenu</t>
+  </si>
+  <si>
+    <t>TenantDeterrenceMenu</t>
+  </si>
+  <si>
+    <t>StaffDirectorySpanishTransfer</t>
+  </si>
+  <si>
+    <t>ImmigrationMenu</t>
+  </si>
+  <si>
+    <t>AddressFaxHoursMenu</t>
+  </si>
+  <si>
+    <t>GetLoggedInFamilyAgents</t>
+  </si>
+  <si>
+    <t>FrontDeskTransfer</t>
+  </si>
+  <si>
+    <t>SimpleDivorceMenu</t>
+  </si>
+  <si>
+    <t>HolidayPrompt</t>
+  </si>
+  <si>
     <t>CriminalRecordsVoicemailTransfer</t>
   </si>
   <si>
-    <t>Agent Left</t>
-  </si>
-  <si>
-    <t>DisconnectContact</t>
-  </si>
-  <si>
-    <t>SetCallerID</t>
-  </si>
-  <si>
-    <t>Customer Left</t>
-  </si>
-  <si>
-    <t>ClosedMenu</t>
-  </si>
-  <si>
-    <t>FrontDeskTransfer1</t>
-  </si>
-  <si>
-    <t>SeniorsConfirmationMenu</t>
-  </si>
-  <si>
-    <t>SuburbsOrCityMenu</t>
+    <t>ChildSupportMenu</t>
+  </si>
+  <si>
+    <t>OtherLegalCriminalCaseMenu</t>
+  </si>
+  <si>
+    <t>HIVMenu</t>
+  </si>
+  <si>
+    <t>OtherLegalPersonalInjuryMenu</t>
+  </si>
+  <si>
+    <t>FamilyQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInConsumerAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorOtherAgents</t>
+  </si>
+  <si>
+    <t>CallbackRetry</t>
+  </si>
+  <si>
+    <t>ConsumerQueue</t>
   </si>
   <si>
     <t>SeniorNotCookCoMenu</t>
   </si>
   <si>
+    <t>GetLoggedInHousingAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorOtherQueue</t>
+  </si>
+  <si>
+    <t>ComplimentOrComplaintMenu</t>
+  </si>
+  <si>
+    <t>HousingQueue</t>
+  </si>
+  <si>
+    <t>CollectCallbackNumber</t>
+  </si>
+  <si>
+    <t>ConfirmCallbackNumber</t>
+  </si>
+  <si>
+    <t>ImmigrationOtherMenu</t>
+  </si>
+  <si>
+    <t>GetLoggedInBenefitsAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorTenantAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorBenefitsAgents</t>
+  </si>
+  <si>
+    <t>HIVVoicemailTransfer</t>
+  </si>
+  <si>
+    <t>BenefitsQueue</t>
+  </si>
+  <si>
+    <t>ScreenPopProcessComplete</t>
+  </si>
+  <si>
+    <t>SubSeniorTenantQueue</t>
+  </si>
+  <si>
+    <t>SubSeniorBenefitsQueue</t>
+  </si>
+  <si>
     <t>ThankYouGoodbye</t>
   </si>
   <si>
-    <t>DisconnectContact1</t>
-  </si>
-  <si>
-    <t>System disconnected the contact</t>
-  </si>
-  <si>
-    <t>FamilyMenu</t>
-  </si>
-  <si>
-    <t>GetLoggedInFamilyAgents</t>
-  </si>
-  <si>
-    <t>IntakePreQueueMessage1</t>
-  </si>
-  <si>
-    <t>FamilyQueue</t>
-  </si>
-  <si>
-    <t>PreQueueMessage2</t>
-  </si>
-  <si>
-    <t>PlayMOH300s</t>
-  </si>
-  <si>
-    <t>QueueMenu1</t>
-  </si>
-  <si>
-    <t>ReadANI</t>
-  </si>
-  <si>
-    <t>CCB</t>
-  </si>
-  <si>
-    <t>PlayCCBConfirmation</t>
-  </si>
-  <si>
-    <t>LegalServerScreenPop</t>
-  </si>
-  <si>
-    <t>RONA_TIMER_EXPIRED</t>
-  </si>
-  <si>
-    <t>NO_ANSWER_FROM_AGENT</t>
-  </si>
-  <si>
-    <t>AGENT_ENDS</t>
-  </si>
-  <si>
-    <t>CallbackRetry</t>
-  </si>
-  <si>
-    <t>Queue Timeout</t>
-  </si>
-  <si>
-    <t>HelpWithLegalorOtherReasonMenu</t>
-  </si>
-  <si>
-    <t>StaffDirectoryEnglishTransfer</t>
-  </si>
-  <si>
-    <t>HousingMenu</t>
-  </si>
-  <si>
-    <t>PreTenantMenu</t>
-  </si>
-  <si>
-    <t>TenantMenu</t>
-  </si>
-  <si>
-    <t>TenantDeterrenceMenu</t>
-  </si>
-  <si>
-    <t>SeniorsADAPTMenu</t>
-  </si>
-  <si>
-    <t>DivorceOrParentingMenu</t>
-  </si>
-  <si>
-    <t>SimpleDivorceMenu</t>
-  </si>
-  <si>
-    <t>ClinicVoicemailTransfer</t>
-  </si>
-  <si>
-    <t>NO_ANSWER_FROM_CUSTOMER</t>
-  </si>
-  <si>
-    <t>RONA Timer Expired</t>
-  </si>
-  <si>
-    <t>CUSTOMER_UNAVAILABLE</t>
-  </si>
-  <si>
-    <t>System Error</t>
-  </si>
-  <si>
-    <t>CUSTOMER_BUSY</t>
-  </si>
-  <si>
-    <t>USER_UNAVAILABLE</t>
-  </si>
-  <si>
-    <t>NO_ANSWER_USER</t>
-  </si>
-  <si>
-    <t>USER_BUSY</t>
-  </si>
-  <si>
-    <t>MEDIA_MANAGER_INTERNAL_ERROR</t>
-  </si>
-  <si>
-    <t>AGENT_UNAVAILABLE</t>
-  </si>
-  <si>
-    <t>MAX_CALLBACK_RETRY_LIMIT_REACHED</t>
-  </si>
-  <si>
-    <t>AGENT_BUSY</t>
-  </si>
-  <si>
-    <t>USER_DECLINED</t>
-  </si>
-  <si>
-    <t>Participant Invite timer expired</t>
-  </si>
-  <si>
-    <t>CONTACT_CALLBACK_IN_PROGRESS</t>
-  </si>
-  <si>
-    <t>OUTDIAL_FAILED</t>
-  </si>
-  <si>
-    <t>CHANNEL_FAILURE</t>
-  </si>
-  <si>
-    <t>NO_ANSWER_CUSTOMER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total: </t>
-  </si>
-  <si>
-    <t>Frequency</t>
-  </si>
-  <si>
-    <t>ClosedQueueMenu</t>
-  </si>
-  <si>
-    <t>OtherLegalMenu</t>
-  </si>
-  <si>
-    <t>AppointmentMenu</t>
-  </si>
-  <si>
-    <t>OtherLegalOtherMenu</t>
-  </si>
-  <si>
-    <t>FarmworkerMainMenu</t>
-  </si>
-  <si>
-    <t>SuburbanSeniorsMenu</t>
-  </si>
-  <si>
-    <t>BenefitsMenu</t>
-  </si>
-  <si>
-    <t>FrontDeskTransfer2</t>
-  </si>
-  <si>
-    <t>ImmigrationMenu</t>
-  </si>
-  <si>
-    <t>EmploymentMenu</t>
-  </si>
-  <si>
-    <t>SubSeniorPreQueueMessage1_1</t>
-  </si>
-  <si>
-    <t>AddressFaxHoursMenu</t>
-  </si>
-  <si>
-    <t>StaffDirectorySpanishTransfer</t>
-  </si>
-  <si>
-    <t>HIVMenu</t>
-  </si>
-  <si>
-    <t>OtherLegalCriminalCaseMenu</t>
-  </si>
-  <si>
-    <t>FrontDeskTransfer</t>
-  </si>
-  <si>
-    <t>ChildSupportMenu</t>
-  </si>
-  <si>
-    <t>OtherLegalPersonalInjuryMenu</t>
-  </si>
-  <si>
-    <t>HolidayPrompt</t>
-  </si>
-  <si>
-    <t>GetLoggedInConsumerAgents</t>
-  </si>
-  <si>
-    <t>CollectCallbackNumber</t>
-  </si>
-  <si>
-    <t>GetLoggedInSubSeniorOtherAgents</t>
-  </si>
-  <si>
-    <t>ConsumerQueue</t>
-  </si>
-  <si>
-    <t>ComplimentOrComplaintMenu</t>
-  </si>
-  <si>
-    <t>GetLoggedInHousingAgents</t>
-  </si>
-  <si>
-    <t>SubSeniorOtherQueue</t>
-  </si>
-  <si>
-    <t>ImmigrationOtherMenu</t>
-  </si>
-  <si>
-    <t>ConfirmCallbackNumber</t>
-  </si>
-  <si>
-    <t>HousingQueue</t>
-  </si>
-  <si>
-    <t>GetLoggedInBenefitsAgents</t>
-  </si>
-  <si>
-    <t>GetLoggedInSubSeniorTenantAgents</t>
-  </si>
-  <si>
-    <t>ScreenPopProcessComplete</t>
-  </si>
-  <si>
-    <t>GetLoggedInSubSeniorBenefitsAgents</t>
-  </si>
-  <si>
-    <t>HIVVoicemailTransfer</t>
-  </si>
-  <si>
-    <t>BenefitsQueue</t>
-  </si>
-  <si>
-    <t>SubSeniorTenantQueue</t>
-  </si>
-  <si>
-    <t>SubSeniorBenefitsQueue</t>
-  </si>
-  <si>
     <t>GetLoggedInEmploymentAgents</t>
   </si>
   <si>
@@ -404,18 +413,18 @@
     <t>GetLoggedInImmigrationSPAgents</t>
   </si>
   <si>
+    <t>GetLoggedInSubSeniorEmploymentAgents</t>
+  </si>
+  <si>
+    <t>VeteransBenefitsVoicemailTransfer</t>
+  </si>
+  <si>
+    <t>SubSeniorPreQueueMessage1_2</t>
+  </si>
+  <si>
     <t>WorkersCompMenu</t>
   </si>
   <si>
-    <t>GetLoggedInSubSeniorEmploymentAgents</t>
-  </si>
-  <si>
-    <t>VeteransBenefitsVoicemailTransfer</t>
-  </si>
-  <si>
-    <t>SubSeniorPreQueueMessage1_2</t>
-  </si>
-  <si>
     <t>ImmigrationSPQueue</t>
   </si>
   <si>
@@ -623,114 +632,180 @@
     <t>EmploymentSubSeniorsSPQueue</t>
   </si>
   <si>
-    <t>Ratio</t>
-  </si>
-  <si>
-    <t>Number of rows</t>
-  </si>
-  <si>
     <t>Last activity</t>
   </si>
   <si>
-    <t>#Calls (distinct contact session IDs)</t>
+    <t>Last activity menu</t>
   </si>
   <si>
     <t>Percent</t>
   </si>
   <si>
-    <t>No activity</t>
-  </si>
-  <si>
     <t>Outcome</t>
   </si>
   <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Verify by calling LegalAid</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Tagging Initiated by</t>
+  </si>
+  <si>
+    <t>Tagging Verified by</t>
+  </si>
+  <si>
+    <t>EDA team 1 / 2</t>
+  </si>
+  <si>
+    <t>Pre-legal seniors menu, legal menu, Family, Housing, Benefits, Employment, Immigration</t>
+  </si>
+  <si>
     <t>Negative</t>
   </si>
   <si>
-    <t>Verify by calling LegalAid</t>
+    <t>Closed queue</t>
+  </si>
+  <si>
+    <t>Krish</t>
+  </si>
+  <si>
+    <t>Main Menu, Holiday &amp; Closed Menu</t>
+  </si>
+  <si>
+    <t>Positive (Tentative)</t>
   </si>
   <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Closed queue</t>
+    <t>Vivi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start Menu (LAC Main Number) </t>
   </si>
   <si>
     <t>Abandoned</t>
   </si>
   <si>
-    <t>Comment</t>
+    <t>Main Menu, Holiday &amp; Closed Menu, Family Menu, Housing Menu, Other Legal Menu, Closed Queue Menu</t>
+  </si>
+  <si>
+    <t>Positive / Negative</t>
+  </si>
+  <si>
+    <t>If EP name = 'Closed Queue Menu Telephony EP', then Negative, and type = "Closed queue",
+otherwise Positive, type = 'Reached voicemail'</t>
+  </si>
+  <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>Neutral / Negative</t>
   </si>
   <si>
     <t>If EP name = Closed Hours-Holidays Menu Telephony EP	, then Neutral, type = "After hours call"
 If EP name = Closed Queue Menu Telephony EP, then Negative, type = "Closed Queue"</t>
   </si>
   <si>
-    <t>Positive / Negative</t>
-  </si>
-  <si>
-    <t>Neutral / Negative</t>
-  </si>
-  <si>
-    <t>Positive (Tentative)</t>
-  </si>
-  <si>
-    <t>If EP name = 'Closed Queue Menu Telephony EP', then Negative, and type = "Closed queue",
-otherwise Positive, type = 'Reached voicemail'</t>
-  </si>
-  <si>
-    <t>Krish</t>
+    <t>Legal Menu</t>
+  </si>
+  <si>
+    <t>Callers are spending time on this activity, but not sure what are they doing, ask Mark</t>
   </si>
   <si>
     <t>ask Mark</t>
   </si>
   <si>
-    <t>Callers are spending time on this activity, but not sure what are they doing, ask Mark</t>
-  </si>
-  <si>
-    <t>EDA team 1 / 2</t>
-  </si>
-  <si>
-    <t>Last activity menu</t>
-  </si>
-  <si>
-    <t>Legal Menu</t>
-  </si>
-  <si>
-    <t>Pre-legal seniors menu, legal menu, Family, Housing, Benefits, Employment, Immigration</t>
+    <t xml:space="preserve">Positive / Neutral </t>
+  </si>
+  <si>
+    <t xml:space="preserve">If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect </t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front Desk </t>
+  </si>
+  <si>
+    <t>No input for language selection;</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Appointment Menu</t>
+  </si>
+  <si>
+    <t>Caller has an appointment scheduled</t>
+  </si>
+  <si>
+    <t>Other Legal Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive </t>
+  </si>
+  <si>
+    <t>Caller requests an interpreter</t>
+  </si>
+  <si>
+    <t>Housing menu</t>
+  </si>
+  <si>
+    <t>Voice Mail Transfer</t>
+  </si>
+  <si>
+    <t>Family menu</t>
+  </si>
+  <si>
+    <t>Legal menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queues </t>
+  </si>
+  <si>
+    <t>Pre-legal seniors menu</t>
+  </si>
+  <si>
+    <t>HIV Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Menu </t>
+  </si>
+  <si>
+    <t>Issue not handled by LAC</t>
+  </si>
+  <si>
+    <t>No input</t>
   </si>
   <si>
     <t>Immigration menu</t>
   </si>
   <si>
-    <t>Benefits menu</t>
-  </si>
-  <si>
-    <t>Family menu</t>
-  </si>
-  <si>
-    <t>Housing menu</t>
-  </si>
-  <si>
-    <t>HIV menu</t>
-  </si>
-  <si>
-    <t>Legal menu</t>
+    <t>Pre-Legal Seniors Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abandoned </t>
+  </si>
+  <si>
+    <t>Benefits Menu</t>
   </si>
   <si>
     <t>Employment menu</t>
   </si>
   <si>
-    <t>Pre-legal seniors menu</t>
-  </si>
-  <si>
-    <t>Tagging Initiated by</t>
-  </si>
-  <si>
-    <t>Tagging Verified by</t>
+    <t>No activity</t>
+  </si>
+  <si>
+    <t>Immigration Menu</t>
   </si>
 </sst>
 </file>
@@ -741,7 +816,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1154,223 +1229,223 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="32.83984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2">
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2">
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2">
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2">
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="B13">
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="B16">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B17">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="B19">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="B20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="B21">
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="B22">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="B23">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2">
         <v>100373</v>
@@ -1384,33 +1459,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="36.83984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.15625" customWidth="1"/>
-    <col min="4" max="4" width="9.15625" customWidth="1"/>
-    <col min="5" max="5" width="11.68359375" customWidth="1"/>
-    <col min="6" max="6" width="31.47265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.3125" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="28.9">
       <c r="A3" s="4" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>194</v>
+        <v>29</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>196</v>
+        <v>30</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2">
         <v>267656</v>
@@ -1422,9 +1497,9 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2">
         <v>186138</v>
@@ -1436,9 +1511,9 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2">
         <v>125748</v>
@@ -1450,9 +1525,9 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2">
         <v>96331</v>
@@ -1464,9 +1539,9 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B8" s="2">
         <v>110890</v>
@@ -1478,9 +1553,9 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="B9" s="2">
         <v>87903</v>
@@ -1492,9 +1567,9 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="B10" s="2">
         <v>30337</v>
@@ -1506,9 +1581,9 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B11" s="2">
         <v>28301</v>
@@ -1520,9 +1595,9 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B12" s="2">
         <v>28035</v>
@@ -1534,9 +1609,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B13" s="2">
         <v>25721</v>
@@ -1548,9 +1623,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2">
         <v>27415</v>
@@ -1562,9 +1637,9 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2">
         <v>23629</v>
@@ -1576,9 +1651,9 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2">
         <v>20584</v>
@@ -1590,9 +1665,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2">
         <v>23145</v>
@@ -1604,9 +1679,9 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B18" s="2">
         <v>21736</v>
@@ -1618,9 +1693,9 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B19" s="2">
         <v>16045</v>
@@ -1632,9 +1707,9 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2">
         <v>31956</v>
@@ -1646,9 +1721,9 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2">
         <v>13946</v>
@@ -1660,9 +1735,9 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2">
         <v>17218</v>
@@ -1674,9 +1749,9 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2">
         <v>12477</v>
@@ -1688,9 +1763,9 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2">
         <v>11815</v>
@@ -1702,9 +1777,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2">
         <v>15190</v>
@@ -1716,9 +1791,9 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B26" s="2">
         <v>13509</v>
@@ -1730,9 +1805,9 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="B27" s="2">
         <v>10243</v>
@@ -1744,9 +1819,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B28" s="2">
         <v>11751</v>
@@ -1758,9 +1833,9 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2">
         <v>9390</v>
@@ -1772,9 +1847,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2">
         <v>18734</v>
@@ -1786,9 +1861,9 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="B31" s="2">
         <v>9500</v>
@@ -1800,9 +1875,9 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B32" s="2">
         <v>25847</v>
@@ -1814,9 +1889,9 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="B33" s="2">
         <v>9028</v>
@@ -1828,9 +1903,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="B34" s="2">
         <v>9028</v>
@@ -1842,9 +1917,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="B35" s="2">
         <v>24299</v>
@@ -1856,9 +1931,9 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B36" s="2">
         <v>8909</v>
@@ -1870,9 +1945,9 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="B37" s="2">
         <v>7912</v>
@@ -1884,9 +1959,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B38" s="2">
         <v>8030</v>
@@ -1898,9 +1973,9 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="B39" s="2">
         <v>7281</v>
@@ -1912,9 +1987,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B40" s="2">
         <v>6895</v>
@@ -1926,9 +2001,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B41" s="2">
         <v>4933</v>
@@ -1940,9 +2015,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B42" s="2">
         <v>5272</v>
@@ -1954,9 +2029,9 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="B43" s="2">
         <v>4567</v>
@@ -1968,9 +2043,9 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B44" s="2">
         <v>3959</v>
@@ -1982,9 +2057,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B45" s="2">
         <v>5299</v>
@@ -1996,9 +2071,9 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B46" s="2">
         <v>4025</v>
@@ -2010,9 +2085,9 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="B47" s="2">
         <v>2563</v>
@@ -2024,9 +2099,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B48" s="2">
         <v>2545</v>
@@ -2038,9 +2113,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="B49" s="2">
         <v>2601</v>
@@ -2052,9 +2127,9 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B50" s="2">
         <v>2394</v>
@@ -2066,9 +2141,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="B51" s="2">
         <v>2267</v>
@@ -2080,9 +2155,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B52" s="2">
         <v>2437</v>
@@ -2094,9 +2169,9 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B53" s="2">
         <v>2570</v>
@@ -2108,9 +2183,9 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B54" s="2">
         <v>3512</v>
@@ -2122,7 +2197,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2136,9 +2211,9 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="B56" s="2">
         <v>1945</v>
@@ -2150,7 +2225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2164,9 +2239,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B58" s="2">
         <v>1527</v>
@@ -2178,9 +2253,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="B59" s="2">
         <v>3011</v>
@@ -2192,7 +2267,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2206,9 +2281,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>16</v>
+        <v>89</v>
       </c>
       <c r="B61" s="2">
         <v>1312</v>
@@ -2220,7 +2295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2234,7 +2309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2248,9 +2323,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B64" s="2">
         <v>1257</v>
@@ -2262,9 +2337,9 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B65" s="2">
         <v>1059</v>
@@ -2276,9 +2351,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B66" s="2">
         <v>1643</v>
@@ -2290,9 +2365,9 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B67" s="2">
         <v>1155</v>
@@ -2304,9 +2379,9 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B68" s="2">
         <v>1188</v>
@@ -2318,9 +2393,9 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B69" s="2">
         <v>970</v>
@@ -2332,9 +2407,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B70" s="2">
         <v>904</v>
@@ -2346,9 +2421,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B71" s="2">
         <v>850</v>
@@ -2360,9 +2435,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B72" s="2">
         <v>836</v>
@@ -2374,9 +2449,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B73" s="2">
         <v>789</v>
@@ -2388,9 +2463,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B74" s="2">
         <v>895</v>
@@ -2402,9 +2477,9 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B75" s="2">
         <v>684</v>
@@ -2416,9 +2491,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B76" s="2">
         <v>683</v>
@@ -2430,9 +2505,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="B77" s="2">
         <v>679</v>
@@ -2444,9 +2519,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B78" s="2">
         <v>662</v>
@@ -2458,9 +2533,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B79" s="2">
         <v>652</v>
@@ -2472,9 +2547,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B80" s="2">
         <v>602</v>
@@ -2486,9 +2561,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B81" s="2">
         <v>571</v>
@@ -2500,9 +2575,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B82" s="2">
         <v>541</v>
@@ -2514,9 +2589,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B83" s="2">
         <v>514</v>
@@ -2528,9 +2603,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B84" s="2">
         <v>508</v>
@@ -2542,9 +2617,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B85" s="2">
         <v>482</v>
@@ -2556,9 +2631,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B86" s="2">
         <v>468</v>
@@ -2570,9 +2645,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B87" s="2">
         <v>453</v>
@@ -2584,9 +2659,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B88" s="2">
         <v>412</v>
@@ -2598,9 +2673,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B89" s="2">
         <v>379</v>
@@ -2612,9 +2687,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B90" s="2">
         <v>316</v>
@@ -2626,9 +2701,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B91" s="2">
         <v>310</v>
@@ -2640,9 +2715,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B92" s="2">
         <v>260</v>
@@ -2654,9 +2729,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B93" s="2">
         <v>257</v>
@@ -2668,9 +2743,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B94" s="2">
         <v>197</v>
@@ -2682,9 +2757,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B95" s="2">
         <v>192</v>
@@ -2696,9 +2771,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B96" s="2">
         <v>185</v>
@@ -2710,9 +2785,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B97" s="2">
         <v>174</v>
@@ -2724,9 +2799,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B98" s="2">
         <v>194</v>
@@ -2738,9 +2813,9 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B99" s="2">
         <v>166</v>
@@ -2752,9 +2827,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B100" s="2">
         <v>158</v>
@@ -2766,9 +2841,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B101" s="2">
         <v>155</v>
@@ -2780,9 +2855,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B102" s="2">
         <v>152</v>
@@ -2794,9 +2869,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B103" s="2">
         <v>146</v>
@@ -2808,9 +2883,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B104" s="2">
         <v>139</v>
@@ -2822,9 +2897,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B105" s="2">
         <v>121</v>
@@ -2836,9 +2911,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B106" s="2">
         <v>120</v>
@@ -2850,9 +2925,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B107" s="2">
         <v>119</v>
@@ -2864,9 +2939,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B108" s="2">
         <v>108</v>
@@ -2878,9 +2953,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B109" s="2">
         <v>95</v>
@@ -2892,9 +2967,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B110" s="2">
         <v>95</v>
@@ -2906,9 +2981,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B111" s="2">
         <v>83</v>
@@ -2920,9 +2995,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B112" s="2">
         <v>82</v>
@@ -2934,9 +3009,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B113" s="2">
         <v>82</v>
@@ -2948,9 +3023,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B114" s="2">
         <v>70</v>
@@ -2962,9 +3037,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B115" s="2">
         <v>67</v>
@@ -2976,9 +3051,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B116" s="2">
         <v>67</v>
@@ -2990,9 +3065,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B117" s="2">
         <v>67</v>
@@ -3004,9 +3079,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B118" s="2">
         <v>63</v>
@@ -3018,9 +3093,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B119" s="2">
         <v>56</v>
@@ -3032,9 +3107,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B120" s="2">
         <v>47</v>
@@ -3046,9 +3121,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B121" s="2">
         <v>46</v>
@@ -3060,9 +3135,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B122" s="2">
         <v>46</v>
@@ -3074,9 +3149,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B123" s="2">
         <v>45</v>
@@ -3088,9 +3163,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B124" s="2">
         <v>44</v>
@@ -3102,9 +3177,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B125" s="2">
         <v>44</v>
@@ -3116,9 +3191,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B126" s="2">
         <v>36</v>
@@ -3130,9 +3205,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B127" s="2">
         <v>36</v>
@@ -3144,9 +3219,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B128" s="2">
         <v>33</v>
@@ -3158,9 +3233,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B129" s="2">
         <v>33</v>
@@ -3172,9 +3247,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B130" s="2">
         <v>30</v>
@@ -3186,9 +3261,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B131" s="2">
         <v>29</v>
@@ -3200,9 +3275,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B132" s="2">
         <v>29</v>
@@ -3214,9 +3289,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B133" s="2">
         <v>27</v>
@@ -3228,9 +3303,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B134" s="2">
         <v>26</v>
@@ -3242,9 +3317,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B135" s="2">
         <v>26</v>
@@ -3256,9 +3331,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B136" s="2">
         <v>24</v>
@@ -3270,9 +3345,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B137" s="2">
         <v>23</v>
@@ -3284,9 +3359,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B138" s="2">
         <v>22</v>
@@ -3298,9 +3373,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B139" s="2">
         <v>21</v>
@@ -3312,9 +3387,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B140" s="2">
         <v>21</v>
@@ -3326,9 +3401,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B141" s="2">
         <v>20</v>
@@ -3340,9 +3415,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B142" s="2">
         <v>19</v>
@@ -3354,9 +3429,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B143" s="2">
         <v>18</v>
@@ -3368,9 +3443,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B144" s="2">
         <v>17</v>
@@ -3382,9 +3457,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B145" s="2">
         <v>17</v>
@@ -3396,9 +3471,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B146" s="2">
         <v>16</v>
@@ -3410,9 +3485,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B147" s="2">
         <v>16</v>
@@ -3424,9 +3499,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B148" s="2">
         <v>15</v>
@@ -3438,9 +3513,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B149" s="2">
         <v>14</v>
@@ -3452,9 +3527,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B150" s="2">
         <v>13</v>
@@ -3466,9 +3541,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B151" s="2">
         <v>12</v>
@@ -3480,9 +3555,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B152" s="2">
         <v>11</v>
@@ -3494,9 +3569,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B153" s="2">
         <v>10</v>
@@ -3508,9 +3583,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B154" s="2">
         <v>9</v>
@@ -3522,9 +3597,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="B155" s="2">
         <v>9</v>
@@ -3536,9 +3611,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B156" s="2">
         <v>9</v>
@@ -3550,9 +3625,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B157" s="2">
         <v>9</v>
@@ -3564,9 +3639,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="B158" s="2">
         <v>7</v>
@@ -3578,9 +3653,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B159" s="2">
         <v>6</v>
@@ -3592,9 +3667,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B160" s="2">
         <v>4</v>
@@ -3606,9 +3681,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B161" s="2">
         <v>4</v>
@@ -3620,9 +3695,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B162" s="2">
         <v>3</v>
@@ -3634,9 +3709,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B163" s="2">
         <v>3</v>
@@ -3648,9 +3723,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B164" s="2">
         <v>2</v>
@@ -3662,9 +3737,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B165" s="2">
         <v>2</v>
@@ -3676,9 +3751,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B166" s="2">
         <v>1</v>
@@ -3690,9 +3765,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B167" s="2">
         <v>1</v>
@@ -3724,59 +3799,59 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="31.47265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.3125" customWidth="1"/>
-    <col min="3" max="3" width="17.15625" customWidth="1"/>
+    <col min="1" max="1" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.83984375" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.47265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.3125" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:11" ht="43.15">
       <c r="A1" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>196</v>
+        <v>30</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E1" s="7" t="s">
         <v>199</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G1" s="7" t="s">
         <v>201</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="57.6">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="57.6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="C2" s="2">
         <v>39892</v>
@@ -3786,21 +3861,27 @@
         <v>0.16056866391350899</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="I2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="J2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>209</v>
+      </c>
+      <c r="K2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="43.5">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>40</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="C3" s="2">
         <v>28035</v>
@@ -3810,18 +3891,27 @@
         <v>0.11284323906585843</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="I3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>209</v>
+      </c>
+      <c r="J3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="29.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>32</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C4" s="2">
         <v>27545</v>
@@ -3831,18 +3921,24 @@
         <v>0.11087094774635528</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F4" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="I4" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="43.2" x14ac:dyDescent="0.55000000000000004">
+        <v>209</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="72.75">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>41</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>216</v>
       </c>
       <c r="C5" s="2">
         <v>25721</v>
@@ -3852,18 +3948,24 @@
         <v>0.10352919393661297</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="I5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>209</v>
+      </c>
+      <c r="K5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>219</v>
       </c>
       <c r="C6" s="2">
         <v>13075</v>
@@ -3873,18 +3975,21 @@
         <v>5.2627977556129801E-2</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F6" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="I6" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="72" x14ac:dyDescent="0.55000000000000004">
+        <v>209</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="72">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2">
         <v>12010</v>
@@ -3894,21 +3999,24 @@
         <v>4.8341262749454599E-2</v>
       </c>
       <c r="E7" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="I7" t="s">
         <v>209</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="I7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C8" s="2">
         <v>11987</v>
@@ -3918,18 +4026,21 @@
         <v>4.8248685809967717E-2</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F8" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="I8" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+        <v>209</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="28.9">
       <c r="A9" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C9" s="2">
         <v>9640</v>
@@ -3939,18 +4050,18 @@
         <v>3.8801812897980216E-2</v>
       </c>
       <c r="G9" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I9" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C10" s="2">
         <v>9358</v>
@@ -3960,12 +4071,12 @@
         <v>3.7666739118184529E-2</v>
       </c>
       <c r="H10" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="43.5">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C11" s="2">
         <v>8939</v>
@@ -3974,10 +4085,25 @@
         <f t="shared" si="0"/>
         <v>3.5980228785793066E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="E11" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="I11" t="s">
+        <v>213</v>
+      </c>
+      <c r="K11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="50.25" customHeight="1">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>65</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C12" s="2">
         <v>7890</v>
@@ -3986,10 +4112,25 @@
         <f t="shared" si="0"/>
         <v>3.1757915328326128E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="E12" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" t="s">
+        <v>228</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I12" t="s">
+        <v>213</v>
+      </c>
+      <c r="K12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2">
         <v>7765</v>
@@ -3998,10 +4139,22 @@
         <f t="shared" si="0"/>
         <v>3.125477978763655E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="E13" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F13" t="s">
+        <v>231</v>
+      </c>
+      <c r="K13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>232</v>
       </c>
       <c r="C14" s="2">
         <v>6895</v>
@@ -4010,10 +4163,28 @@
         <f t="shared" si="0"/>
         <v>2.7752956424437092E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="E14" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F14" t="s">
+        <v>228</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="I14" t="s">
+        <v>213</v>
+      </c>
+      <c r="K14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>234</v>
       </c>
       <c r="C15" s="2">
         <v>6863</v>
@@ -4022,10 +4193,25 @@
         <f t="shared" si="0"/>
         <v>2.7624153726020562E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="E15" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F15" t="s">
+        <v>215</v>
+      </c>
+      <c r="I15" t="s">
+        <v>213</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="29.25">
       <c r="A16" t="s">
-        <v>78</v>
+        <v>72</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="C16" s="2">
         <v>3959</v>
@@ -4034,10 +4220,19 @@
         <f t="shared" si="0"/>
         <v>1.5935308844720296E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E16" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="K16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15">
       <c r="A17" t="s">
-        <v>81</v>
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>222</v>
       </c>
       <c r="C17" s="2">
         <v>2545</v>
@@ -4046,13 +4241,28 @@
         <f t="shared" si="0"/>
         <v>1.0243839608439796E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E17" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" t="s">
+        <v>228</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="I17" t="s">
+        <v>213</v>
+      </c>
+      <c r="K17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C18" s="2">
         <v>2394</v>
@@ -4061,10 +4271,25 @@
         <f t="shared" si="0"/>
         <v>9.6360518752867871E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E18" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F18" t="s">
+        <v>215</v>
+      </c>
+      <c r="I18" t="s">
+        <v>213</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>222</v>
       </c>
       <c r="C19" s="2">
         <v>2267</v>
@@ -4073,10 +4298,25 @@
         <f t="shared" si="0"/>
         <v>9.1248661659461758E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E19" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F19" t="s">
+        <v>238</v>
+      </c>
+      <c r="I19" t="s">
+        <v>213</v>
+      </c>
+      <c r="K19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15">
       <c r="A20" t="s">
-        <v>69</v>
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
+        <v>234</v>
       </c>
       <c r="C20" s="2">
         <v>2136</v>
@@ -4085,13 +4325,25 @@
         <f t="shared" si="0"/>
         <v>8.5975801193034999E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E20" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F20" t="s">
+        <v>215</v>
+      </c>
+      <c r="I20" t="s">
+        <v>213</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2">
         <v>1462</v>
@@ -4100,10 +4352,25 @@
         <f t="shared" si="0"/>
         <v>5.8846732839052977E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E21" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F21" t="s">
+        <v>215</v>
+      </c>
+      <c r="I21" t="s">
+        <v>213</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>63</v>
+      </c>
+      <c r="B22" t="s">
+        <v>240</v>
       </c>
       <c r="C22" s="2">
         <v>1287</v>
@@ -4112,13 +4379,25 @@
         <f t="shared" si="0"/>
         <v>5.1802835269398892E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E22" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F22" t="s">
+        <v>215</v>
+      </c>
+      <c r="I22" t="s">
+        <v>213</v>
+      </c>
+      <c r="K22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2">
         <v>1267</v>
@@ -4127,13 +4406,25 @@
         <f t="shared" si="0"/>
         <v>5.099781840429557E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E23" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" t="s">
+        <v>215</v>
+      </c>
+      <c r="I23" t="s">
+        <v>213</v>
+      </c>
+      <c r="K23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2">
         <v>1209</v>
@@ -4142,13 +4433,25 @@
         <f t="shared" si="0"/>
         <v>4.8663269495495933E-3</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E24" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F24" t="s">
+        <v>215</v>
+      </c>
+      <c r="I24" t="s">
+        <v>213</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15">
       <c r="A25" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2">
         <v>870</v>
@@ -4157,13 +4460,19 @@
         <f t="shared" si="0"/>
         <v>3.5018233631994591E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E25" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="K25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2">
         <v>837</v>
@@ -4172,10 +4481,25 @@
         <f t="shared" si="0"/>
         <v>3.3689955804574105E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E26" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F26" t="s">
+        <v>215</v>
+      </c>
+      <c r="I26" t="s">
+        <v>213</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="B27" t="s">
+        <v>243</v>
       </c>
       <c r="C27" s="2">
         <v>836</v>
@@ -4184,10 +4508,25 @@
         <f t="shared" si="0"/>
         <v>3.3649704961318939E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E27" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F27" t="s">
+        <v>238</v>
+      </c>
+      <c r="I27" t="s">
+        <v>213</v>
+      </c>
+      <c r="K27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15">
       <c r="A28" t="s">
-        <v>25</v>
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>241</v>
       </c>
       <c r="C28" s="2">
         <v>785</v>
@@ -4196,13 +4535,25 @@
         <f t="shared" si="0"/>
         <v>3.1596911955305462E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E28" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F28" t="s">
+        <v>215</v>
+      </c>
+      <c r="I28" t="s">
+        <v>213</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2">
         <v>771</v>
@@ -4211,10 +4562,22 @@
         <f t="shared" si="0"/>
         <v>3.1033400149733138E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E29" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F29" t="s">
+        <v>215</v>
+      </c>
+      <c r="I29" t="s">
+        <v>213</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15">
       <c r="A30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C30" s="2">
         <v>694</v>
@@ -4224,9 +4587,12 @@
         <v>2.793408521908534E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:11" ht="15">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>74</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>244</v>
       </c>
       <c r="C31" s="2">
         <v>672</v>
@@ -4236,12 +4602,12 @@
         <v>2.7048566667471682E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:11" ht="15">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="C32" s="2">
         <v>604</v>
@@ -4250,13 +4616,26 @@
         <f t="shared" si="0"/>
         <v>2.4311509326120384E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E32" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F32" t="s">
+        <v>245</v>
+      </c>
+      <c r="H32" s="5"/>
+      <c r="I32" t="s">
+        <v>213</v>
+      </c>
+      <c r="K32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C33" s="2">
         <v>543</v>
@@ -4265,10 +4644,25 @@
         <f t="shared" si="0"/>
         <v>2.1856207887555245E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E33" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F33" t="s">
+        <v>215</v>
+      </c>
+      <c r="I33" t="s">
+        <v>213</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15">
       <c r="A34" t="s">
-        <v>107</v>
+        <v>110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>219</v>
       </c>
       <c r="C34" s="2">
         <v>541</v>
@@ -4277,13 +4671,28 @@
         <f t="shared" si="0"/>
         <v>2.1775706201044914E-3</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E34" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F34" t="s">
+        <v>228</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I34" t="s">
+        <v>213</v>
+      </c>
+      <c r="K34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15">
       <c r="A35" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C35" s="2">
         <v>540</v>
@@ -4292,13 +4701,22 @@
         <f t="shared" si="0"/>
         <v>2.1735455357789744E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E35" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="I35" t="s">
+        <v>213</v>
+      </c>
+      <c r="K35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>219</v>
+        <v>247</v>
       </c>
       <c r="C36" s="2">
         <v>527</v>
@@ -4307,10 +4725,25 @@
         <f t="shared" si="0"/>
         <v>2.1212194395472585E-3</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E36" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F36" t="s">
+        <v>215</v>
+      </c>
+      <c r="I36" t="s">
+        <v>213</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="15">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="B37" t="s">
+        <v>248</v>
       </c>
       <c r="C37" s="2">
         <v>502</v>
@@ -4319,11 +4752,26 @@
         <f t="shared" si="0"/>
         <v>2.020592331409343E-3</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E37" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F37" t="s">
+        <v>215</v>
+      </c>
+      <c r="I37" t="s">
+        <v>213</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15">
       <c r="A38" t="s">
         <v>83</v>
       </c>
+      <c r="B38" t="s">
+        <v>234</v>
+      </c>
       <c r="C38" s="2">
         <v>479</v>
       </c>
@@ -4331,10 +4779,25 @@
         <f t="shared" si="0"/>
         <v>1.9280153919224608E-3</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E38" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F38" t="s">
+        <v>245</v>
+      </c>
+      <c r="I38" t="s">
+        <v>213</v>
+      </c>
+      <c r="K38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="B39" t="s">
+        <v>234</v>
       </c>
       <c r="C39" s="2">
         <v>454</v>
@@ -4343,13 +4806,25 @@
         <f t="shared" si="0"/>
         <v>1.8273882837845452E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E39" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F39" t="s">
+        <v>245</v>
+      </c>
+      <c r="I39" t="s">
+        <v>213</v>
+      </c>
+      <c r="K39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C40" s="2">
         <v>444</v>
@@ -4358,13 +4833,25 @@
         <f t="shared" si="0"/>
         <v>1.7871374405293791E-3</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E40" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F40" t="s">
+        <v>249</v>
+      </c>
+      <c r="I40" t="s">
+        <v>213</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C41" s="2">
         <v>442</v>
@@ -4373,10 +4860,22 @@
         <f t="shared" si="0"/>
         <v>1.779087271878346E-3</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E41" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F41" t="s">
+        <v>249</v>
+      </c>
+      <c r="I41" t="s">
+        <v>213</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C42" s="2">
         <v>412</v>
@@ -4386,12 +4885,12 @@
         <v>1.6583347421128473E-3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C43" s="2">
         <v>353</v>
@@ -4401,12 +4900,12 @@
         <v>1.4208547669073666E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="C44" s="2">
         <v>298</v>
@@ -4416,9 +4915,12 @@
         <v>1.1994751290039527E-3</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>69</v>
+      </c>
+      <c r="B45" t="s">
+        <v>248</v>
       </c>
       <c r="C45" s="2">
         <v>278</v>
@@ -4428,9 +4930,9 @@
         <v>1.1189734424936202E-3</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="C46" s="2">
         <v>228</v>
@@ -4440,9 +4942,9 @@
         <v>9.1771922621778929E-4</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="C47" s="2">
         <v>219</v>
@@ -4452,9 +4954,12 @@
         <v>8.8149346728813973E-4</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>248</v>
       </c>
       <c r="C48" s="2">
         <v>212</v>
@@ -4464,9 +4969,12 @@
         <v>8.533178770095233E-4</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
-        <v>122</v>
+        <v>124</v>
+      </c>
+      <c r="B49" t="s">
+        <v>250</v>
       </c>
       <c r="C49" s="2">
         <v>185</v>
@@ -4476,12 +4984,12 @@
         <v>7.446406002205746E-4</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:11">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C50" s="2">
         <v>183</v>
@@ -4491,9 +4999,9 @@
         <v>7.3659043156954135E-4</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="C51" s="2">
         <v>177</v>
@@ -4503,9 +5011,9 @@
         <v>7.1243992561644172E-4</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C52" s="2">
         <v>158</v>
@@ -4515,9 +5023,12 @@
         <v>6.3596332343162591E-4</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:11" ht="15">
       <c r="A53" t="s">
-        <v>129</v>
+        <v>132</v>
+      </c>
+      <c r="B53" t="s">
+        <v>253</v>
       </c>
       <c r="C53" s="2">
         <v>139</v>
@@ -4526,10 +5037,25 @@
         <f t="shared" si="0"/>
         <v>5.594867212468101E-4</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E53" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F53" t="s">
+        <v>238</v>
+      </c>
+      <c r="I53" t="s">
+        <v>213</v>
+      </c>
+      <c r="K53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15">
       <c r="A54" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="B54" t="s">
+        <v>232</v>
       </c>
       <c r="C54" s="2">
         <v>138</v>
@@ -4538,10 +5064,25 @@
         <f t="shared" si="0"/>
         <v>5.5546163692129352E-4</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E54" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F54" t="s">
+        <v>215</v>
+      </c>
+      <c r="I54" t="s">
+        <v>213</v>
+      </c>
+      <c r="K54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="15">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>89</v>
+      </c>
+      <c r="B55" t="s">
+        <v>248</v>
       </c>
       <c r="C55" s="2">
         <v>127</v>
@@ -4550,10 +5091,25 @@
         <f t="shared" si="0"/>
         <v>5.1118570934061071E-4</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E55" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F55" t="s">
+        <v>245</v>
+      </c>
+      <c r="I55" t="s">
+        <v>213</v>
+      </c>
+      <c r="K55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>96</v>
+      </c>
+      <c r="B56" t="s">
+        <v>253</v>
       </c>
       <c r="C56" s="2">
         <v>116</v>
@@ -4562,10 +5118,22 @@
         <f t="shared" si="0"/>
         <v>4.669097817599279E-4</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="E56" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F56" t="s">
+        <v>215</v>
+      </c>
+      <c r="I56" t="s">
+        <v>213</v>
+      </c>
+      <c r="K56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C57" s="2">
         <v>85</v>
@@ -4575,9 +5143,9 @@
         <v>3.4213216766891265E-4</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C58" s="2">
         <v>70</v>
@@ -4587,9 +5155,9 @@
         <v>2.8175590278616339E-4</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C59" s="2">
         <v>67</v>
@@ -4599,9 +5167,9 @@
         <v>2.6968064980961351E-4</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C60" s="2">
         <v>58</v>
@@ -4611,9 +5179,9 @@
         <v>2.3345489087996395E-4</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C61" s="2">
         <v>37</v>
@@ -4623,9 +5191,9 @@
         <v>1.4892812004411492E-4</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C62" s="2">
         <v>34</v>
@@ -4635,9 +5203,9 @@
         <v>1.3685286706756507E-4</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:11">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="C63" s="2">
         <v>32</v>
@@ -4647,9 +5215,9 @@
         <v>1.2880269841653182E-4</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="C64" s="2">
         <v>31</v>
@@ -4659,9 +5227,9 @@
         <v>1.247776140910152E-4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C65" s="2">
         <v>27</v>
@@ -4671,9 +5239,9 @@
         <v>1.0867727678894872E-4</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C66" s="2">
         <v>27</v>
@@ -4683,9 +5251,9 @@
         <v>1.0867727678894872E-4</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C67" s="2">
         <v>22</v>
@@ -4695,9 +5263,9 @@
         <v>8.855185516136563E-5</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="C68" s="2">
         <v>13</v>
@@ -4707,9 +5275,9 @@
         <v>5.2326096231716057E-5</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C69" s="2">
         <v>8</v>
@@ -4719,9 +5287,9 @@
         <v>3.2200674604132955E-5</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C70" s="2">
         <v>5</v>
@@ -4731,9 +5299,9 @@
         <v>2.0125421627583099E-5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C71" s="2">
         <v>4</v>
@@ -4743,9 +5311,12 @@
         <v>1.6100337302066478E-5</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>123</v>
+        <v>125</v>
+      </c>
+      <c r="B72" t="s">
+        <v>248</v>
       </c>
       <c r="C72" s="2">
         <v>4</v>
@@ -4755,9 +5326,9 @@
         <v>1.6100337302066478E-5</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C73" s="2">
         <v>2</v>
@@ -4767,9 +5338,12 @@
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>91</v>
+      </c>
+      <c r="B74" t="s">
+        <v>248</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
@@ -4779,7 +5353,7 @@
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -4791,9 +5365,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>124</v>
+        <v>127</v>
+      </c>
+      <c r="B76" t="s">
+        <v>253</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -4803,9 +5380,9 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -4815,9 +5392,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>101</v>
+        <v>103</v>
+      </c>
+      <c r="B78" t="s">
+        <v>248</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -4827,9 +5407,9 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -4839,9 +5419,9 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -4851,9 +5431,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>112</v>
+        <v>115</v>
+      </c>
+      <c r="B81" t="s">
+        <v>248</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -4863,9 +5446,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>109</v>
+        <v>112</v>
+      </c>
+      <c r="B82" t="s">
+        <v>248</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -4875,9 +5461,9 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99C9471B-EF4E-4FDE-9648-2B2FF6D3D5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{538C4851-CE75-4D27-B7D4-E7EA3B18DE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="274">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -760,52 +760,112 @@
     <t>Housing menu</t>
   </si>
   <si>
+    <t>Voicemail Transfer</t>
+  </si>
+  <si>
+    <t>Family menu</t>
+  </si>
+  <si>
+    <t>Legal menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queues </t>
+  </si>
+  <si>
+    <t>Pre-legal seniors menu</t>
+  </si>
+  <si>
+    <t>HIV Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Menu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive (tenative) </t>
+  </si>
+  <si>
+    <t>Caller listens to message; no option given to return to previous menus</t>
+  </si>
+  <si>
+    <t>Issue not handled by LAC</t>
+  </si>
+  <si>
+    <t>No input</t>
+  </si>
+  <si>
+    <t>Immigration menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abandoned </t>
+  </si>
+  <si>
+    <t>Family Menu</t>
+  </si>
+  <si>
+    <t>Benefits Menu</t>
+  </si>
+  <si>
+    <t>Negative (tenative)</t>
+  </si>
+  <si>
+    <t>Need to call to verify verbiage does not suggest that some caller should abandon at this point</t>
+  </si>
+  <si>
+    <t>Caller is non-Cook County Senior and did not make a selection after message</t>
+  </si>
+  <si>
+    <t>Queues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral </t>
+  </si>
+  <si>
+    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
+  </si>
+  <si>
+    <t>Employment menu</t>
+  </si>
+  <si>
+    <t>No activity</t>
+  </si>
+  <si>
+    <t>Caller selected Other Legal option (8) in Suburban Seniors Menu</t>
+  </si>
+  <si>
+    <t>Immigration Menu</t>
+  </si>
+  <si>
     <t>Voice Mail Transfer</t>
   </si>
   <si>
-    <t>Family menu</t>
-  </si>
-  <si>
-    <t>Legal menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queues </t>
-  </si>
-  <si>
-    <t>Pre-legal seniors menu</t>
-  </si>
-  <si>
-    <t>HIV Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Menu </t>
-  </si>
-  <si>
-    <t>Issue not handled by LAC</t>
-  </si>
-  <si>
-    <t>No input</t>
-  </si>
-  <si>
-    <t>Immigration menu</t>
-  </si>
-  <si>
-    <t>Pre-Legal Seniors Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abandoned </t>
-  </si>
-  <si>
-    <t>Benefits Menu</t>
-  </si>
-  <si>
-    <t>Employment menu</t>
-  </si>
-  <si>
-    <t>No activity</t>
-  </si>
-  <si>
-    <t>Immigration Menu</t>
+    <t>Holiday &amp; Closed Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed </t>
+  </si>
+  <si>
+    <t>Unsuccessful Courtesy Callback</t>
+  </si>
+  <si>
+    <t>No Agent Name for attempted courtesy callback</t>
+  </si>
+  <si>
+    <t>Farmworker Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assuming this corresponds to Farm Worker Voicemail transfer on flow charts </t>
+  </si>
+  <si>
+    <t>Verbiage tells callers that they can leave comments online</t>
+  </si>
+  <si>
+    <t>Outbound call failed to connect; system error</t>
+  </si>
+  <si>
+    <t>Employment Menu</t>
   </si>
 </sst>
 </file>
@@ -840,12 +900,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -877,7 +943,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -890,6 +956,12 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3806,7 +3878,7 @@
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="41.28515625" customWidth="1"/>
   </cols>
@@ -4509,7 +4581,7 @@
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F27" t="s">
         <v>238</v>
@@ -4576,18 +4648,26 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="15">
-      <c r="A30" t="s">
+      <c r="A30" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="C30" s="2">
+      <c r="B30" s="8"/>
+      <c r="C30" s="9">
         <v>694</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="10">
         <f t="shared" si="0"/>
         <v>2.793408521908534E-3</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" ht="15">
+      <c r="E30" s="11"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+    </row>
+    <row r="31" spans="1:11" ht="29.25">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -4600,6 +4680,18 @@
       <c r="D31" s="6">
         <f t="shared" si="0"/>
         <v>2.7048566667471682E-3</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="I31" t="s">
+        <v>213</v>
+      </c>
+      <c r="K31">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="15">
@@ -4620,7 +4712,7 @@
         <v>230</v>
       </c>
       <c r="F32" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" t="s">
@@ -4678,7 +4770,7 @@
         <v>228</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I34" t="s">
         <v>213</v>
@@ -4716,7 +4808,7 @@
         <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2">
         <v>527</v>
@@ -4743,7 +4835,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C37" s="2">
         <v>502</v>
@@ -4783,7 +4875,7 @@
         <v>230</v>
       </c>
       <c r="F38" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I38" t="s">
         <v>213</v>
@@ -4810,7 +4902,7 @@
         <v>230</v>
       </c>
       <c r="F39" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I39" t="s">
         <v>213</v>
@@ -4837,7 +4929,7 @@
         <v>207</v>
       </c>
       <c r="F40" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I40" t="s">
         <v>213</v>
@@ -4864,7 +4956,7 @@
         <v>207</v>
       </c>
       <c r="F41" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="I41" t="s">
         <v>213</v>
@@ -4874,23 +4966,33 @@
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" t="s">
+      <c r="A42" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="C42" s="2">
+      <c r="B42" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" s="9">
         <v>412</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="10">
         <f t="shared" si="0"/>
         <v>1.6583347421128473E-3</v>
       </c>
-    </row>
-    <row r="43" spans="1:11">
+      <c r="E42" s="11"/>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+      <c r="H42" s="8"/>
+      <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+    </row>
+    <row r="43" spans="1:11" ht="15">
       <c r="A43" t="s">
         <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="C43" s="2">
         <v>353</v>
@@ -4899,13 +5001,25 @@
         <f t="shared" si="0"/>
         <v>1.4208547669073666E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="E43" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F43" t="s">
+        <v>247</v>
+      </c>
+      <c r="I43" t="s">
+        <v>213</v>
+      </c>
+      <c r="K43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15">
       <c r="A44" t="s">
         <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C44" s="2">
         <v>298</v>
@@ -4914,13 +5028,25 @@
         <f t="shared" si="0"/>
         <v>1.1994751290039527E-3</v>
       </c>
-    </row>
-    <row r="45" spans="1:11">
+      <c r="E44" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F44" t="s">
+        <v>215</v>
+      </c>
+      <c r="I44" t="s">
+        <v>213</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="29.25">
       <c r="A45" t="s">
         <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C45" s="2">
         <v>278</v>
@@ -4929,11 +5055,29 @@
         <f t="shared" si="0"/>
         <v>1.1189734424936202E-3</v>
       </c>
-    </row>
-    <row r="46" spans="1:11">
+      <c r="E45" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" t="s">
+        <v>251</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="I45" t="s">
+        <v>213</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="29.25">
       <c r="A46" t="s">
         <v>105</v>
       </c>
+      <c r="B46" t="s">
+        <v>250</v>
+      </c>
       <c r="C46" s="2">
         <v>228</v>
       </c>
@@ -4941,11 +5085,29 @@
         <f t="shared" si="0"/>
         <v>9.1771922621778929E-4</v>
       </c>
-    </row>
-    <row r="47" spans="1:11">
+      <c r="E46" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F46" t="s">
+        <v>247</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="I46" t="s">
+        <v>213</v>
+      </c>
+      <c r="K46">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="43.5">
       <c r="A47" t="s">
         <v>67</v>
       </c>
+      <c r="B47" t="s">
+        <v>257</v>
+      </c>
       <c r="C47" s="2">
         <v>219</v>
       </c>
@@ -4953,13 +5115,28 @@
         <f t="shared" si="0"/>
         <v>8.8149346728813973E-4</v>
       </c>
-    </row>
-    <row r="48" spans="1:11">
+      <c r="E47" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F47" t="s">
+        <v>247</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="I47" t="s">
+        <v>213</v>
+      </c>
+      <c r="K47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="15">
       <c r="A48" t="s">
         <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C48" s="2">
         <v>212</v>
@@ -4968,13 +5145,25 @@
         <f t="shared" si="0"/>
         <v>8.533178770095233E-4</v>
       </c>
-    </row>
-    <row r="49" spans="1:11">
+      <c r="E48" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F48" t="s">
+        <v>215</v>
+      </c>
+      <c r="I48" t="s">
+        <v>213</v>
+      </c>
+      <c r="K48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="15">
       <c r="A49" t="s">
         <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C49" s="2">
         <v>185</v>
@@ -4983,13 +5172,25 @@
         <f t="shared" si="0"/>
         <v>7.446406002205746E-4</v>
       </c>
-    </row>
-    <row r="50" spans="1:11">
+      <c r="E49" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F49" t="s">
+        <v>238</v>
+      </c>
+      <c r="I49" t="s">
+        <v>213</v>
+      </c>
+      <c r="K49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="15">
       <c r="A50" t="s">
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C50" s="2">
         <v>183</v>
@@ -4998,29 +5199,67 @@
         <f t="shared" si="0"/>
         <v>7.3659043156954135E-4</v>
       </c>
+      <c r="E50" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F50" t="s">
+        <v>251</v>
+      </c>
+      <c r="I50" t="s">
+        <v>213</v>
+      </c>
+      <c r="K50">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" t="s">
-        <v>252</v>
-      </c>
-      <c r="C51" s="2">
+      <c r="A51" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B51" s="8"/>
+      <c r="C51" s="9">
         <v>177</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="10">
         <f t="shared" si="0"/>
         <v>7.1243992561644172E-4</v>
       </c>
-    </row>
-    <row r="52" spans="1:11">
+      <c r="E51" s="11"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+    </row>
+    <row r="52" spans="1:11" ht="29.25">
       <c r="A52" t="s">
         <v>128</v>
       </c>
+      <c r="B52" t="s">
+        <v>250</v>
+      </c>
       <c r="C52" s="2">
         <v>158</v>
       </c>
       <c r="D52" s="6">
         <f t="shared" si="0"/>
         <v>6.3596332343162591E-4</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F52" t="s">
+        <v>247</v>
+      </c>
+      <c r="H52" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="I52" t="s">
+        <v>213</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="15">
@@ -5028,7 +5267,7 @@
         <v>132</v>
       </c>
       <c r="B53" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C53" s="2">
         <v>139</v>
@@ -5038,10 +5277,10 @@
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F53" t="s">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="I53" t="s">
         <v>213</v>
@@ -5082,7 +5321,7 @@
         <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C55" s="2">
         <v>127</v>
@@ -5095,7 +5334,7 @@
         <v>230</v>
       </c>
       <c r="F55" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I55" t="s">
         <v>213</v>
@@ -5109,7 +5348,7 @@
         <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C56" s="2">
         <v>116</v>
@@ -5131,10 +5370,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" ht="15">
       <c r="A57" t="s">
         <v>78</v>
       </c>
+      <c r="B57" t="s">
+        <v>265</v>
+      </c>
       <c r="C57" s="2">
         <v>85</v>
       </c>
@@ -5142,8 +5384,20 @@
         <f t="shared" si="0"/>
         <v>3.4213216766891265E-4</v>
       </c>
-    </row>
-    <row r="58" spans="1:11">
+      <c r="E57" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F57" t="s">
+        <v>266</v>
+      </c>
+      <c r="I57" t="s">
+        <v>213</v>
+      </c>
+      <c r="K57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="29.25">
       <c r="A58" t="s">
         <v>142</v>
       </c>
@@ -5154,11 +5408,29 @@
         <f t="shared" si="0"/>
         <v>2.8175590278616339E-4</v>
       </c>
-    </row>
-    <row r="59" spans="1:11">
+      <c r="E58" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F58" t="s">
+        <v>267</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="I58" t="s">
+        <v>213</v>
+      </c>
+      <c r="K58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="29.25">
       <c r="A59" t="s">
         <v>144</v>
       </c>
+      <c r="B59" t="s">
+        <v>269</v>
+      </c>
       <c r="C59" s="2">
         <v>67</v>
       </c>
@@ -5166,11 +5438,29 @@
         <f t="shared" si="0"/>
         <v>2.6968064980961351E-4</v>
       </c>
-    </row>
-    <row r="60" spans="1:11">
+      <c r="E59" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="F59" t="s">
+        <v>238</v>
+      </c>
+      <c r="H59" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="I59" t="s">
+        <v>213</v>
+      </c>
+      <c r="K59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="29.25">
       <c r="A60" t="s">
         <v>92</v>
       </c>
+      <c r="B60" t="s">
+        <v>244</v>
+      </c>
       <c r="C60" s="2">
         <v>58</v>
       </c>
@@ -5178,11 +5468,26 @@
         <f t="shared" si="0"/>
         <v>2.3345489087996395E-4</v>
       </c>
-    </row>
-    <row r="61" spans="1:11">
+      <c r="E60" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="H60" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="I60" t="s">
+        <v>213</v>
+      </c>
+      <c r="K60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="15">
       <c r="A61" t="s">
         <v>52</v>
       </c>
+      <c r="B61" t="s">
+        <v>257</v>
+      </c>
       <c r="C61" s="2">
         <v>37</v>
       </c>
@@ -5190,11 +5495,26 @@
         <f t="shared" si="0"/>
         <v>1.4892812004411492E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:11">
+      <c r="E61" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F61" t="s">
+        <v>251</v>
+      </c>
+      <c r="I61" t="s">
+        <v>213</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="15">
       <c r="A62" t="s">
         <v>51</v>
       </c>
+      <c r="B62" t="s">
+        <v>244</v>
+      </c>
       <c r="C62" s="2">
         <v>34</v>
       </c>
@@ -5202,8 +5522,20 @@
         <f t="shared" si="0"/>
         <v>1.3685286706756507E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:11">
+      <c r="E62" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F62" t="s">
+        <v>251</v>
+      </c>
+      <c r="I62" t="s">
+        <v>213</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15">
       <c r="A63" t="s">
         <v>57</v>
       </c>
@@ -5214,11 +5546,26 @@
         <f t="shared" si="0"/>
         <v>1.2880269841653182E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:11">
+      <c r="E63" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H63" t="s">
+        <v>272</v>
+      </c>
+      <c r="I63" t="s">
+        <v>213</v>
+      </c>
+      <c r="K63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="15">
       <c r="A64" t="s">
         <v>126</v>
       </c>
+      <c r="B64" t="s">
+        <v>273</v>
+      </c>
       <c r="C64" s="2">
         <v>31</v>
       </c>
@@ -5226,10 +5573,25 @@
         <f t="shared" si="0"/>
         <v>1.247776140910152E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:4">
+      <c r="E64" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="F64" t="s">
+        <v>247</v>
+      </c>
+      <c r="I64" t="s">
+        <v>213</v>
+      </c>
+      <c r="K64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15">
       <c r="A65" t="s">
         <v>98</v>
+      </c>
+      <c r="B65" t="s">
+        <v>257</v>
       </c>
       <c r="C65" s="2">
         <v>27</v>
@@ -5316,7 +5678,7 @@
         <v>125</v>
       </c>
       <c r="B72" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C72" s="2">
         <v>4</v>
@@ -5343,7 +5705,7 @@
         <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
@@ -5370,7 +5732,7 @@
         <v>127</v>
       </c>
       <c r="B76" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -5397,7 +5759,7 @@
         <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5436,7 +5798,7 @@
         <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5451,7 +5813,7 @@
         <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{538C4851-CE75-4D27-B7D4-E7EA3B18DE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BEEFB17-85C4-490F-8A3C-2E64DFEB2BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="278">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -705,6 +705,9 @@
     <t>Main Menu</t>
   </si>
   <si>
+    <t>Courtesy Callback</t>
+  </si>
+  <si>
     <t>Neutral / Negative</t>
   </si>
   <si>
@@ -724,7 +727,7 @@
     <t xml:space="preserve">Positive / Neutral </t>
   </si>
   <si>
-    <t xml:space="preserve">If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect </t>
+    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect - tenative</t>
   </si>
   <si>
     <t>Positive</t>
@@ -736,6 +739,9 @@
     <t>No input for language selection;</t>
   </si>
   <si>
+    <t>Holiday &amp; Closed Menu</t>
+  </si>
+  <si>
     <t>Neutral</t>
   </si>
   <si>
@@ -766,12 +772,12 @@
     <t>Family menu</t>
   </si>
   <si>
-    <t>Legal menu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Queues </t>
   </si>
   <si>
+    <t xml:space="preserve">Legal Menu </t>
+  </si>
+  <si>
     <t>Pre-legal seniors menu</t>
   </si>
   <si>
@@ -808,12 +814,6 @@
     <t>Benefits Menu</t>
   </si>
   <si>
-    <t>Negative (tenative)</t>
-  </si>
-  <si>
-    <t>Need to call to verify verbiage does not suggest that some caller should abandon at this point</t>
-  </si>
-  <si>
     <t>Caller is non-Cook County Senior and did not make a selection after message</t>
   </si>
   <si>
@@ -841,9 +841,6 @@
     <t>Voice Mail Transfer</t>
   </si>
   <si>
-    <t>Holiday &amp; Closed Menu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Closed </t>
   </si>
   <si>
@@ -866,6 +863,21 @@
   </si>
   <si>
     <t>Employment Menu</t>
+  </si>
+  <si>
+    <t>Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
+  </si>
+  <si>
+    <t>System failure in courtesy callback attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caller hangs up before being connected with an agent, system tries to progress but gives error since there's no caller </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative </t>
+  </si>
+  <si>
+    <t>Caller did not finish confirming callback</t>
   </si>
 </sst>
 </file>
@@ -3873,7 +3885,7 @@
   <dimension ref="A1:K83"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
     <col min="2" max="2" width="22.28515625" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
@@ -4063,6 +4075,9 @@
       <c r="A7" t="s">
         <v>44</v>
       </c>
+      <c r="B7" t="s">
+        <v>220</v>
+      </c>
       <c r="C7" s="2">
         <v>12010</v>
       </c>
@@ -4071,10 +4086,10 @@
         <v>4.8341262749454599E-2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="I7" t="s">
         <v>209</v>
@@ -4088,7 +4103,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C8" s="2">
         <v>11987</v>
@@ -4111,45 +4126,60 @@
       </c>
     </row>
     <row r="9" spans="1:11" ht="28.9">
-      <c r="A9" t="s">
+      <c r="A9" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="2">
+      <c r="B9" s="8"/>
+      <c r="C9" s="9">
         <v>9640</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="10">
         <f t="shared" si="0"/>
         <v>3.8801812897980216E-2</v>
       </c>
-      <c r="G9" t="s">
+      <c r="E9" s="11"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="H9" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="I9" s="8" t="s">
         <v>209</v>
       </c>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" t="s">
+      <c r="A10" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="2">
+      <c r="B10" s="8"/>
+      <c r="C10" s="9">
         <v>9358</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="10">
         <f t="shared" si="0"/>
         <v>3.7666739118184529E-2</v>
       </c>
-      <c r="H10" t="s">
-        <v>224</v>
-      </c>
+      <c r="E10" s="11"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="43.5">
       <c r="A11" t="s">
         <v>56</v>
       </c>
+      <c r="B11" t="s">
+        <v>220</v>
+      </c>
       <c r="C11" s="2">
         <v>8939</v>
       </c>
@@ -4158,10 +4188,10 @@
         <v>3.5980228785793066E-2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I11" t="s">
         <v>213</v>
@@ -4185,13 +4215,13 @@
         <v>3.1757915328326128E-2</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I12" t="s">
         <v>213</v>
@@ -4204,6 +4234,9 @@
       <c r="A13" t="s">
         <v>43</v>
       </c>
+      <c r="B13" t="s">
+        <v>231</v>
+      </c>
       <c r="C13" s="2">
         <v>7765</v>
       </c>
@@ -4212,10 +4245,13 @@
         <v>3.125477978763655E-2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F13" t="s">
-        <v>231</v>
+        <v>233</v>
+      </c>
+      <c r="I13" t="s">
+        <v>213</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -4226,7 +4262,7 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C14" s="2">
         <v>6895</v>
@@ -4236,13 +4272,13 @@
         <v>2.7752956424437092E-2</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I14" t="s">
         <v>213</v>
@@ -4256,7 +4292,7 @@
         <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C15" s="2">
         <v>6863</v>
@@ -4295,6 +4331,9 @@
       <c r="E16" s="5" t="s">
         <v>211</v>
       </c>
+      <c r="I16" t="s">
+        <v>213</v>
+      </c>
       <c r="K16">
         <v>2</v>
       </c>
@@ -4304,7 +4343,7 @@
         <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C17" s="2">
         <v>2545</v>
@@ -4314,13 +4353,13 @@
         <v>1.0243839608439796E-2</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F17" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="I17" t="s">
         <v>213</v>
@@ -4334,7 +4373,7 @@
         <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C18" s="2">
         <v>2394</v>
@@ -4361,7 +4400,7 @@
         <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2">
         <v>2267</v>
@@ -4371,10 +4410,10 @@
         <v>9.1248661659461758E-3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F19" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I19" t="s">
         <v>213</v>
@@ -4388,7 +4427,7 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C20" s="2">
         <v>2136</v>
@@ -4415,7 +4454,7 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C21" s="2">
         <v>1462</v>
@@ -4442,7 +4481,7 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C22" s="2">
         <v>1287</v>
@@ -4469,7 +4508,7 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2">
         <v>1267</v>
@@ -4496,7 +4535,7 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2">
         <v>1209</v>
@@ -4523,7 +4562,7 @@
         <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2">
         <v>870</v>
@@ -4533,7 +4572,10 @@
         <v>3.5018233631994591E-3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
+      </c>
+      <c r="I25" t="s">
+        <v>213</v>
       </c>
       <c r="K25">
         <v>2</v>
@@ -4544,7 +4586,7 @@
         <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C26" s="2">
         <v>837</v>
@@ -4571,7 +4613,7 @@
         <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C27" s="2">
         <v>836</v>
@@ -4581,10 +4623,10 @@
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F27" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I27" t="s">
         <v>213</v>
@@ -4598,7 +4640,7 @@
         <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2">
         <v>785</v>
@@ -4625,7 +4667,7 @@
         <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C29" s="2">
         <v>771</v>
@@ -4672,7 +4714,7 @@
         <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C31" s="2">
         <v>672</v>
@@ -4682,10 +4724,10 @@
         <v>2.7048566667471682E-3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I31" t="s">
         <v>213</v>
@@ -4699,7 +4741,7 @@
         <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C32" s="2">
         <v>604</v>
@@ -4709,10 +4751,10 @@
         <v>2.4311509326120384E-3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F32" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" t="s">
@@ -4727,7 +4769,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C33" s="2">
         <v>543</v>
@@ -4764,13 +4806,13 @@
         <v>2.1775706201044914E-3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="I34" t="s">
         <v>213</v>
@@ -4784,7 +4826,7 @@
         <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C35" s="2">
         <v>540</v>
@@ -4794,7 +4836,7 @@
         <v>2.1735455357789744E-3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I35" t="s">
         <v>213</v>
@@ -4808,7 +4850,7 @@
         <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C36" s="2">
         <v>527</v>
@@ -4835,7 +4877,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C37" s="2">
         <v>502</v>
@@ -4862,7 +4904,7 @@
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C38" s="2">
         <v>479</v>
@@ -4872,10 +4914,10 @@
         <v>1.9280153919224608E-3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F38" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I38" t="s">
         <v>213</v>
@@ -4889,7 +4931,7 @@
         <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C39" s="2">
         <v>454</v>
@@ -4899,10 +4941,10 @@
         <v>1.8273882837845452E-3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F39" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I39" t="s">
         <v>213</v>
@@ -4916,7 +4958,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C40" s="2">
         <v>444</v>
@@ -4929,7 +4971,7 @@
         <v>207</v>
       </c>
       <c r="F40" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I40" t="s">
         <v>213</v>
@@ -4943,7 +4985,7 @@
         <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C41" s="2">
         <v>442</v>
@@ -4956,7 +4998,7 @@
         <v>207</v>
       </c>
       <c r="F41" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I41" t="s">
         <v>213</v>
@@ -4970,7 +5012,7 @@
         <v>116</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C42" s="9">
         <v>412</v>
@@ -4992,7 +5034,7 @@
         <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C43" s="2">
         <v>353</v>
@@ -5002,10 +5044,10 @@
         <v>1.4208547669073666E-3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F43" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I43" t="s">
         <v>213</v>
@@ -5019,7 +5061,7 @@
         <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C44" s="2">
         <v>298</v>
@@ -5041,33 +5083,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="29.25">
-      <c r="A45" t="s">
+    <row r="45" spans="1:11" ht="15">
+      <c r="A45" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B45" t="s">
-        <v>250</v>
-      </c>
-      <c r="C45" s="2">
+      <c r="B45" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C45" s="9">
         <v>278</v>
       </c>
-      <c r="D45" s="6">
+      <c r="D45" s="10">
         <f t="shared" si="0"/>
         <v>1.1189734424936202E-3</v>
       </c>
-      <c r="E45" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="F45" t="s">
-        <v>251</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="I45" t="s">
-        <v>213</v>
-      </c>
-      <c r="K45">
+      <c r="E45" s="11"/>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="8"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8">
         <v>1</v>
       </c>
     </row>
@@ -5076,7 +5112,7 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C46" s="2">
         <v>228</v>
@@ -5086,10 +5122,10 @@
         <v>9.1771922621778929E-4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F46" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>256</v>
@@ -5119,7 +5155,7 @@
         <v>258</v>
       </c>
       <c r="F47" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H47" s="5" t="s">
         <v>259</v>
@@ -5136,7 +5172,7 @@
         <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C48" s="2">
         <v>212</v>
@@ -5163,7 +5199,7 @@
         <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C49" s="2">
         <v>185</v>
@@ -5173,10 +5209,10 @@
         <v>7.446406002205746E-4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F49" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I49" t="s">
         <v>213</v>
@@ -5203,7 +5239,7 @@
         <v>207</v>
       </c>
       <c r="F50" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I50" t="s">
         <v>213</v>
@@ -5237,7 +5273,7 @@
         <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C52" s="2">
         <v>158</v>
@@ -5247,10 +5283,10 @@
         <v>6.3596332343162591E-4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F52" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>262</v>
@@ -5277,7 +5313,7 @@
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F53" t="s">
         <v>264</v>
@@ -5294,7 +5330,7 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C54" s="2">
         <v>138</v>
@@ -5321,7 +5357,7 @@
         <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C55" s="2">
         <v>127</v>
@@ -5331,10 +5367,10 @@
         <v>5.1118570934061071E-4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F55" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I55" t="s">
         <v>213</v>
@@ -5375,7 +5411,7 @@
         <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>265</v>
+        <v>231</v>
       </c>
       <c r="C57" s="2">
         <v>85</v>
@@ -5385,10 +5421,10 @@
         <v>3.4213216766891265E-4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F57" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I57" t="s">
         <v>213</v>
@@ -5401,6 +5437,9 @@
       <c r="A58" t="s">
         <v>142</v>
       </c>
+      <c r="B58" t="s">
+        <v>220</v>
+      </c>
       <c r="C58" s="2">
         <v>70</v>
       </c>
@@ -5412,10 +5451,10 @@
         <v>207</v>
       </c>
       <c r="F58" t="s">
+        <v>266</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="I58" t="s">
         <v>213</v>
@@ -5429,7 +5468,7 @@
         <v>144</v>
       </c>
       <c r="B59" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C59" s="2">
         <v>67</v>
@@ -5439,13 +5478,13 @@
         <v>2.6968064980961351E-4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I59" t="s">
         <v>213</v>
@@ -5459,7 +5498,7 @@
         <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C60" s="2">
         <v>58</v>
@@ -5469,10 +5508,10 @@
         <v>2.3345489087996395E-4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I60" t="s">
         <v>213</v>
@@ -5499,7 +5538,7 @@
         <v>207</v>
       </c>
       <c r="F61" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I61" t="s">
         <v>213</v>
@@ -5513,7 +5552,7 @@
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C62" s="2">
         <v>34</v>
@@ -5526,7 +5565,7 @@
         <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I62" t="s">
         <v>213</v>
@@ -5550,7 +5589,7 @@
         <v>207</v>
       </c>
       <c r="H63" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I63" t="s">
         <v>213</v>
@@ -5564,7 +5603,7 @@
         <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2">
         <v>31</v>
@@ -5574,10 +5613,10 @@
         <v>1.247776140910152E-4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F64" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I64" t="s">
         <v>213</v>
@@ -5586,7 +5625,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="15">
+    <row r="65" spans="1:11" ht="57.75">
       <c r="A65" t="s">
         <v>98</v>
       </c>
@@ -5600,11 +5639,26 @@
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H65" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I65" t="s">
+        <v>213</v>
+      </c>
+      <c r="K65">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="15">
       <c r="A66" t="s">
         <v>59</v>
       </c>
+      <c r="B66" t="s">
+        <v>220</v>
+      </c>
       <c r="C66" s="2">
         <v>27</v>
       </c>
@@ -5612,10 +5666,25 @@
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" t="s">
+        <v>274</v>
+      </c>
+      <c r="I66" t="s">
+        <v>213</v>
+      </c>
+      <c r="K66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" ht="43.5">
       <c r="A67" t="s">
         <v>166</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="C67" s="2">
         <v>22</v>
@@ -5624,10 +5693,28 @@
         <f t="shared" ref="D67:D83" si="1">C67/SUM(($C$2:$C$83))</f>
         <v>8.855185516136563E-5</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="E67" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F67" t="s">
+        <v>253</v>
+      </c>
+      <c r="H67" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="I67" t="s">
+        <v>213</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="15">
       <c r="A68" t="s">
         <v>87</v>
+      </c>
+      <c r="B68" t="s">
+        <v>220</v>
       </c>
       <c r="C68" s="2">
         <v>13</v>
@@ -5636,10 +5723,25 @@
         <f t="shared" si="1"/>
         <v>5.2326096231716057E-5</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="E68" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F68" t="s">
+        <v>266</v>
+      </c>
+      <c r="I68" t="s">
+        <v>213</v>
+      </c>
+      <c r="K68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="57.75">
       <c r="A69" t="s">
         <v>86</v>
+      </c>
+      <c r="B69" t="s">
+        <v>242</v>
       </c>
       <c r="C69" s="2">
         <v>8</v>
@@ -5648,10 +5750,25 @@
         <f t="shared" si="1"/>
         <v>3.2200674604132955E-5</v>
       </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="E69" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="H69" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I69" t="s">
+        <v>213</v>
+      </c>
+      <c r="K69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="15">
       <c r="A70" t="s">
         <v>94</v>
+      </c>
+      <c r="B70" t="s">
+        <v>220</v>
       </c>
       <c r="C70" s="2">
         <v>5</v>
@@ -5660,10 +5777,28 @@
         <f t="shared" si="1"/>
         <v>2.0125421627583099E-5</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F70" t="s">
+        <v>253</v>
+      </c>
+      <c r="H70" t="s">
+        <v>277</v>
+      </c>
+      <c r="I70" t="s">
+        <v>213</v>
+      </c>
+      <c r="K70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="15">
       <c r="A71" t="s">
         <v>95</v>
+      </c>
+      <c r="B71" t="s">
+        <v>220</v>
       </c>
       <c r="C71" s="2">
         <v>4</v>
@@ -5672,25 +5807,50 @@
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
+      <c r="E71" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F71" t="s">
+        <v>253</v>
+      </c>
+      <c r="H71" t="s">
+        <v>277</v>
+      </c>
+      <c r="I71" t="s">
+        <v>213</v>
+      </c>
+      <c r="K71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="15">
+      <c r="A72" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B72" t="s">
-        <v>250</v>
-      </c>
-      <c r="C72" s="2">
+      <c r="B72" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C72" s="9">
         <v>4</v>
       </c>
-      <c r="D72" s="6">
+      <c r="D72" s="10">
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="E72" s="11"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="8"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+    </row>
+    <row r="73" spans="1:11" ht="57.75">
       <c r="A73" t="s">
         <v>129</v>
+      </c>
+      <c r="B73" t="s">
+        <v>242</v>
       </c>
       <c r="C73" s="2">
         <v>2</v>
@@ -5699,13 +5859,25 @@
         <f t="shared" si="1"/>
         <v>8.0501686510332388E-6</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="E73" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H73" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="I73" t="s">
+        <v>213</v>
+      </c>
+      <c r="K73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
         <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
@@ -5715,9 +5887,12 @@
         <v>8.0501686510332388E-6</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
         <v>85</v>
+      </c>
+      <c r="B75" t="s">
+        <v>243</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -5727,7 +5902,7 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
         <v>127</v>
       </c>
@@ -5742,9 +5917,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:11">
       <c r="A77" t="s">
         <v>148</v>
+      </c>
+      <c r="B77" t="s">
+        <v>242</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -5754,12 +5932,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:11">
       <c r="A78" t="s">
         <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -5769,9 +5947,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
         <v>176</v>
+      </c>
+      <c r="B79" t="s">
+        <v>242</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -5781,9 +5962,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
         <v>61</v>
+      </c>
+      <c r="B80" t="s">
+        <v>242</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -5798,7 +5982,7 @@
         <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -5813,7 +5997,7 @@
         <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -5826,6 +6010,9 @@
     <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>153</v>
+      </c>
+      <c r="B83" t="s">
+        <v>242</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BEEFB17-85C4-490F-8A3C-2E64DFEB2BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE32BE3A-24C5-D443-8BFC-E9463969DA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="16640" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -34,7 +34,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="281">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -878,6 +877,15 @@
   </si>
   <si>
     <t>Caller did not finish confirming callback</t>
+  </si>
+  <si>
+    <t>Sabrina</t>
+  </si>
+  <si>
+    <t>Should check if agents are logged into queue, if last activity then caller never entered the queue (never heard pre-queue message1), customer may have ended call after waiting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Should check if agent are logged into quque, if last activity then the call never entered queue (did not hear pre-queue message1), </t>
   </si>
 </sst>
 </file>
@@ -888,7 +896,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1313,13 +1321,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1327,7 +1335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1335,7 +1343,7 @@
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1343,7 +1351,7 @@
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1351,7 +1359,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1359,7 +1367,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1367,7 +1375,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1375,7 +1383,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1383,7 +1391,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1391,7 +1399,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1399,7 +1407,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1407,7 +1415,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1415,7 +1423,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1423,7 +1431,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1431,7 +1439,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1439,7 +1447,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1447,7 +1455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1455,7 +1463,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1463,7 +1471,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1471,7 +1479,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1479,7 +1487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1487,7 +1495,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1495,7 +1503,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1503,7 +1511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1511,7 +1519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1519,7 +1527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1527,7 +1535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1543,17 +1551,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="28.9">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1567,7 +1575,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1581,7 +1589,7 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1595,7 +1603,7 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1609,7 +1617,7 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1623,7 +1631,7 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1637,7 +1645,7 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1651,7 +1659,7 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1665,7 +1673,7 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1679,7 +1687,7 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1693,7 +1701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1707,7 +1715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1721,7 +1729,7 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1735,7 +1743,7 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1749,7 +1757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1763,7 +1771,7 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1777,7 +1785,7 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1791,7 +1799,7 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1805,7 +1813,7 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1819,7 +1827,7 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1833,7 +1841,7 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1847,7 +1855,7 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1861,7 +1869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1875,7 +1883,7 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1889,7 +1897,7 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1903,7 +1911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1917,7 +1925,7 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1931,7 +1939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -1945,7 +1953,7 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1959,7 +1967,7 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -1973,7 +1981,7 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -1987,7 +1995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -2001,7 +2009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -2015,7 +2023,7 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -2029,7 +2037,7 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2043,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2057,7 +2065,7 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -2071,7 +2079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -2085,7 +2093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -2099,7 +2107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2113,7 +2121,7 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2127,7 +2135,7 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -2141,7 +2149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2155,7 +2163,7 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2169,7 +2177,7 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2183,7 +2191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -2197,7 +2205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2211,7 +2219,7 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2225,7 +2233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -2239,7 +2247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -2253,7 +2261,7 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -2267,7 +2275,7 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -2281,7 +2289,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2295,7 +2303,7 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -2309,7 +2317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2323,7 +2331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -2337,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -2351,7 +2359,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2365,7 +2373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -2379,7 +2387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2393,7 +2401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2407,7 +2415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -2421,7 +2429,7 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -2435,7 +2443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -2449,7 +2457,7 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -2463,7 +2471,7 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -2477,7 +2485,7 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2491,7 +2499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -2505,7 +2513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>99</v>
       </c>
@@ -2519,7 +2527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -2533,7 +2541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -2547,7 +2555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -2561,7 +2569,7 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -2575,7 +2583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -2589,7 +2597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -2603,7 +2611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -2617,7 +2625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -2631,7 +2639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -2645,7 +2653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -2659,7 +2667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -2673,7 +2681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>111</v>
       </c>
@@ -2687,7 +2695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -2701,7 +2709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -2715,7 +2723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>114</v>
       </c>
@@ -2729,7 +2737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -2743,7 +2751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -2757,7 +2765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -2771,7 +2779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -2785,7 +2793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>119</v>
       </c>
@@ -2799,7 +2807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -2813,7 +2821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -2827,7 +2835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -2841,7 +2849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -2855,7 +2863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -2869,7 +2877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -2883,7 +2891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -2897,7 +2905,7 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -2911,7 +2919,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -2925,7 +2933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -2939,7 +2947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -2953,7 +2961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -2967,7 +2975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -2981,7 +2989,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -2995,7 +3003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -3009,7 +3017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -3023,7 +3031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -3037,7 +3045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -3051,7 +3059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -3065,7 +3073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3079,7 +3087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -3093,7 +3101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>141</v>
       </c>
@@ -3107,7 +3115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>142</v>
       </c>
@@ -3121,7 +3129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>143</v>
       </c>
@@ -3135,7 +3143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>144</v>
       </c>
@@ -3149,7 +3157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>145</v>
       </c>
@@ -3163,7 +3171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3177,7 +3185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>147</v>
       </c>
@@ -3191,7 +3199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -3205,7 +3213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>149</v>
       </c>
@@ -3219,7 +3227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>150</v>
       </c>
@@ -3233,7 +3241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>151</v>
       </c>
@@ -3247,7 +3255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>152</v>
       </c>
@@ -3261,7 +3269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -3275,7 +3283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -3289,7 +3297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>155</v>
       </c>
@@ -3303,7 +3311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>156</v>
       </c>
@@ -3317,7 +3325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>157</v>
       </c>
@@ -3331,7 +3339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>158</v>
       </c>
@@ -3345,7 +3353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>159</v>
       </c>
@@ -3359,7 +3367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -3373,7 +3381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>161</v>
       </c>
@@ -3387,7 +3395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -3401,7 +3409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -3415,7 +3423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -3429,7 +3437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -3443,7 +3451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -3457,7 +3465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -3471,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -3485,7 +3493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -3499,7 +3507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -3513,7 +3521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -3527,7 +3535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -3541,7 +3549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -3555,7 +3563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -3569,7 +3577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -3583,7 +3591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>176</v>
       </c>
@@ -3597,7 +3605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>177</v>
       </c>
@@ -3611,7 +3619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>178</v>
       </c>
@@ -3625,7 +3633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -3639,7 +3647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>180</v>
       </c>
@@ -3653,7 +3661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>181</v>
       </c>
@@ -3667,7 +3675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -3681,7 +3689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>183</v>
       </c>
@@ -3695,7 +3703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>184</v>
       </c>
@@ -3709,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>185</v>
       </c>
@@ -3723,7 +3731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>186</v>
       </c>
@@ -3737,7 +3745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -3751,7 +3759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -3765,7 +3773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -3779,7 +3787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -3793,7 +3801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -3807,7 +3815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -3821,7 +3829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -3835,7 +3843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>194</v>
       </c>
@@ -3849,7 +3857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>195</v>
       </c>
@@ -3883,19 +3891,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.5" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.15">
+    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>196</v>
       </c>
@@ -3930,7 +3938,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="57.6">
+    <row r="2" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -3960,7 +3968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="43.5">
+    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -3990,7 +3998,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="29.25">
+    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -4017,7 +4025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="72.75">
+    <row r="5" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -4044,7 +4052,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -4071,7 +4079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="72">
+    <row r="7" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -4098,7 +4106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4125,7 +4133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="28.9">
+    <row r="9" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
         <v>55</v>
       </c>
@@ -4151,7 +4159,7 @@
       <c r="J9" s="8"/>
       <c r="K9" s="8"/>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>58</v>
       </c>
@@ -4173,7 +4181,7 @@
       <c r="J10" s="8"/>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" ht="43.5">
+    <row r="11" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>56</v>
       </c>
@@ -4200,7 +4208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="50.25" customHeight="1">
+    <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -4230,7 +4238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -4257,7 +4265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15">
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -4287,7 +4295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15">
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -4314,7 +4322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="29.25">
+    <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -4338,7 +4346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15">
+    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>76</v>
       </c>
@@ -4368,7 +4376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15">
+    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -4395,7 +4403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15">
+    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -4422,7 +4430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15">
+    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -4449,7 +4457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15">
+    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -4476,7 +4484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15">
+    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -4503,7 +4511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15">
+    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -4530,7 +4538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15">
+    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>34</v>
       </c>
@@ -4557,7 +4565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15">
+    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>71</v>
       </c>
@@ -4581,7 +4589,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15">
+    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -4608,7 +4616,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15">
+    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>100</v>
       </c>
@@ -4635,7 +4643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15">
+    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>60</v>
       </c>
@@ -4662,7 +4670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15">
+    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -4689,7 +4697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>102</v>
       </c>
@@ -4709,7 +4717,7 @@
       <c r="J30" s="8"/>
       <c r="K30" s="8"/>
     </row>
-    <row r="31" spans="1:11" ht="29.25">
+    <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -4736,7 +4744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15">
+    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>47</v>
       </c>
@@ -4764,7 +4772,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15">
+    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>42</v>
       </c>
@@ -4791,7 +4799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15">
+    <row r="34" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -4821,7 +4829,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15">
+    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>80</v>
       </c>
@@ -4845,7 +4853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15">
+    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>73</v>
       </c>
@@ -4872,7 +4880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15">
+    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -4899,7 +4907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15">
+    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>83</v>
       </c>
@@ -4926,7 +4934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15">
+    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -4953,7 +4961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15">
+    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -4980,7 +4988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15">
+    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>64</v>
       </c>
@@ -5007,7 +5015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>116</v>
       </c>
@@ -5029,7 +5037,7 @@
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" ht="15">
+    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>77</v>
       </c>
@@ -5056,7 +5064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15">
+    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>66</v>
       </c>
@@ -5083,7 +5091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="15">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>69</v>
       </c>
@@ -5107,7 +5115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="29.25">
+    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>105</v>
       </c>
@@ -5137,7 +5145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="43.5">
+    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>67</v>
       </c>
@@ -5167,7 +5175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15">
+    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>38</v>
       </c>
@@ -5194,7 +5202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15">
+    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>124</v>
       </c>
@@ -5221,7 +5229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15">
+    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>70</v>
       </c>
@@ -5248,7 +5256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>261</v>
       </c>
@@ -5268,7 +5276,7 @@
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="29.25">
+    <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>128</v>
       </c>
@@ -5298,7 +5306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15">
+    <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>132</v>
       </c>
@@ -5325,7 +5333,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15">
+    <row r="54" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -5352,7 +5360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15">
+    <row r="55" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>89</v>
       </c>
@@ -5379,7 +5387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15">
+    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>96</v>
       </c>
@@ -5406,7 +5414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15">
+    <row r="57" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>78</v>
       </c>
@@ -5433,7 +5441,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="29.25">
+    <row r="58" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>142</v>
       </c>
@@ -5463,7 +5471,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="29.25">
+    <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>144</v>
       </c>
@@ -5493,7 +5501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="29.25">
+    <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>92</v>
       </c>
@@ -5520,7 +5528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15">
+    <row r="61" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>52</v>
       </c>
@@ -5547,7 +5555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15">
+    <row r="62" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>51</v>
       </c>
@@ -5574,7 +5582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="15">
+    <row r="63" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>57</v>
       </c>
@@ -5598,7 +5606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15">
+    <row r="64" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>126</v>
       </c>
@@ -5625,7 +5633,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="57.75">
+    <row r="65" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>98</v>
       </c>
@@ -5652,7 +5660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15">
+    <row r="66" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -5679,7 +5687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="43.5">
+    <row r="67" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>166</v>
       </c>
@@ -5709,7 +5717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15">
+    <row r="68" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>87</v>
       </c>
@@ -5736,7 +5744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="57.75">
+    <row r="69" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>86</v>
       </c>
@@ -5763,7 +5771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="15">
+    <row r="70" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>94</v>
       </c>
@@ -5793,7 +5801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15">
+    <row r="71" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>95</v>
       </c>
@@ -5823,7 +5831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="15">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>125</v>
       </c>
@@ -5845,7 +5853,7 @@
       <c r="J72" s="8"/>
       <c r="K72" s="8"/>
     </row>
-    <row r="73" spans="1:11" ht="57.75">
+    <row r="73" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>129</v>
       </c>
@@ -5872,7 +5880,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>91</v>
       </c>
@@ -5886,8 +5894,14 @@
         <f t="shared" si="1"/>
         <v>8.0501686510332388E-6</v>
       </c>
-    </row>
-    <row r="75" spans="1:11">
+      <c r="E74" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="I74" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -5901,8 +5915,14 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
-    </row>
-    <row r="76" spans="1:11">
+      <c r="H75" t="s">
+        <v>279</v>
+      </c>
+      <c r="I75" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>127</v>
       </c>
@@ -5916,8 +5936,17 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
-    </row>
-    <row r="77" spans="1:11">
+      <c r="E76" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H76" t="s">
+        <v>280</v>
+      </c>
+      <c r="I76" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>148</v>
       </c>
@@ -5931,8 +5960,11 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
-    </row>
-    <row r="78" spans="1:11">
+      <c r="I77" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>103</v>
       </c>
@@ -5946,8 +5978,11 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
-    </row>
-    <row r="79" spans="1:11">
+      <c r="I78" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>176</v>
       </c>
@@ -5961,8 +5996,11 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
-    </row>
-    <row r="80" spans="1:11">
+      <c r="I79" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>61</v>
       </c>
@@ -5976,8 +6014,11 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="I80" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -5991,8 +6032,11 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="I81" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -6006,8 +6050,11 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="I82" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>153</v>
       </c>
@@ -6020,6 +6067,9 @@
       <c r="D83" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
+      </c>
+      <c r="I83" t="s">
+        <v>278</v>
       </c>
     </row>
   </sheetData>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE32BE3A-24C5-D443-8BFC-E9463969DA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9663A007-92A2-BA4B-A43D-A286E96EA149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="16640" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="282">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -885,7 +885,10 @@
     <t>Should check if agents are logged into queue, if last activity then caller never entered the queue (never heard pre-queue message1), customer may have ended call after waiting</t>
   </si>
   <si>
-    <t xml:space="preserve">Should check if agent are logged into quque, if last activity then the call never entered queue (did not hear pre-queue message1), </t>
+    <t xml:space="preserve">"Play Courtesy CallBack Confirmation" . This is typically played right before the contact is disconnected from the system. The consumer selected a courtesy callback but hung up before the system could disconnect so this is neutral. </t>
+  </si>
+  <si>
+    <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
   </si>
 </sst>
 </file>
@@ -5897,11 +5900,17 @@
       <c r="E74" s="5" t="s">
         <v>207</v>
       </c>
+      <c r="F74" t="s">
+        <v>215</v>
+      </c>
+      <c r="H74" t="s">
+        <v>281</v>
+      </c>
       <c r="I74" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>85</v>
       </c>
@@ -5915,6 +5924,9 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
+      <c r="E75" s="5" t="s">
+        <v>207</v>
+      </c>
       <c r="H75" t="s">
         <v>279</v>
       </c>
@@ -5939,14 +5951,17 @@
       <c r="E76" s="5" t="s">
         <v>207</v>
       </c>
+      <c r="F76" t="s">
+        <v>215</v>
+      </c>
       <c r="H76" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I76" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>148</v>
       </c>
@@ -5960,11 +5975,17 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
+      <c r="E77" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H77" t="s">
+        <v>279</v>
+      </c>
       <c r="I77" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>103</v>
       </c>
@@ -5978,11 +5999,20 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
+      <c r="E78" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F78" t="s">
+        <v>215</v>
+      </c>
+      <c r="H78" t="s">
+        <v>281</v>
+      </c>
       <c r="I78" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>176</v>
       </c>
@@ -5996,11 +6026,20 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
+      <c r="E79" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="F79" t="s">
+        <v>215</v>
+      </c>
+      <c r="H79" t="s">
+        <v>281</v>
+      </c>
       <c r="I79" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>61</v>
       </c>
@@ -6014,11 +6053,17 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
+      <c r="E80" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="H80" t="s">
+        <v>280</v>
+      </c>
       <c r="I80" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -6032,11 +6077,20 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
+      <c r="E81" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F81" t="s">
+        <v>215</v>
+      </c>
+      <c r="H81" t="s">
+        <v>281</v>
+      </c>
       <c r="I81" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -6050,11 +6104,20 @@
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
+      <c r="E82" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F82" t="s">
+        <v>215</v>
+      </c>
+      <c r="H82" t="s">
+        <v>281</v>
+      </c>
       <c r="I82" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>153</v>
       </c>
@@ -6067,6 +6130,12 @@
       <c r="D83" s="6">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="H83" t="s">
+        <v>279</v>
       </c>
       <c r="I83" t="s">
         <v>278</v>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9663A007-92A2-BA4B-A43D-A286E96EA149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E24930-D70C-8142-B27B-29CD533DABE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="16640" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="282">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -4024,6 +4024,9 @@
       <c r="I4" t="s">
         <v>209</v>
       </c>
+      <c r="J4" t="s">
+        <v>278</v>
+      </c>
       <c r="K4">
         <v>1</v>
       </c>
@@ -4051,6 +4054,9 @@
       <c r="I5" t="s">
         <v>209</v>
       </c>
+      <c r="J5" t="s">
+        <v>278</v>
+      </c>
       <c r="K5">
         <v>2</v>
       </c>
@@ -4078,6 +4084,9 @@
       <c r="I6" t="s">
         <v>209</v>
       </c>
+      <c r="J6" t="s">
+        <v>278</v>
+      </c>
       <c r="K6">
         <v>1</v>
       </c>
@@ -4105,6 +4114,9 @@
       <c r="I7" t="s">
         <v>209</v>
       </c>
+      <c r="J7" t="s">
+        <v>278</v>
+      </c>
       <c r="K7">
         <v>2</v>
       </c>
@@ -4131,6 +4143,9 @@
       </c>
       <c r="I8" t="s">
         <v>209</v>
+      </c>
+      <c r="J8" t="s">
+        <v>278</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -4159,7 +4174,9 @@
       <c r="I9" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="J9" s="8"/>
+      <c r="J9" t="s">
+        <v>278</v>
+      </c>
       <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -4181,7 +4198,9 @@
         <v>225</v>
       </c>
       <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
+      <c r="J10" t="s">
+        <v>278</v>
+      </c>
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4207,6 +4226,9 @@
       <c r="I11" t="s">
         <v>213</v>
       </c>
+      <c r="J11" t="s">
+        <v>278</v>
+      </c>
       <c r="K11">
         <v>2</v>
       </c>
@@ -4237,6 +4259,9 @@
       <c r="I12" t="s">
         <v>213</v>
       </c>
+      <c r="J12" t="s">
+        <v>278</v>
+      </c>
       <c r="K12">
         <v>2</v>
       </c>
@@ -4264,6 +4289,9 @@
       <c r="I13" t="s">
         <v>213</v>
       </c>
+      <c r="J13" t="s">
+        <v>278</v>
+      </c>
       <c r="K13">
         <v>2</v>
       </c>
@@ -4294,6 +4322,9 @@
       <c r="I14" t="s">
         <v>213</v>
       </c>
+      <c r="J14" t="s">
+        <v>278</v>
+      </c>
       <c r="K14">
         <v>2</v>
       </c>
@@ -4321,6 +4352,9 @@
       <c r="I15" t="s">
         <v>213</v>
       </c>
+      <c r="J15" t="s">
+        <v>278</v>
+      </c>
       <c r="K15">
         <v>1</v>
       </c>
@@ -4345,6 +4379,9 @@
       <c r="I16" t="s">
         <v>213</v>
       </c>
+      <c r="J16" t="s">
+        <v>278</v>
+      </c>
       <c r="K16">
         <v>2</v>
       </c>
@@ -4375,6 +4412,9 @@
       <c r="I17" t="s">
         <v>213</v>
       </c>
+      <c r="J17" t="s">
+        <v>278</v>
+      </c>
       <c r="K17">
         <v>2</v>
       </c>
@@ -4402,6 +4442,9 @@
       <c r="I18" t="s">
         <v>213</v>
       </c>
+      <c r="J18" t="s">
+        <v>278</v>
+      </c>
       <c r="K18">
         <v>1</v>
       </c>
@@ -4429,6 +4472,9 @@
       <c r="I19" t="s">
         <v>213</v>
       </c>
+      <c r="J19" t="s">
+        <v>278</v>
+      </c>
       <c r="K19">
         <v>2</v>
       </c>
@@ -4456,6 +4502,9 @@
       <c r="I20" t="s">
         <v>213</v>
       </c>
+      <c r="J20" t="s">
+        <v>278</v>
+      </c>
       <c r="K20">
         <v>1</v>
       </c>
@@ -4483,6 +4532,9 @@
       <c r="I21" t="s">
         <v>213</v>
       </c>
+      <c r="J21" t="s">
+        <v>278</v>
+      </c>
       <c r="K21">
         <v>1</v>
       </c>
@@ -4510,6 +4562,9 @@
       <c r="I22" t="s">
         <v>213</v>
       </c>
+      <c r="J22" t="s">
+        <v>278</v>
+      </c>
       <c r="K22">
         <v>1</v>
       </c>
@@ -4537,6 +4592,9 @@
       <c r="I23" t="s">
         <v>213</v>
       </c>
+      <c r="J23" t="s">
+        <v>278</v>
+      </c>
       <c r="K23">
         <v>1</v>
       </c>
@@ -4564,6 +4622,9 @@
       <c r="I24" t="s">
         <v>213</v>
       </c>
+      <c r="J24" t="s">
+        <v>278</v>
+      </c>
       <c r="K24">
         <v>1</v>
       </c>
@@ -4588,6 +4649,9 @@
       <c r="I25" t="s">
         <v>213</v>
       </c>
+      <c r="J25" t="s">
+        <v>278</v>
+      </c>
       <c r="K25">
         <v>2</v>
       </c>
@@ -4615,6 +4679,9 @@
       <c r="I26" t="s">
         <v>213</v>
       </c>
+      <c r="J26" t="s">
+        <v>278</v>
+      </c>
       <c r="K26">
         <v>1</v>
       </c>
@@ -4642,6 +4709,9 @@
       <c r="I27" t="s">
         <v>213</v>
       </c>
+      <c r="J27" t="s">
+        <v>278</v>
+      </c>
       <c r="K27">
         <v>2</v>
       </c>
@@ -4669,6 +4739,9 @@
       <c r="I28" t="s">
         <v>213</v>
       </c>
+      <c r="J28" t="s">
+        <v>278</v>
+      </c>
       <c r="K28">
         <v>1</v>
       </c>
@@ -4695,6 +4768,9 @@
       </c>
       <c r="I29" t="s">
         <v>213</v>
+      </c>
+      <c r="J29" t="s">
+        <v>278</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -4717,7 +4793,9 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" s="8"/>
+      <c r="J30" t="s">
+        <v>278</v>
+      </c>
       <c r="K30" s="8"/>
     </row>
     <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4743,6 +4821,9 @@
       <c r="I31" t="s">
         <v>213</v>
       </c>
+      <c r="J31" t="s">
+        <v>278</v>
+      </c>
       <c r="K31">
         <v>2</v>
       </c>
@@ -4771,6 +4852,9 @@
       <c r="I32" t="s">
         <v>213</v>
       </c>
+      <c r="J32" t="s">
+        <v>278</v>
+      </c>
       <c r="K32">
         <v>2</v>
       </c>
@@ -4798,6 +4882,9 @@
       <c r="I33" t="s">
         <v>213</v>
       </c>
+      <c r="J33" t="s">
+        <v>278</v>
+      </c>
       <c r="K33">
         <v>1</v>
       </c>
@@ -4828,6 +4915,9 @@
       <c r="I34" t="s">
         <v>213</v>
       </c>
+      <c r="J34" t="s">
+        <v>278</v>
+      </c>
       <c r="K34">
         <v>2</v>
       </c>
@@ -4852,6 +4942,9 @@
       <c r="I35" t="s">
         <v>213</v>
       </c>
+      <c r="J35" t="s">
+        <v>278</v>
+      </c>
       <c r="K35">
         <v>2</v>
       </c>
@@ -4879,6 +4972,9 @@
       <c r="I36" t="s">
         <v>213</v>
       </c>
+      <c r="J36" t="s">
+        <v>278</v>
+      </c>
       <c r="K36">
         <v>1</v>
       </c>
@@ -4906,6 +5002,9 @@
       <c r="I37" t="s">
         <v>213</v>
       </c>
+      <c r="J37" t="s">
+        <v>278</v>
+      </c>
       <c r="K37">
         <v>1</v>
       </c>
@@ -4933,6 +5032,9 @@
       <c r="I38" t="s">
         <v>213</v>
       </c>
+      <c r="J38" t="s">
+        <v>278</v>
+      </c>
       <c r="K38">
         <v>2</v>
       </c>
@@ -4960,6 +5062,9 @@
       <c r="I39" t="s">
         <v>213</v>
       </c>
+      <c r="J39" t="s">
+        <v>278</v>
+      </c>
       <c r="K39">
         <v>2</v>
       </c>
@@ -4987,6 +5092,9 @@
       <c r="I40" t="s">
         <v>213</v>
       </c>
+      <c r="J40" t="s">
+        <v>278</v>
+      </c>
       <c r="K40">
         <v>1</v>
       </c>
@@ -5013,6 +5121,9 @@
       </c>
       <c r="I41" t="s">
         <v>213</v>
+      </c>
+      <c r="J41" t="s">
+        <v>278</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -5037,7 +5148,9 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
+      <c r="J42" t="s">
+        <v>278</v>
+      </c>
       <c r="K42" s="8"/>
     </row>
     <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -5063,6 +5176,9 @@
       <c r="I43" t="s">
         <v>213</v>
       </c>
+      <c r="J43" t="s">
+        <v>278</v>
+      </c>
       <c r="K43">
         <v>2</v>
       </c>
@@ -5089,6 +5205,9 @@
       </c>
       <c r="I44" t="s">
         <v>213</v>
+      </c>
+      <c r="J44" t="s">
+        <v>278</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -5113,7 +5232,9 @@
       <c r="G45" s="8"/>
       <c r="H45" s="11"/>
       <c r="I45" s="8"/>
-      <c r="J45" s="8"/>
+      <c r="J45" t="s">
+        <v>278</v>
+      </c>
       <c r="K45" s="8">
         <v>1</v>
       </c>
@@ -5144,6 +5265,9 @@
       <c r="I46" t="s">
         <v>213</v>
       </c>
+      <c r="J46" t="s">
+        <v>278</v>
+      </c>
       <c r="K46">
         <v>2</v>
       </c>
@@ -5174,6 +5298,9 @@
       <c r="I47" t="s">
         <v>213</v>
       </c>
+      <c r="J47" t="s">
+        <v>278</v>
+      </c>
       <c r="K47">
         <v>2</v>
       </c>
@@ -5201,6 +5328,9 @@
       <c r="I48" t="s">
         <v>213</v>
       </c>
+      <c r="J48" t="s">
+        <v>278</v>
+      </c>
       <c r="K48">
         <v>1</v>
       </c>
@@ -5228,6 +5358,9 @@
       <c r="I49" t="s">
         <v>213</v>
       </c>
+      <c r="J49" t="s">
+        <v>278</v>
+      </c>
       <c r="K49">
         <v>2</v>
       </c>
@@ -5254,6 +5387,9 @@
       </c>
       <c r="I50" t="s">
         <v>213</v>
+      </c>
+      <c r="J50" t="s">
+        <v>278</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -5276,7 +5412,9 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
+      <c r="J51" t="s">
+        <v>278</v>
+      </c>
       <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5305,6 +5443,9 @@
       <c r="I52" t="s">
         <v>213</v>
       </c>
+      <c r="J52" t="s">
+        <v>278</v>
+      </c>
       <c r="K52">
         <v>2</v>
       </c>
@@ -5332,6 +5473,9 @@
       <c r="I53" t="s">
         <v>213</v>
       </c>
+      <c r="J53" t="s">
+        <v>278</v>
+      </c>
       <c r="K53">
         <v>2</v>
       </c>
@@ -5359,6 +5503,9 @@
       <c r="I54" t="s">
         <v>213</v>
       </c>
+      <c r="J54" t="s">
+        <v>278</v>
+      </c>
       <c r="K54">
         <v>1</v>
       </c>
@@ -5386,6 +5533,9 @@
       <c r="I55" t="s">
         <v>213</v>
       </c>
+      <c r="J55" t="s">
+        <v>278</v>
+      </c>
       <c r="K55">
         <v>2</v>
       </c>
@@ -5413,6 +5563,9 @@
       <c r="I56" t="s">
         <v>213</v>
       </c>
+      <c r="J56" t="s">
+        <v>278</v>
+      </c>
       <c r="K56">
         <v>1</v>
       </c>
@@ -5440,6 +5593,9 @@
       <c r="I57" t="s">
         <v>213</v>
       </c>
+      <c r="J57" t="s">
+        <v>278</v>
+      </c>
       <c r="K57">
         <v>2</v>
       </c>
@@ -5470,6 +5626,9 @@
       <c r="I58" t="s">
         <v>213</v>
       </c>
+      <c r="J58" t="s">
+        <v>278</v>
+      </c>
       <c r="K58">
         <v>2</v>
       </c>
@@ -5500,6 +5659,9 @@
       <c r="I59" t="s">
         <v>213</v>
       </c>
+      <c r="J59" t="s">
+        <v>278</v>
+      </c>
       <c r="K59">
         <v>2</v>
       </c>
@@ -5527,6 +5689,9 @@
       <c r="I60" t="s">
         <v>213</v>
       </c>
+      <c r="J60" t="s">
+        <v>278</v>
+      </c>
       <c r="K60">
         <v>2</v>
       </c>
@@ -5554,6 +5719,9 @@
       <c r="I61" t="s">
         <v>213</v>
       </c>
+      <c r="J61" t="s">
+        <v>278</v>
+      </c>
       <c r="K61">
         <v>1</v>
       </c>
@@ -5581,6 +5749,9 @@
       <c r="I62" t="s">
         <v>213</v>
       </c>
+      <c r="J62" t="s">
+        <v>278</v>
+      </c>
       <c r="K62">
         <v>1</v>
       </c>
@@ -5605,6 +5776,9 @@
       <c r="I63" t="s">
         <v>213</v>
       </c>
+      <c r="J63" t="s">
+        <v>278</v>
+      </c>
       <c r="K63">
         <v>2</v>
       </c>
@@ -5632,6 +5806,9 @@
       <c r="I64" t="s">
         <v>213</v>
       </c>
+      <c r="J64" t="s">
+        <v>278</v>
+      </c>
       <c r="K64">
         <v>2</v>
       </c>
@@ -5659,6 +5836,9 @@
       <c r="I65" t="s">
         <v>213</v>
       </c>
+      <c r="J65" t="s">
+        <v>278</v>
+      </c>
       <c r="K65">
         <v>2</v>
       </c>
@@ -5686,6 +5866,9 @@
       <c r="I66" t="s">
         <v>213</v>
       </c>
+      <c r="J66" t="s">
+        <v>278</v>
+      </c>
       <c r="K66">
         <v>2</v>
       </c>
@@ -5716,6 +5899,9 @@
       <c r="I67" t="s">
         <v>213</v>
       </c>
+      <c r="J67" t="s">
+        <v>278</v>
+      </c>
       <c r="K67">
         <v>1</v>
       </c>
@@ -5743,6 +5929,9 @@
       <c r="I68" t="s">
         <v>213</v>
       </c>
+      <c r="J68" t="s">
+        <v>278</v>
+      </c>
       <c r="K68">
         <v>2</v>
       </c>
@@ -5770,6 +5959,9 @@
       <c r="I69" t="s">
         <v>213</v>
       </c>
+      <c r="J69" t="s">
+        <v>278</v>
+      </c>
       <c r="K69">
         <v>2</v>
       </c>
@@ -5800,6 +5992,9 @@
       <c r="I70" t="s">
         <v>213</v>
       </c>
+      <c r="J70" t="s">
+        <v>278</v>
+      </c>
       <c r="K70">
         <v>1</v>
       </c>
@@ -5829,6 +6024,9 @@
       </c>
       <c r="I71" t="s">
         <v>213</v>
+      </c>
+      <c r="J71" t="s">
+        <v>278</v>
       </c>
       <c r="K71">
         <v>1</v>
@@ -5853,7 +6051,9 @@
       <c r="G72" s="8"/>
       <c r="H72" s="11"/>
       <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
+      <c r="J72" t="s">
+        <v>278</v>
+      </c>
       <c r="K72" s="8"/>
     </row>
     <row r="73" spans="1:11" ht="64" x14ac:dyDescent="0.2">
@@ -5879,6 +6079,9 @@
       <c r="I73" t="s">
         <v>213</v>
       </c>
+      <c r="J73" t="s">
+        <v>278</v>
+      </c>
       <c r="K73">
         <v>2</v>
       </c>
@@ -5909,6 +6112,9 @@
       <c r="I74" t="s">
         <v>278</v>
       </c>
+      <c r="J74" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="75" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
@@ -5933,6 +6139,9 @@
       <c r="I75" t="s">
         <v>278</v>
       </c>
+      <c r="J75" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="76" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
@@ -5960,6 +6169,9 @@
       <c r="I76" t="s">
         <v>278</v>
       </c>
+      <c r="J76" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="77" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
@@ -5984,6 +6196,9 @@
       <c r="I77" t="s">
         <v>278</v>
       </c>
+      <c r="J77" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="78" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
@@ -6011,6 +6226,9 @@
       <c r="I78" t="s">
         <v>278</v>
       </c>
+      <c r="J78" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="79" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
@@ -6038,6 +6256,9 @@
       <c r="I79" t="s">
         <v>278</v>
       </c>
+      <c r="J79" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="80" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
@@ -6062,8 +6283,11 @@
       <c r="I80" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="J80" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>115</v>
       </c>
@@ -6089,8 +6313,11 @@
       <c r="I81" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="J81" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>112</v>
       </c>
@@ -6116,8 +6343,11 @@
       <c r="I82" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="J82" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>153</v>
       </c>
@@ -6138,6 +6368,9 @@
         <v>279</v>
       </c>
       <c r="I83" t="s">
+        <v>278</v>
+      </c>
+      <c r="J83" t="s">
         <v>278</v>
       </c>
     </row>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21E24930-D70C-8142-B27B-29CD533DABE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9903CEB-E247-5843-AB42-7F769ED81C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="16640" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="282">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -692,13 +692,6 @@
   </si>
   <si>
     <t>Main Menu, Holiday &amp; Closed Menu, Family Menu, Housing Menu, Other Legal Menu, Closed Queue Menu</t>
-  </si>
-  <si>
-    <t>Positive / Negative</t>
-  </si>
-  <si>
-    <t>If EP name = 'Closed Queue Menu Telephony EP', then Negative, and type = "Closed queue",
-otherwise Positive, type = 'Reached voicemail'</t>
   </si>
   <si>
     <t>Main Menu</t>
@@ -889,6 +882,13 @@
   </si>
   <si>
     <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
+  </si>
+  <si>
+    <t>If EP name = 'Closed Queue Menu Telephony EP', then Negative, and type = "Closed queue",
+otherwise Positive, type = 'Reached voicemail', if EP name = 'Closed Hours-Holidays Menu Telephony EP' then neutral, and type = 'After hours call</t>
+  </si>
+  <si>
+    <t>Positive / Negative / Neutral</t>
   </si>
 </sst>
 </file>
@@ -4025,13 +4025,13 @@
         <v>209</v>
       </c>
       <c r="J4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -4046,16 +4046,16 @@
         <v>0.10352919393661297</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>217</v>
+        <v>281</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>218</v>
+        <v>280</v>
       </c>
       <c r="I5" t="s">
         <v>209</v>
       </c>
       <c r="J5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K5">
         <v>2</v>
@@ -4066,7 +4066,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C6" s="2">
         <v>13075</v>
@@ -4085,7 +4085,7 @@
         <v>209</v>
       </c>
       <c r="J6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -4096,7 +4096,7 @@
         <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C7" s="2">
         <v>12010</v>
@@ -4106,16 +4106,16 @@
         <v>4.8341262749454599E-2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="I7" t="s">
         <v>209</v>
       </c>
       <c r="J7" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K7">
         <v>2</v>
@@ -4126,7 +4126,7 @@
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C8" s="2">
         <v>11987</v>
@@ -4145,7 +4145,7 @@
         <v>209</v>
       </c>
       <c r="J8" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K8">
         <v>1</v>
@@ -4169,13 +4169,10 @@
         <v>212</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I9" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="J9" t="s">
-        <v>278</v>
       </c>
       <c r="K9" s="8"/>
     </row>
@@ -4195,12 +4192,9 @@
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
       <c r="H10" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="I10" s="8"/>
-      <c r="J10" t="s">
-        <v>278</v>
-      </c>
       <c r="K10" s="8"/>
     </row>
     <row r="11" spans="1:11" ht="48" x14ac:dyDescent="0.2">
@@ -4208,7 +4202,7 @@
         <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C11" s="2">
         <v>8939</v>
@@ -4218,16 +4212,16 @@
         <v>3.5980228785793066E-2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="I11" t="s">
         <v>213</v>
       </c>
       <c r="J11" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K11">
         <v>2</v>
@@ -4248,19 +4242,19 @@
         <v>3.1757915328326128E-2</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F12" t="s">
+        <v>227</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>228</v>
-      </c>
-      <c r="F12" t="s">
-        <v>229</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>230</v>
       </c>
       <c r="I12" t="s">
         <v>213</v>
       </c>
       <c r="J12" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K12">
         <v>2</v>
@@ -4271,7 +4265,7 @@
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C13" s="2">
         <v>7765</v>
@@ -4281,16 +4275,16 @@
         <v>3.125477978763655E-2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I13" t="s">
         <v>213</v>
       </c>
       <c r="J13" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K13">
         <v>2</v>
@@ -4301,7 +4295,7 @@
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C14" s="2">
         <v>6895</v>
@@ -4311,19 +4305,19 @@
         <v>2.7752956424437092E-2</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="I14" t="s">
         <v>213</v>
       </c>
       <c r="J14" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K14">
         <v>2</v>
@@ -4334,7 +4328,7 @@
         <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C15" s="2">
         <v>6863</v>
@@ -4353,7 +4347,7 @@
         <v>213</v>
       </c>
       <c r="J15" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -4380,7 +4374,7 @@
         <v>213</v>
       </c>
       <c r="J16" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K16">
         <v>2</v>
@@ -4391,7 +4385,7 @@
         <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C17" s="2">
         <v>2545</v>
@@ -4401,19 +4395,19 @@
         <v>1.0243839608439796E-2</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="I17" t="s">
         <v>213</v>
       </c>
       <c r="J17" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K17">
         <v>2</v>
@@ -4424,7 +4418,7 @@
         <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C18" s="2">
         <v>2394</v>
@@ -4443,7 +4437,7 @@
         <v>213</v>
       </c>
       <c r="J18" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -4454,7 +4448,7 @@
         <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2">
         <v>2267</v>
@@ -4464,16 +4458,16 @@
         <v>9.1248661659461758E-3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F19" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I19" t="s">
         <v>213</v>
       </c>
       <c r="J19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K19">
         <v>2</v>
@@ -4484,7 +4478,7 @@
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C20" s="2">
         <v>2136</v>
@@ -4503,7 +4497,7 @@
         <v>213</v>
       </c>
       <c r="J20" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -4514,7 +4508,7 @@
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C21" s="2">
         <v>1462</v>
@@ -4533,7 +4527,7 @@
         <v>213</v>
       </c>
       <c r="J21" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -4544,7 +4538,7 @@
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C22" s="2">
         <v>1287</v>
@@ -4563,7 +4557,7 @@
         <v>213</v>
       </c>
       <c r="J22" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -4574,7 +4568,7 @@
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C23" s="2">
         <v>1267</v>
@@ -4593,7 +4587,7 @@
         <v>213</v>
       </c>
       <c r="J23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -4604,7 +4598,7 @@
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C24" s="2">
         <v>1209</v>
@@ -4623,7 +4617,7 @@
         <v>213</v>
       </c>
       <c r="J24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -4634,7 +4628,7 @@
         <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C25" s="2">
         <v>870</v>
@@ -4644,13 +4638,13 @@
         <v>3.5018233631994591E-3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I25" t="s">
         <v>213</v>
       </c>
       <c r="J25" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K25">
         <v>2</v>
@@ -4661,7 +4655,7 @@
         <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2">
         <v>837</v>
@@ -4680,7 +4674,7 @@
         <v>213</v>
       </c>
       <c r="J26" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -4691,7 +4685,7 @@
         <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C27" s="2">
         <v>836</v>
@@ -4701,16 +4695,16 @@
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F27" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I27" t="s">
         <v>213</v>
       </c>
       <c r="J27" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K27">
         <v>2</v>
@@ -4721,7 +4715,7 @@
         <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C28" s="2">
         <v>785</v>
@@ -4740,7 +4734,7 @@
         <v>213</v>
       </c>
       <c r="J28" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -4751,7 +4745,7 @@
         <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2">
         <v>771</v>
@@ -4770,7 +4764,7 @@
         <v>213</v>
       </c>
       <c r="J29" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -4793,9 +4787,6 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
-      <c r="J30" t="s">
-        <v>278</v>
-      </c>
       <c r="K30" s="8"/>
     </row>
     <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -4803,7 +4794,7 @@
         <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C31" s="2">
         <v>672</v>
@@ -4813,16 +4804,16 @@
         <v>2.7048566667471682E-3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I31" t="s">
         <v>213</v>
       </c>
       <c r="J31" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K31">
         <v>2</v>
@@ -4833,7 +4824,7 @@
         <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C32" s="2">
         <v>604</v>
@@ -4843,17 +4834,17 @@
         <v>2.4311509326120384E-3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F32" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" t="s">
         <v>213</v>
       </c>
       <c r="J32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K32">
         <v>2</v>
@@ -4864,7 +4855,7 @@
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C33" s="2">
         <v>543</v>
@@ -4883,7 +4874,7 @@
         <v>213</v>
       </c>
       <c r="J33" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -4894,7 +4885,7 @@
         <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C34" s="2">
         <v>541</v>
@@ -4904,19 +4895,19 @@
         <v>2.1775706201044914E-3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F34" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I34" t="s">
         <v>213</v>
       </c>
       <c r="J34" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K34">
         <v>2</v>
@@ -4927,7 +4918,7 @@
         <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C35" s="2">
         <v>540</v>
@@ -4937,13 +4928,13 @@
         <v>2.1735455357789744E-3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="I35" t="s">
         <v>213</v>
       </c>
       <c r="J35" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K35">
         <v>2</v>
@@ -4954,7 +4945,7 @@
         <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C36" s="2">
         <v>527</v>
@@ -4973,7 +4964,7 @@
         <v>213</v>
       </c>
       <c r="J36" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -4984,7 +4975,7 @@
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C37" s="2">
         <v>502</v>
@@ -5003,7 +4994,7 @@
         <v>213</v>
       </c>
       <c r="J37" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -5014,7 +5005,7 @@
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C38" s="2">
         <v>479</v>
@@ -5024,16 +5015,16 @@
         <v>1.9280153919224608E-3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I38" t="s">
         <v>213</v>
       </c>
       <c r="J38" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K38">
         <v>2</v>
@@ -5044,7 +5035,7 @@
         <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C39" s="2">
         <v>454</v>
@@ -5054,16 +5045,16 @@
         <v>1.8273882837845452E-3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F39" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I39" t="s">
         <v>213</v>
       </c>
       <c r="J39" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K39">
         <v>2</v>
@@ -5074,7 +5065,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C40" s="2">
         <v>444</v>
@@ -5087,13 +5078,13 @@
         <v>207</v>
       </c>
       <c r="F40" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I40" t="s">
         <v>213</v>
       </c>
       <c r="J40" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K40">
         <v>1</v>
@@ -5104,7 +5095,7 @@
         <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C41" s="2">
         <v>442</v>
@@ -5117,13 +5108,13 @@
         <v>207</v>
       </c>
       <c r="F41" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I41" t="s">
         <v>213</v>
       </c>
       <c r="J41" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -5134,7 +5125,7 @@
         <v>116</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C42" s="9">
         <v>412</v>
@@ -5148,9 +5139,6 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
-      <c r="J42" t="s">
-        <v>278</v>
-      </c>
       <c r="K42" s="8"/>
     </row>
     <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -5158,7 +5146,7 @@
         <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C43" s="2">
         <v>353</v>
@@ -5168,16 +5156,16 @@
         <v>1.4208547669073666E-3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F43" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I43" t="s">
         <v>213</v>
       </c>
       <c r="J43" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K43">
         <v>2</v>
@@ -5188,7 +5176,7 @@
         <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C44" s="2">
         <v>298</v>
@@ -5207,7 +5195,7 @@
         <v>213</v>
       </c>
       <c r="J44" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -5218,7 +5206,7 @@
         <v>69</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C45" s="9">
         <v>278</v>
@@ -5232,9 +5220,6 @@
       <c r="G45" s="8"/>
       <c r="H45" s="11"/>
       <c r="I45" s="8"/>
-      <c r="J45" t="s">
-        <v>278</v>
-      </c>
       <c r="K45" s="8">
         <v>1</v>
       </c>
@@ -5244,7 +5229,7 @@
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C46" s="2">
         <v>228</v>
@@ -5254,19 +5239,19 @@
         <v>9.1771922621778929E-4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F46" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I46" t="s">
         <v>213</v>
       </c>
       <c r="J46" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K46">
         <v>2</v>
@@ -5277,7 +5262,7 @@
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C47" s="2">
         <v>219</v>
@@ -5287,19 +5272,19 @@
         <v>8.8149346728813973E-4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F47" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I47" t="s">
         <v>213</v>
       </c>
       <c r="J47" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K47">
         <v>2</v>
@@ -5310,7 +5295,7 @@
         <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C48" s="2">
         <v>212</v>
@@ -5329,7 +5314,7 @@
         <v>213</v>
       </c>
       <c r="J48" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -5340,7 +5325,7 @@
         <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C49" s="2">
         <v>185</v>
@@ -5350,16 +5335,16 @@
         <v>7.446406002205746E-4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F49" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="I49" t="s">
         <v>213</v>
       </c>
       <c r="J49" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K49">
         <v>2</v>
@@ -5370,7 +5355,7 @@
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C50" s="2">
         <v>183</v>
@@ -5383,13 +5368,13 @@
         <v>207</v>
       </c>
       <c r="F50" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I50" t="s">
         <v>213</v>
       </c>
       <c r="J50" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -5397,7 +5382,7 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="9">
@@ -5412,9 +5397,6 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
-      <c r="J51" t="s">
-        <v>278</v>
-      </c>
       <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
@@ -5422,7 +5404,7 @@
         <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C52" s="2">
         <v>158</v>
@@ -5432,19 +5414,19 @@
         <v>6.3596332343162591E-4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F52" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I52" t="s">
         <v>213</v>
       </c>
       <c r="J52" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K52">
         <v>2</v>
@@ -5455,7 +5437,7 @@
         <v>132</v>
       </c>
       <c r="B53" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C53" s="2">
         <v>139</v>
@@ -5465,16 +5447,16 @@
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F53" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I53" t="s">
         <v>213</v>
       </c>
       <c r="J53" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K53">
         <v>2</v>
@@ -5485,7 +5467,7 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C54" s="2">
         <v>138</v>
@@ -5504,7 +5486,7 @@
         <v>213</v>
       </c>
       <c r="J54" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K54">
         <v>1</v>
@@ -5515,7 +5497,7 @@
         <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C55" s="2">
         <v>127</v>
@@ -5525,16 +5507,16 @@
         <v>5.1118570934061071E-4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F55" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I55" t="s">
         <v>213</v>
       </c>
       <c r="J55" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K55">
         <v>2</v>
@@ -5545,7 +5527,7 @@
         <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C56" s="2">
         <v>116</v>
@@ -5564,7 +5546,7 @@
         <v>213</v>
       </c>
       <c r="J56" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K56">
         <v>1</v>
@@ -5575,7 +5557,7 @@
         <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C57" s="2">
         <v>85</v>
@@ -5585,16 +5567,16 @@
         <v>3.4213216766891265E-4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F57" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I57" t="s">
         <v>213</v>
       </c>
       <c r="J57" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K57">
         <v>2</v>
@@ -5605,7 +5587,7 @@
         <v>142</v>
       </c>
       <c r="B58" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C58" s="2">
         <v>70</v>
@@ -5618,16 +5600,16 @@
         <v>207</v>
       </c>
       <c r="F58" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="I58" t="s">
         <v>213</v>
       </c>
       <c r="J58" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K58">
         <v>2</v>
@@ -5638,7 +5620,7 @@
         <v>144</v>
       </c>
       <c r="B59" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2">
         <v>67</v>
@@ -5648,19 +5630,19 @@
         <v>2.6968064980961351E-4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F59" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I59" t="s">
         <v>213</v>
       </c>
       <c r="J59" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K59">
         <v>2</v>
@@ -5671,7 +5653,7 @@
         <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C60" s="2">
         <v>58</v>
@@ -5681,16 +5663,16 @@
         <v>2.3345489087996395E-4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I60" t="s">
         <v>213</v>
       </c>
       <c r="J60" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K60">
         <v>2</v>
@@ -5701,7 +5683,7 @@
         <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C61" s="2">
         <v>37</v>
@@ -5714,13 +5696,13 @@
         <v>207</v>
       </c>
       <c r="F61" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I61" t="s">
         <v>213</v>
       </c>
       <c r="J61" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K61">
         <v>1</v>
@@ -5731,7 +5713,7 @@
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C62" s="2">
         <v>34</v>
@@ -5744,13 +5726,13 @@
         <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="I62" t="s">
         <v>213</v>
       </c>
       <c r="J62" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K62">
         <v>1</v>
@@ -5771,13 +5753,13 @@
         <v>207</v>
       </c>
       <c r="H63" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I63" t="s">
         <v>213</v>
       </c>
       <c r="J63" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K63">
         <v>2</v>
@@ -5788,7 +5770,7 @@
         <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C64" s="2">
         <v>31</v>
@@ -5798,16 +5780,16 @@
         <v>1.247776140910152E-4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F64" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="I64" t="s">
         <v>213</v>
       </c>
       <c r="J64" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K64">
         <v>2</v>
@@ -5818,7 +5800,7 @@
         <v>98</v>
       </c>
       <c r="B65" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C65" s="2">
         <v>27</v>
@@ -5831,13 +5813,13 @@
         <v>207</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I65" t="s">
         <v>213</v>
       </c>
       <c r="J65" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K65">
         <v>2</v>
@@ -5848,7 +5830,7 @@
         <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C66" s="2">
         <v>27</v>
@@ -5861,13 +5843,13 @@
         <v>207</v>
       </c>
       <c r="H66" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I66" t="s">
         <v>213</v>
       </c>
       <c r="J66" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K66">
         <v>2</v>
@@ -5891,16 +5873,16 @@
         <v>207</v>
       </c>
       <c r="F67" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I67" t="s">
         <v>213</v>
       </c>
       <c r="J67" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K67">
         <v>1</v>
@@ -5911,7 +5893,7 @@
         <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C68" s="2">
         <v>13</v>
@@ -5924,13 +5906,13 @@
         <v>207</v>
       </c>
       <c r="F68" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I68" t="s">
         <v>213</v>
       </c>
       <c r="J68" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K68">
         <v>2</v>
@@ -5941,7 +5923,7 @@
         <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C69" s="2">
         <v>8</v>
@@ -5951,16 +5933,16 @@
         <v>3.2200674604132955E-5</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I69" t="s">
         <v>213</v>
       </c>
       <c r="J69" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K69">
         <v>2</v>
@@ -5971,7 +5953,7 @@
         <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C70" s="2">
         <v>5</v>
@@ -5984,16 +5966,16 @@
         <v>207</v>
       </c>
       <c r="F70" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H70" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I70" t="s">
         <v>213</v>
       </c>
       <c r="J70" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K70">
         <v>1</v>
@@ -6004,7 +5986,7 @@
         <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C71" s="2">
         <v>4</v>
@@ -6017,16 +5999,16 @@
         <v>207</v>
       </c>
       <c r="F71" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H71" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I71" t="s">
         <v>213</v>
       </c>
       <c r="J71" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K71">
         <v>1</v>
@@ -6037,7 +6019,7 @@
         <v>125</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C72" s="9">
         <v>4</v>
@@ -6051,9 +6033,6 @@
       <c r="G72" s="8"/>
       <c r="H72" s="11"/>
       <c r="I72" s="8"/>
-      <c r="J72" t="s">
-        <v>278</v>
-      </c>
       <c r="K72" s="8"/>
     </row>
     <row r="73" spans="1:11" ht="64" x14ac:dyDescent="0.2">
@@ -6061,7 +6040,7 @@
         <v>129</v>
       </c>
       <c r="B73" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C73" s="2">
         <v>2</v>
@@ -6074,13 +6053,13 @@
         <v>207</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I73" t="s">
         <v>213</v>
       </c>
       <c r="J73" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="K73">
         <v>2</v>
@@ -6091,7 +6070,7 @@
         <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
@@ -6107,13 +6086,13 @@
         <v>215</v>
       </c>
       <c r="H74" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I74" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J74" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -6121,7 +6100,7 @@
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -6134,13 +6113,13 @@
         <v>207</v>
       </c>
       <c r="H75" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I75" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J75" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -6148,7 +6127,7 @@
         <v>127</v>
       </c>
       <c r="B76" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -6164,13 +6143,13 @@
         <v>215</v>
       </c>
       <c r="H76" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I76" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J76" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -6178,7 +6157,7 @@
         <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -6191,13 +6170,13 @@
         <v>207</v>
       </c>
       <c r="H77" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I77" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J77" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="78" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -6205,7 +6184,7 @@
         <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -6221,13 +6200,13 @@
         <v>215</v>
       </c>
       <c r="H78" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I78" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J78" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -6235,7 +6214,7 @@
         <v>176</v>
       </c>
       <c r="B79" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -6245,19 +6224,19 @@
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F79" t="s">
         <v>215</v>
       </c>
       <c r="H79" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I79" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J79" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="80" spans="1:11" ht="16" x14ac:dyDescent="0.2">
@@ -6265,7 +6244,7 @@
         <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -6275,16 +6254,16 @@
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H80" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I80" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J80" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6292,7 +6271,7 @@
         <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -6308,13 +6287,13 @@
         <v>215</v>
       </c>
       <c r="H81" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I81" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J81" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6322,7 +6301,7 @@
         <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -6338,13 +6317,13 @@
         <v>215</v>
       </c>
       <c r="H82" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I82" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J82" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
@@ -6352,7 +6331,7 @@
         <v>153</v>
       </c>
       <c r="B83" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -6365,13 +6344,13 @@
         <v>207</v>
       </c>
       <c r="H83" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="I83" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="J83" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9903CEB-E247-5843-AB42-7F769ED81C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{584E58ED-953E-46FD-9EA9-69225F98A99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -34,6 +34,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="288">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -691,7 +692,17 @@
     <t>Abandoned</t>
   </si>
   <si>
+    <t>Sabrina</t>
+  </si>
+  <si>
     <t>Main Menu, Holiday &amp; Closed Menu, Family Menu, Housing Menu, Other Legal Menu, Closed Queue Menu</t>
+  </si>
+  <si>
+    <t>Positive / Negative / Neutral</t>
+  </si>
+  <si>
+    <t>If EP name = 'Closed Queue Menu Telephony EP', then Negative, and type = "Closed queue",
+otherwise Positive, type = 'Reached voicemail', if EP name = 'Closed Hours-Holidays Menu Telephony EP' then neutral, and type = 'After hours call</t>
   </si>
   <si>
     <t>Main Menu</t>
@@ -710,16 +721,31 @@
     <t>Legal Menu</t>
   </si>
   <si>
-    <t>Callers are spending time on this activity, but not sure what are they doing, ask Mark</t>
-  </si>
-  <si>
-    <t>ask Mark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive / Neutral </t>
-  </si>
-  <si>
-    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect - tenative</t>
+    <t>Farmworker Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative </t>
+  </si>
+  <si>
+    <t>Abandoned (tenative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on info from Mark, this reflects no activity at Farmworker Menu and cannot progress without a selection; either call disconnects after max number of repetitions or the caller hangs up; max step counter is unknown so believe calls should be considered abandoned </t>
+  </si>
+  <si>
+    <t>N/A - Ad Hoc Outbound Call</t>
+  </si>
+  <si>
+    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up</t>
+  </si>
+  <si>
+    <t>Courtesy Callback, Queues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive / neutral (tenative) </t>
+  </si>
+  <si>
+    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect  to customer; uncertainty b/c there are not activity names that indicate connection in the data</t>
   </si>
   <si>
     <t>Positive</t>
@@ -776,6 +802,12 @@
     <t>HIV Menu</t>
   </si>
   <si>
+    <t xml:space="preserve">Positive / Neutral (tenative) </t>
+  </si>
+  <si>
+    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect; uncertainty b/c there are not activity names that indicate connection in the data</t>
+  </si>
+  <si>
     <t xml:space="preserve">Main Menu </t>
   </si>
   <si>
@@ -806,18 +838,18 @@
     <t>Benefits Menu</t>
   </si>
   <si>
+    <t xml:space="preserve">Neutral </t>
+  </si>
+  <si>
+    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
+  </si>
+  <si>
     <t>Caller is non-Cook County Senior and did not make a selection after message</t>
   </si>
   <si>
     <t>Queues</t>
   </si>
   <si>
-    <t xml:space="preserve">Neutral </t>
-  </si>
-  <si>
-    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
-  </si>
-  <si>
     <t>Employment menu</t>
   </si>
   <si>
@@ -842,9 +874,6 @@
     <t>No Agent Name for attempted courtesy callback</t>
   </si>
   <si>
-    <t>Farmworker Menu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Assuming this corresponds to Farm Worker Voicemail transfer on flow charts </t>
   </si>
   <si>
@@ -866,29 +895,19 @@
     <t xml:space="preserve">Caller hangs up before being connected with an agent, system tries to progress but gives error since there's no caller </t>
   </si>
   <si>
-    <t xml:space="preserve">Negative </t>
-  </si>
-  <si>
     <t>Caller did not finish confirming callback</t>
   </si>
   <si>
-    <t>Sabrina</t>
+    <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
   </si>
   <si>
     <t>Should check if agents are logged into queue, if last activity then caller never entered the queue (never heard pre-queue message1), customer may have ended call after waiting</t>
   </si>
   <si>
+    <t>VIvi</t>
+  </si>
+  <si>
     <t xml:space="preserve">"Play Courtesy CallBack Confirmation" . This is typically played right before the contact is disconnected from the system. The consumer selected a courtesy callback but hung up before the system could disconnect so this is neutral. </t>
-  </si>
-  <si>
-    <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
-  </si>
-  <si>
-    <t>If EP name = 'Closed Queue Menu Telephony EP', then Negative, and type = "Closed queue",
-otherwise Positive, type = 'Reached voicemail', if EP name = 'Closed Hours-Holidays Menu Telephony EP' then neutral, and type = 'After hours call</t>
-  </si>
-  <si>
-    <t>Positive / Negative / Neutral</t>
   </si>
 </sst>
 </file>
@@ -899,7 +918,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -923,7 +942,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -933,6 +952,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -966,7 +991,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -985,6 +1010,15 @@
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1324,13 +1358,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1338,7 +1372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1346,7 +1380,7 @@
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1354,7 +1388,7 @@
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1362,7 +1396,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1370,7 +1404,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1378,7 +1412,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1386,7 +1420,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1394,7 +1428,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1402,7 +1436,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1410,7 +1444,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1418,7 +1452,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1426,7 +1460,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1434,7 +1468,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1442,7 +1476,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1450,7 +1484,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1458,7 +1492,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1466,7 +1500,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1474,7 +1508,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1482,7 +1516,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1490,7 +1524,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1498,7 +1532,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1506,7 +1540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1514,7 +1548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1522,7 +1556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1530,7 +1564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1538,7 +1572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1554,17 +1588,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="32.1">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1578,7 +1612,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1592,7 +1626,7 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1606,7 +1640,7 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1620,7 +1654,7 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1634,7 +1668,7 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1648,7 +1682,7 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1662,7 +1696,7 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1676,7 +1710,7 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1690,7 +1724,7 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1704,7 +1738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1718,7 +1752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1732,7 +1766,7 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1746,7 +1780,7 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1760,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1774,7 +1808,7 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1788,7 +1822,7 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1802,7 +1836,7 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1816,7 +1850,7 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1830,7 +1864,7 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1844,7 +1878,7 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1858,7 +1892,7 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1872,7 +1906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1886,7 +1920,7 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1900,7 +1934,7 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1914,7 +1948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1928,7 +1962,7 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1942,7 +1976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -1956,7 +1990,7 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1970,7 +2004,7 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -1984,7 +2018,7 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -1998,7 +2032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -2012,7 +2046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -2026,7 +2060,7 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -2040,7 +2074,7 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2054,7 +2088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2068,7 +2102,7 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -2082,7 +2116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -2096,7 +2130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -2110,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2124,7 +2158,7 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2138,7 +2172,7 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -2152,7 +2186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2166,7 +2200,7 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2180,7 +2214,7 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2194,7 +2228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -2208,7 +2242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2222,7 +2256,7 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2236,7 +2270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -2250,7 +2284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -2264,7 +2298,7 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -2278,7 +2312,7 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -2292,7 +2326,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2306,7 +2340,7 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -2320,7 +2354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2334,7 +2368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -2348,7 +2382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -2362,7 +2396,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2376,7 +2410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -2390,7 +2424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2404,7 +2438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2418,7 +2452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -2432,7 +2466,7 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -2446,7 +2480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -2460,7 +2494,7 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -2474,7 +2508,7 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -2488,7 +2522,7 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2502,7 +2536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -2516,7 +2550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>99</v>
       </c>
@@ -2530,7 +2564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -2544,7 +2578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -2558,7 +2592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -2572,7 +2606,7 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -2586,7 +2620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -2600,7 +2634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -2614,7 +2648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -2628,7 +2662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -2642,7 +2676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -2656,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -2670,7 +2704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -2684,7 +2718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>111</v>
       </c>
@@ -2698,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -2712,7 +2746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -2726,7 +2760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>114</v>
       </c>
@@ -2740,7 +2774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -2754,7 +2788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -2768,7 +2802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -2782,7 +2816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -2796,7 +2830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>119</v>
       </c>
@@ -2810,7 +2844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -2824,7 +2858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -2838,7 +2872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -2852,7 +2886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -2866,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -2880,7 +2914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -2894,7 +2928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -2908,7 +2942,7 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -2922,7 +2956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -2936,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -2950,7 +2984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -2964,7 +2998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -2978,7 +3012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -2992,7 +3026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -3006,7 +3040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -3020,7 +3054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -3034,7 +3068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -3048,7 +3082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -3062,7 +3096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -3076,7 +3110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3090,7 +3124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -3104,7 +3138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
         <v>141</v>
       </c>
@@ -3118,7 +3152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
         <v>142</v>
       </c>
@@ -3132,7 +3166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
         <v>143</v>
       </c>
@@ -3146,7 +3180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
         <v>144</v>
       </c>
@@ -3160,7 +3194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
         <v>145</v>
       </c>
@@ -3174,7 +3208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3188,7 +3222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
         <v>147</v>
       </c>
@@ -3202,7 +3236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -3216,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
         <v>149</v>
       </c>
@@ -3230,7 +3264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
         <v>150</v>
       </c>
@@ -3244,7 +3278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
         <v>151</v>
       </c>
@@ -3258,7 +3292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
         <v>152</v>
       </c>
@@ -3272,7 +3306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -3286,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -3300,7 +3334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
         <v>155</v>
       </c>
@@ -3314,7 +3348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
         <v>156</v>
       </c>
@@ -3328,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
         <v>157</v>
       </c>
@@ -3342,7 +3376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
         <v>158</v>
       </c>
@@ -3356,7 +3390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
         <v>159</v>
       </c>
@@ -3370,7 +3404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -3384,7 +3418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
         <v>161</v>
       </c>
@@ -3398,7 +3432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -3412,7 +3446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -3426,7 +3460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -3440,7 +3474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -3454,7 +3488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -3468,7 +3502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -3482,7 +3516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -3496,7 +3530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -3510,7 +3544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -3524,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -3538,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -3552,7 +3586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -3566,7 +3600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -3580,7 +3614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -3594,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
         <v>176</v>
       </c>
@@ -3608,7 +3642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
         <v>177</v>
       </c>
@@ -3622,7 +3656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
         <v>178</v>
       </c>
@@ -3636,7 +3670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -3650,7 +3684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
         <v>180</v>
       </c>
@@ -3664,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
         <v>181</v>
       </c>
@@ -3678,7 +3712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -3692,7 +3726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
         <v>183</v>
       </c>
@@ -3706,7 +3740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
         <v>184</v>
       </c>
@@ -3720,7 +3754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
         <v>185</v>
       </c>
@@ -3734,7 +3768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
         <v>186</v>
       </c>
@@ -3748,7 +3782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -3762,7 +3796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -3776,7 +3810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -3790,7 +3824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -3804,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -3818,7 +3852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -3832,7 +3866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -3846,7 +3880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
         <v>194</v>
       </c>
@@ -3860,7 +3894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
         <v>195</v>
       </c>
@@ -3894,19 +3928,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.5" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="48">
       <c r="A1" s="7" t="s">
         <v>196</v>
       </c>
@@ -3941,7 +3975,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="63.95">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -3971,7 +4005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="32.1">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -4001,7 +4035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="32.1">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -4025,18 +4059,18 @@
         <v>209</v>
       </c>
       <c r="J4" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="80.099999999999994">
       <c r="A5" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C5" s="2">
         <v>25721</v>
@@ -4046,27 +4080,27 @@
         <v>0.10352919393661297</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>281</v>
+        <v>218</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>280</v>
+        <v>219</v>
       </c>
       <c r="I5" t="s">
         <v>209</v>
       </c>
       <c r="J5" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="15.95">
       <c r="A6" t="s">
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C6" s="2">
         <v>13075</v>
@@ -4085,18 +4119,18 @@
         <v>209</v>
       </c>
       <c r="J6" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="63.95">
       <c r="A7" t="s">
         <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C7" s="2">
         <v>12010</v>
@@ -4106,27 +4140,27 @@
         <v>4.8341262749454599E-2</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="I7" t="s">
         <v>209</v>
       </c>
       <c r="J7" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15.95">
       <c r="A8" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C8" s="2">
         <v>11987</v>
@@ -4145,89 +4179,111 @@
         <v>209</v>
       </c>
       <c r="J8" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
+    <row r="9" spans="1:11" ht="87">
+      <c r="A9" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="9">
+      <c r="B9" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="15">
         <v>9640</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="16">
         <f t="shared" si="0"/>
         <v>3.8801812897980216E-2</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8" t="s">
+      <c r="E9" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>212</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="I9" s="17" t="s">
         <v>209</v>
       </c>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="J9" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="K9" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="62.25" customHeight="1">
+      <c r="A10" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="9">
+      <c r="B10" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="15">
         <v>9358</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="16">
         <f t="shared" si="0"/>
         <v>3.7666739118184529E-2</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="I10" s="8"/>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+      <c r="E10" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="18" t="s">
+        <v>230</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10" s="17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="72.75">
       <c r="A11" t="s">
         <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="2">
+        <v>231</v>
+      </c>
+      <c r="C11" s="15">
         <v>8939</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="16">
         <f t="shared" si="0"/>
         <v>3.5980228785793066E-2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="I11" t="s">
         <v>213</v>
       </c>
       <c r="J11" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K11">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="50.25" customHeight="1">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -4242,30 +4298,30 @@
         <v>3.1757915328326128E-2</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F12" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="I12" t="s">
         <v>213</v>
       </c>
       <c r="J12" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="15.95">
       <c r="A13" t="s">
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C13" s="2">
         <v>7765</v>
@@ -4275,27 +4331,27 @@
         <v>3.125477978763655E-2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F13" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="I13" t="s">
         <v>213</v>
       </c>
       <c r="J13" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K13">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="15.95">
       <c r="A14" t="s">
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C14" s="2">
         <v>6895</v>
@@ -4305,30 +4361,30 @@
         <v>2.7752956424437092E-2</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F14" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="I14" t="s">
         <v>213</v>
       </c>
       <c r="J14" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K14">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="15.95">
       <c r="A15" t="s">
         <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C15" s="2">
         <v>6863</v>
@@ -4347,13 +4403,13 @@
         <v>213</v>
       </c>
       <c r="J15" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="32.1">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -4374,18 +4430,18 @@
         <v>213</v>
       </c>
       <c r="J16" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K16">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="15.95">
       <c r="A17" t="s">
         <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C17" s="2">
         <v>2545</v>
@@ -4395,30 +4451,30 @@
         <v>1.0243839608439796E-2</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F17" t="s">
         <v>235</v>
       </c>
-      <c r="F17" t="s">
-        <v>227</v>
-      </c>
       <c r="H17" s="5" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="I17" t="s">
         <v>213</v>
       </c>
       <c r="J17" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K17">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="15.95">
       <c r="A18" t="s">
         <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C18" s="2">
         <v>2394</v>
@@ -4437,18 +4493,18 @@
         <v>213</v>
       </c>
       <c r="J18" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="15.95">
       <c r="A19" t="s">
         <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C19" s="2">
         <v>2267</v>
@@ -4458,27 +4514,27 @@
         <v>9.1248661659461758E-3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F19" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="I19" t="s">
         <v>213</v>
       </c>
       <c r="J19" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K19">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="15.95">
       <c r="A20" t="s">
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C20" s="2">
         <v>2136</v>
@@ -4497,18 +4553,18 @@
         <v>213</v>
       </c>
       <c r="J20" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="15.95">
       <c r="A21" t="s">
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C21" s="2">
         <v>1462</v>
@@ -4527,18 +4583,18 @@
         <v>213</v>
       </c>
       <c r="J21" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="15.95">
       <c r="A22" t="s">
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2">
         <v>1287</v>
@@ -4557,18 +4613,18 @@
         <v>213</v>
       </c>
       <c r="J22" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="15.95">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2">
         <v>1267</v>
@@ -4587,18 +4643,18 @@
         <v>213</v>
       </c>
       <c r="J23" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="15.95">
       <c r="A24" t="s">
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2">
         <v>1209</v>
@@ -4617,18 +4673,18 @@
         <v>213</v>
       </c>
       <c r="J24" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K24">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="15.95">
       <c r="A25" t="s">
         <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2">
         <v>870</v>
@@ -4638,24 +4694,24 @@
         <v>3.5018233631994591E-3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I25" t="s">
         <v>213</v>
       </c>
       <c r="J25" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K25">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="15.95">
       <c r="A26" t="s">
         <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2">
         <v>837</v>
@@ -4674,18 +4730,18 @@
         <v>213</v>
       </c>
       <c r="J26" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="15.95">
       <c r="A27" t="s">
         <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2">
         <v>836</v>
@@ -4695,27 +4751,27 @@
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F27" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="I27" t="s">
         <v>213</v>
       </c>
       <c r="J27" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K27">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="15.95">
       <c r="A28" t="s">
         <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C28" s="2">
         <v>785</v>
@@ -4734,18 +4790,18 @@
         <v>213</v>
       </c>
       <c r="J28" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="15.95">
       <c r="A29" t="s">
         <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2">
         <v>771</v>
@@ -4764,37 +4820,45 @@
         <v>213</v>
       </c>
       <c r="J29" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="8" t="s">
+    <row r="30" spans="1:11" ht="72.75">
+      <c r="A30" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="8"/>
-      <c r="C30" s="9">
+      <c r="B30" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" s="15">
         <v>694</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="16">
         <f t="shared" si="0"/>
         <v>2.793408521908534E-3</v>
       </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
-      <c r="K30" s="8"/>
-    </row>
-    <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="E30" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="I30" t="s">
+        <v>213</v>
+      </c>
+      <c r="K30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="32.1">
       <c r="A31" t="s">
         <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C31" s="2">
         <v>672</v>
@@ -4804,27 +4868,27 @@
         <v>2.7048566667471682E-3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="I31" t="s">
         <v>213</v>
       </c>
       <c r="J31" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="15.95">
       <c r="A32" t="s">
         <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="C32" s="2">
         <v>604</v>
@@ -4834,28 +4898,28 @@
         <v>2.4311509326120384E-3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F32" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" t="s">
         <v>213</v>
       </c>
       <c r="J32" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="15.95">
       <c r="A33" t="s">
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C33" s="2">
         <v>543</v>
@@ -4874,18 +4938,18 @@
         <v>213</v>
       </c>
       <c r="J33" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K33">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="15.95">
       <c r="A34" t="s">
         <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C34" s="2">
         <v>541</v>
@@ -4895,30 +4959,30 @@
         <v>2.1775706201044914E-3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F34" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="H34" s="5" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I34" t="s">
         <v>213</v>
       </c>
       <c r="J34" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="15.95">
       <c r="A35" t="s">
         <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="C35" s="2">
         <v>540</v>
@@ -4928,24 +4992,24 @@
         <v>2.1735455357789744E-3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="I35" t="s">
         <v>213</v>
       </c>
       <c r="J35" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K35">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="15.95">
       <c r="A36" t="s">
         <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C36" s="2">
         <v>527</v>
@@ -4964,18 +5028,18 @@
         <v>213</v>
       </c>
       <c r="J36" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="15.95">
       <c r="A37" t="s">
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C37" s="2">
         <v>502</v>
@@ -4994,18 +5058,18 @@
         <v>213</v>
       </c>
       <c r="J37" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K37">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="15.95">
       <c r="A38" t="s">
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C38" s="2">
         <v>479</v>
@@ -5015,27 +5079,27 @@
         <v>1.9280153919224608E-3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F38" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="I38" t="s">
         <v>213</v>
       </c>
       <c r="J38" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K38">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="15.95">
       <c r="A39" t="s">
         <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C39" s="2">
         <v>454</v>
@@ -5045,27 +5109,27 @@
         <v>1.8273882837845452E-3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F39" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="I39" t="s">
         <v>213</v>
       </c>
       <c r="J39" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K39">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="15.95">
       <c r="A40" t="s">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C40" s="2">
         <v>444</v>
@@ -5078,24 +5142,24 @@
         <v>207</v>
       </c>
       <c r="F40" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="I40" t="s">
         <v>213</v>
       </c>
       <c r="J40" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="15.95">
       <c r="A41" t="s">
         <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="C41" s="2">
         <v>442</v>
@@ -5108,24 +5172,24 @@
         <v>207</v>
       </c>
       <c r="F41" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="I41" t="s">
         <v>213</v>
       </c>
       <c r="J41" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K41">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11">
       <c r="A42" s="8" t="s">
         <v>116</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C42" s="9">
         <v>412</v>
@@ -5139,14 +5203,15 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
+      <c r="J42" s="8"/>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="15.95">
       <c r="A43" t="s">
         <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C43" s="2">
         <v>353</v>
@@ -5156,27 +5221,27 @@
         <v>1.4208547669073666E-3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F43" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="I43" t="s">
         <v>213</v>
       </c>
       <c r="J43" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K43">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="15.95">
       <c r="A44" t="s">
         <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C44" s="2">
         <v>298</v>
@@ -5195,41 +5260,51 @@
         <v>213</v>
       </c>
       <c r="J44" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A45" s="8" t="s">
+    <row r="45" spans="1:11" ht="43.5">
+      <c r="A45" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C45" s="9">
+      <c r="B45" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C45" s="13">
         <v>278</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="14">
         <f t="shared" si="0"/>
         <v>1.1189734424936202E-3</v>
       </c>
-      <c r="E45" s="11"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="8"/>
-      <c r="K45" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+      <c r="E45" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F45" t="s">
+        <v>257</v>
+      </c>
+      <c r="H45" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="I45" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45" t="s">
+        <v>216</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="32.1">
       <c r="A46" t="s">
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C46" s="2">
         <v>228</v>
@@ -5239,30 +5314,30 @@
         <v>9.1771922621778929E-4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F46" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="I46" t="s">
         <v>213</v>
       </c>
       <c r="J46" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="32.1">
       <c r="A47" t="s">
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C47" s="2">
         <v>219</v>
@@ -5272,30 +5347,30 @@
         <v>8.8149346728813973E-4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F47" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="I47" t="s">
         <v>213</v>
       </c>
       <c r="J47" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K47">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="15.95">
       <c r="A48" t="s">
         <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C48" s="2">
         <v>212</v>
@@ -5314,18 +5389,18 @@
         <v>213</v>
       </c>
       <c r="J48" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="15.95">
       <c r="A49" t="s">
         <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="C49" s="2">
         <v>185</v>
@@ -5335,27 +5410,27 @@
         <v>7.446406002205746E-4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F49" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="I49" t="s">
         <v>213</v>
       </c>
       <c r="J49" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="15.95">
       <c r="A50" t="s">
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="C50" s="2">
         <v>183</v>
@@ -5368,21 +5443,21 @@
         <v>207</v>
       </c>
       <c r="F50" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="I50" t="s">
         <v>213</v>
       </c>
       <c r="J50" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11">
       <c r="A51" s="8" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="9">
@@ -5397,14 +5472,15 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="32.1">
       <c r="A52" t="s">
         <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C52" s="2">
         <v>158</v>
@@ -5414,30 +5490,30 @@
         <v>6.3596332343162591E-4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F52" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="I52" t="s">
         <v>213</v>
       </c>
       <c r="J52" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="15.95">
       <c r="A53" t="s">
         <v>132</v>
       </c>
       <c r="B53" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="C53" s="2">
         <v>139</v>
@@ -5447,27 +5523,27 @@
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F53" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="I53" t="s">
         <v>213</v>
       </c>
       <c r="J53" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="15.95">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="C54" s="2">
         <v>138</v>
@@ -5486,18 +5562,18 @@
         <v>213</v>
       </c>
       <c r="J54" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K54">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="15.95">
       <c r="A55" t="s">
         <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="C55" s="2">
         <v>127</v>
@@ -5507,27 +5583,27 @@
         <v>5.1118570934061071E-4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F55" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="I55" t="s">
         <v>213</v>
       </c>
       <c r="J55" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K55">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="15.95">
       <c r="A56" t="s">
         <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="C56" s="2">
         <v>116</v>
@@ -5546,18 +5622,18 @@
         <v>213</v>
       </c>
       <c r="J56" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K56">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="15.95">
       <c r="A57" t="s">
         <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="C57" s="2">
         <v>85</v>
@@ -5567,27 +5643,27 @@
         <v>3.4213216766891265E-4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F57" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="I57" t="s">
         <v>213</v>
       </c>
       <c r="J57" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="15.95">
       <c r="A58" t="s">
         <v>142</v>
       </c>
       <c r="B58" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C58" s="2">
         <v>70</v>
@@ -5600,27 +5676,27 @@
         <v>207</v>
       </c>
       <c r="F58" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="I58" t="s">
         <v>213</v>
       </c>
       <c r="J58" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K58">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" ht="32.1">
       <c r="A59" t="s">
         <v>144</v>
       </c>
       <c r="B59" t="s">
-        <v>266</v>
+        <v>225</v>
       </c>
       <c r="C59" s="2">
         <v>67</v>
@@ -5630,30 +5706,30 @@
         <v>2.6968064980961351E-4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F59" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="I59" t="s">
         <v>213</v>
       </c>
       <c r="J59" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="32.1">
       <c r="A60" t="s">
         <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C60" s="2">
         <v>58</v>
@@ -5663,27 +5739,27 @@
         <v>2.3345489087996395E-4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="I60" t="s">
         <v>213</v>
       </c>
       <c r="J60" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K60">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="15.95">
       <c r="A61" t="s">
         <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C61" s="2">
         <v>37</v>
@@ -5696,24 +5772,24 @@
         <v>207</v>
       </c>
       <c r="F61" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="I61" t="s">
         <v>213</v>
       </c>
       <c r="J61" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K61">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="15.95">
       <c r="A62" t="s">
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C62" s="2">
         <v>34</v>
@@ -5726,19 +5802,19 @@
         <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="I62" t="s">
         <v>213</v>
       </c>
       <c r="J62" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K62">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="15.95">
       <c r="A63" t="s">
         <v>57</v>
       </c>
@@ -5753,24 +5829,24 @@
         <v>207</v>
       </c>
       <c r="H63" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="I63" t="s">
         <v>213</v>
       </c>
       <c r="J63" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K63">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="15.95">
       <c r="A64" t="s">
         <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C64" s="2">
         <v>31</v>
@@ -5780,27 +5856,27 @@
         <v>1.247776140910152E-4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F64" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="I64" t="s">
         <v>213</v>
       </c>
       <c r="J64" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K64">
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="63.95">
       <c r="A65" t="s">
         <v>98</v>
       </c>
       <c r="B65" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C65" s="2">
         <v>27</v>
@@ -5813,24 +5889,24 @@
         <v>207</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="I65" t="s">
         <v>213</v>
       </c>
       <c r="J65" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K65">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="15.95">
       <c r="A66" t="s">
         <v>59</v>
       </c>
       <c r="B66" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C66" s="2">
         <v>27</v>
@@ -5843,19 +5919,19 @@
         <v>207</v>
       </c>
       <c r="H66" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="I66" t="s">
         <v>213</v>
       </c>
       <c r="J66" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K66">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" ht="48">
       <c r="A67" t="s">
         <v>166</v>
       </c>
@@ -5873,27 +5949,27 @@
         <v>207</v>
       </c>
       <c r="F67" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="I67" t="s">
         <v>213</v>
       </c>
       <c r="J67" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K67">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" ht="15.95">
       <c r="A68" t="s">
         <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C68" s="2">
         <v>13</v>
@@ -5906,24 +5982,24 @@
         <v>207</v>
       </c>
       <c r="F68" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="I68" t="s">
         <v>213</v>
       </c>
       <c r="J68" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K68">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" ht="63.95">
       <c r="A69" t="s">
         <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C69" s="2">
         <v>8</v>
@@ -5933,27 +6009,27 @@
         <v>3.2200674604132955E-5</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="I69" t="s">
         <v>213</v>
       </c>
       <c r="J69" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K69">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" ht="15.95">
       <c r="A70" t="s">
         <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C70" s="2">
         <v>5</v>
@@ -5966,27 +6042,27 @@
         <v>207</v>
       </c>
       <c r="F70" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H70" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="I70" t="s">
         <v>213</v>
       </c>
       <c r="J70" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="15.95">
       <c r="A71" t="s">
         <v>95</v>
       </c>
       <c r="B71" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C71" s="2">
         <v>4</v>
@@ -5999,48 +6075,57 @@
         <v>207</v>
       </c>
       <c r="F71" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="H71" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="I71" t="s">
         <v>213</v>
       </c>
       <c r="J71" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A72" s="8" t="s">
+    <row r="72" spans="1:11">
+      <c r="A72" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B72" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="C72" s="9">
+      <c r="B72" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C72" s="13">
         <v>4</v>
       </c>
-      <c r="D72" s="10">
+      <c r="D72" s="14">
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
-      <c r="E72" s="11"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="8"/>
-      <c r="K72" s="8"/>
-    </row>
-    <row r="73" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+      <c r="E72" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F72" t="s">
+        <v>261</v>
+      </c>
+      <c r="I72" t="s">
+        <v>213</v>
+      </c>
+      <c r="J72" t="s">
+        <v>216</v>
+      </c>
+      <c r="K72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="63.95">
       <c r="A73" t="s">
         <v>129</v>
       </c>
       <c r="B73" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C73" s="2">
         <v>2</v>
@@ -6053,24 +6138,24 @@
         <v>207</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="I73" t="s">
         <v>213</v>
       </c>
       <c r="J73" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="K73">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11">
       <c r="A74" t="s">
         <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
@@ -6086,21 +6171,24 @@
         <v>215</v>
       </c>
       <c r="H74" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I74" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J74" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="K74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
       <c r="A75" t="s">
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -6113,21 +6201,24 @@
         <v>207</v>
       </c>
       <c r="H75" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I75" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J75" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+      <c r="K75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
       <c r="A76" t="s">
         <v>127</v>
       </c>
       <c r="B76" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -6143,21 +6234,24 @@
         <v>215</v>
       </c>
       <c r="H76" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I76" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J76" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
       <c r="A77" t="s">
         <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -6170,21 +6264,24 @@
         <v>207</v>
       </c>
       <c r="H77" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I77" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J77" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="K77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
       <c r="A78" t="s">
         <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -6200,21 +6297,24 @@
         <v>215</v>
       </c>
       <c r="H78" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I78" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J78" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
       <c r="A79" t="s">
         <v>176</v>
       </c>
       <c r="B79" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -6224,27 +6324,30 @@
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>274</v>
+        <v>226</v>
       </c>
       <c r="F79" t="s">
         <v>215</v>
       </c>
       <c r="H79" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I79" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J79" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
       <c r="A80" t="s">
         <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -6254,24 +6357,27 @@
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="H80" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="I80" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J80" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="K80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
       <c r="A81" t="s">
         <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -6287,21 +6393,24 @@
         <v>215</v>
       </c>
       <c r="H81" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I81" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J81" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
       <c r="A82" t="s">
         <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -6317,21 +6426,24 @@
         <v>215</v>
       </c>
       <c r="H82" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="I82" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J82" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
       <c r="A83" t="s">
         <v>153</v>
       </c>
       <c r="B83" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -6344,13 +6456,16 @@
         <v>207</v>
       </c>
       <c r="H83" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="I83" t="s">
-        <v>276</v>
+        <v>216</v>
       </c>
       <c r="J83" t="s">
-        <v>276</v>
+        <v>213</v>
+      </c>
+      <c r="K83">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9903CEB-E247-5843-AB42-7F769ED81C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{904275DD-0B53-BA45-80E9-849742C25332}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -884,11 +884,11 @@
     <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
   </si>
   <si>
+    <t>Positive / Negative / Neutral</t>
+  </si>
+  <si>
     <t>If EP name = 'Closed Queue Menu Telephony EP', then Negative, and type = "Closed queue",
-otherwise Positive, type = 'Reached voicemail', if EP name = 'Closed Hours-Holidays Menu Telephony EP' then neutral, and type = 'After hours call</t>
-  </si>
-  <si>
-    <t>Positive / Negative / Neutral</t>
+otherwise Positive, type = 'Reached voicemail', if EP name = 'Closed Hours-Holidays Menu Telephony EP' then neutral, and type = 'After hours call'</t>
   </si>
 </sst>
 </file>
@@ -4046,10 +4046,10 @@
         <v>0.10352919393661297</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>280</v>
       </c>
       <c r="I5" t="s">
         <v>209</v>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{584E58ED-953E-46FD-9EA9-69225F98A99D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD96ECA9-4CD7-0544-9753-3CC6E3DA31DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -34,7 +34,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -714,200 +713,200 @@
     <t>Neutral / Negative</t>
   </si>
   <si>
+    <t>Legal Menu</t>
+  </si>
+  <si>
+    <t>Farmworker Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative </t>
+  </si>
+  <si>
+    <t>Abandoned (tenative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on info from Mark, this reflects no activity at Farmworker Menu and cannot progress without a selection; either call disconnects after max number of repetitions or the caller hangs up; max step counter is unknown so believe calls should be considered abandoned </t>
+  </si>
+  <si>
+    <t>N/A - Ad Hoc Outbound Call</t>
+  </si>
+  <si>
+    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up</t>
+  </si>
+  <si>
+    <t>Courtesy Callback, Queues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive / neutral (tenative) </t>
+  </si>
+  <si>
+    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect  to customer; uncertainty b/c there are not activity names that indicate connection in the data</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front Desk </t>
+  </si>
+  <si>
+    <t>No input for language selection;</t>
+  </si>
+  <si>
+    <t>Holiday &amp; Closed Menu</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Appointment Menu</t>
+  </si>
+  <si>
+    <t>Caller has an appointment scheduled</t>
+  </si>
+  <si>
+    <t>Other Legal Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive </t>
+  </si>
+  <si>
+    <t>Caller requests an interpreter</t>
+  </si>
+  <si>
+    <t>Housing menu</t>
+  </si>
+  <si>
+    <t>Voicemail Transfer</t>
+  </si>
+  <si>
+    <t>Family menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queues </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal Menu </t>
+  </si>
+  <si>
+    <t>Pre-legal seniors menu</t>
+  </si>
+  <si>
+    <t>HIV Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive / Neutral (tenative) </t>
+  </si>
+  <si>
+    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect; uncertainty b/c there are not activity names that indicate connection in the data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Menu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive (tenative) </t>
+  </si>
+  <si>
+    <t>Caller listens to message; no option given to return to previous menus</t>
+  </si>
+  <si>
+    <t>Issue not handled by LAC</t>
+  </si>
+  <si>
+    <t>No input</t>
+  </si>
+  <si>
+    <t>Immigration menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abandoned </t>
+  </si>
+  <si>
+    <t>Family Menu</t>
+  </si>
+  <si>
+    <t>Benefits Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral </t>
+  </si>
+  <si>
+    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
+  </si>
+  <si>
+    <t>Caller is non-Cook County Senior and did not make a selection after message</t>
+  </si>
+  <si>
+    <t>Queues</t>
+  </si>
+  <si>
+    <t>Employment menu</t>
+  </si>
+  <si>
+    <t>No activity</t>
+  </si>
+  <si>
+    <t>Caller selected Other Legal option (8) in Suburban Seniors Menu</t>
+  </si>
+  <si>
+    <t>Immigration Menu</t>
+  </si>
+  <si>
+    <t>Voice Mail Transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed </t>
+  </si>
+  <si>
+    <t>Unsuccessful Courtesy Callback</t>
+  </si>
+  <si>
+    <t>No Agent Name for attempted courtesy callback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assuming this corresponds to Farm Worker Voicemail transfer on flow charts </t>
+  </si>
+  <si>
+    <t>Verbiage tells callers that they can leave comments online</t>
+  </si>
+  <si>
+    <t>Outbound call failed to connect; system error</t>
+  </si>
+  <si>
+    <t>Employment Menu</t>
+  </si>
+  <si>
+    <t>Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
+  </si>
+  <si>
+    <t>System failure in courtesy callback attempt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caller hangs up before being connected with an agent, system tries to progress but gives error since there's no caller </t>
+  </si>
+  <si>
+    <t>Caller did not finish confirming callback</t>
+  </si>
+  <si>
+    <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
+  </si>
+  <si>
+    <t>Should check if agents are logged into queue, if last activity then caller never entered the queue (never heard pre-queue message1), customer may have ended call after waiting</t>
+  </si>
+  <si>
+    <t>VIvi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Play Courtesy CallBack Confirmation" . This is typically played right before the contact is disconnected from the system. The consumer selected a courtesy callback but hung up before the system could disconnect so this is neutral. </t>
+  </si>
+  <si>
     <t>If EP name = Closed Hours-Holidays Menu Telephony EP	, then Neutral, type = "After hours call"
-If EP name = Closed Queue Menu Telephony EP, then Negative, type = "Closed Queue"</t>
-  </si>
-  <si>
-    <t>Legal Menu</t>
-  </si>
-  <si>
-    <t>Farmworker Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative </t>
-  </si>
-  <si>
-    <t>Abandoned (tenative)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on info from Mark, this reflects no activity at Farmworker Menu and cannot progress without a selection; either call disconnects after max number of repetitions or the caller hangs up; max step counter is unknown so believe calls should be considered abandoned </t>
-  </si>
-  <si>
-    <t>N/A - Ad Hoc Outbound Call</t>
-  </si>
-  <si>
-    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up</t>
-  </si>
-  <si>
-    <t>Courtesy Callback, Queues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive / neutral (tenative) </t>
-  </si>
-  <si>
-    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect  to customer; uncertainty b/c there are not activity names that indicate connection in the data</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front Desk </t>
-  </si>
-  <si>
-    <t>No input for language selection;</t>
-  </si>
-  <si>
-    <t>Holiday &amp; Closed Menu</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>Appointment Menu</t>
-  </si>
-  <si>
-    <t>Caller has an appointment scheduled</t>
-  </si>
-  <si>
-    <t>Other Legal Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive </t>
-  </si>
-  <si>
-    <t>Caller requests an interpreter</t>
-  </si>
-  <si>
-    <t>Housing menu</t>
-  </si>
-  <si>
-    <t>Voicemail Transfer</t>
-  </si>
-  <si>
-    <t>Family menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queues </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal Menu </t>
-  </si>
-  <si>
-    <t>Pre-legal seniors menu</t>
-  </si>
-  <si>
-    <t>HIV Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive / Neutral (tenative) </t>
-  </si>
-  <si>
-    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect; uncertainty b/c there are not activity names that indicate connection in the data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Menu </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive (tenative) </t>
-  </si>
-  <si>
-    <t>Caller listens to message; no option given to return to previous menus</t>
-  </si>
-  <si>
-    <t>Issue not handled by LAC</t>
-  </si>
-  <si>
-    <t>No input</t>
-  </si>
-  <si>
-    <t>Immigration menu</t>
-  </si>
-  <si>
-    <t>Pre-Legal Seniors Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abandoned </t>
-  </si>
-  <si>
-    <t>Family Menu</t>
-  </si>
-  <si>
-    <t>Benefits Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neutral </t>
-  </si>
-  <si>
-    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
-  </si>
-  <si>
-    <t>Caller is non-Cook County Senior and did not make a selection after message</t>
-  </si>
-  <si>
-    <t>Queues</t>
-  </si>
-  <si>
-    <t>Employment menu</t>
-  </si>
-  <si>
-    <t>No activity</t>
-  </si>
-  <si>
-    <t>Caller selected Other Legal option (8) in Suburban Seniors Menu</t>
-  </si>
-  <si>
-    <t>Immigration Menu</t>
-  </si>
-  <si>
-    <t>Voice Mail Transfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed </t>
-  </si>
-  <si>
-    <t>Unsuccessful Courtesy Callback</t>
-  </si>
-  <si>
-    <t>No Agent Name for attempted courtesy callback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assuming this corresponds to Farm Worker Voicemail transfer on flow charts </t>
-  </si>
-  <si>
-    <t>Verbiage tells callers that they can leave comments online</t>
-  </si>
-  <si>
-    <t>Outbound call failed to connect; system error</t>
-  </si>
-  <si>
-    <t>Employment Menu</t>
-  </si>
-  <si>
-    <t>Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
-  </si>
-  <si>
-    <t>System failure in courtesy callback attempt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caller hangs up before being connected with an agent, system tries to progress but gives error since there's no caller </t>
-  </si>
-  <si>
-    <t>Caller did not finish confirming callback</t>
-  </si>
-  <si>
-    <t>customer made it to a queue but was never connected with an agent or scheduled a callback. Likely that customer abandoned the call after waiting.</t>
-  </si>
-  <si>
-    <t>Should check if agents are logged into queue, if last activity then caller never entered the queue (never heard pre-queue message1), customer may have ended call after waiting</t>
-  </si>
-  <si>
-    <t>VIvi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">"Play Courtesy CallBack Confirmation" . This is typically played right before the contact is disconnected from the system. The consumer selected a courtesy callback but hung up before the system could disconnect so this is neutral. </t>
+If EP name = Closed Queue Menu Telephony EP, then Negative, type = "Closed Queue", if EP Name = "Pre-Legal Menu Seniors Menu Telephony EP", then neutral, type = "issue not handled by LAC"</t>
   </si>
 </sst>
 </file>
@@ -918,7 +917,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -991,7 +990,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1017,10 +1016,6 @@
     <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1358,13 +1353,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1372,7 +1367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1380,7 +1375,7 @@
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1388,7 +1383,7 @@
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1396,7 +1391,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1404,7 +1399,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1412,7 +1407,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1420,7 +1415,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1428,7 +1423,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1436,7 +1431,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1444,7 +1439,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1452,7 +1447,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1460,7 +1455,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1468,7 +1463,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1476,7 +1471,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1484,7 +1479,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1492,7 +1487,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1500,7 +1495,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1508,7 +1503,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1516,7 +1511,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1524,7 +1519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1532,7 +1527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1540,7 +1535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1548,7 +1543,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1556,7 +1551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1564,7 +1559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1572,7 +1567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1588,17 +1583,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="32.1">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1612,7 +1607,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1626,7 +1621,7 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1640,7 +1635,7 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1654,7 +1649,7 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1668,7 +1663,7 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1682,7 +1677,7 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1696,7 +1691,7 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1710,7 +1705,7 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1724,7 +1719,7 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1738,7 +1733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1752,7 +1747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1766,7 +1761,7 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1780,7 +1775,7 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1794,7 +1789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1808,7 +1803,7 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1822,7 +1817,7 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1836,7 +1831,7 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1850,7 +1845,7 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1864,7 +1859,7 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1878,7 +1873,7 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1892,7 +1887,7 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1906,7 +1901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1920,7 +1915,7 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1934,7 +1929,7 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1948,7 +1943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1962,7 +1957,7 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1976,7 +1971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -1990,7 +1985,7 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2004,7 +1999,7 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -2018,7 +2013,7 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2032,7 +2027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -2046,7 +2041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -2060,7 +2055,7 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -2074,7 +2069,7 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2088,7 +2083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2102,7 +2097,7 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -2116,7 +2111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -2130,7 +2125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -2144,7 +2139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2158,7 +2153,7 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2172,7 +2167,7 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -2186,7 +2181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2200,7 +2195,7 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2214,7 +2209,7 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2228,7 +2223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -2242,7 +2237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2256,7 +2251,7 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2270,7 +2265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -2284,7 +2279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -2298,7 +2293,7 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -2312,7 +2307,7 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -2326,7 +2321,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2340,7 +2335,7 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -2354,7 +2349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2368,7 +2363,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -2382,7 +2377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -2396,7 +2391,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2410,7 +2405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -2424,7 +2419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2438,7 +2433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2452,7 +2447,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -2466,7 +2461,7 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -2480,7 +2475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -2494,7 +2489,7 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -2508,7 +2503,7 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -2522,7 +2517,7 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2536,7 +2531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -2550,7 +2545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>99</v>
       </c>
@@ -2564,7 +2559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -2578,7 +2573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -2592,7 +2587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -2606,7 +2601,7 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -2620,7 +2615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -2634,7 +2629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -2648,7 +2643,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -2662,7 +2657,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -2676,7 +2671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -2690,7 +2685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -2704,7 +2699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -2718,7 +2713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>111</v>
       </c>
@@ -2732,7 +2727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -2746,7 +2741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -2760,7 +2755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>114</v>
       </c>
@@ -2774,7 +2769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -2788,7 +2783,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -2802,7 +2797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -2816,7 +2811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -2830,7 +2825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>119</v>
       </c>
@@ -2844,7 +2839,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -2858,7 +2853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -2872,7 +2867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -2886,7 +2881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -2900,7 +2895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -2914,7 +2909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -2928,7 +2923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -2942,7 +2937,7 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -2956,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -2970,7 +2965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -2984,7 +2979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -2998,7 +2993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -3012,7 +3007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -3026,7 +3021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -3040,7 +3035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -3054,7 +3049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -3068,7 +3063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -3082,7 +3077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -3096,7 +3091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -3110,7 +3105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3124,7 +3119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -3138,7 +3133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>141</v>
       </c>
@@ -3152,7 +3147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>142</v>
       </c>
@@ -3166,7 +3161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>143</v>
       </c>
@@ -3180,7 +3175,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>144</v>
       </c>
@@ -3194,7 +3189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>145</v>
       </c>
@@ -3208,7 +3203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3222,7 +3217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>147</v>
       </c>
@@ -3236,7 +3231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -3250,7 +3245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>149</v>
       </c>
@@ -3264,7 +3259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>150</v>
       </c>
@@ -3278,7 +3273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>151</v>
       </c>
@@ -3292,7 +3287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>152</v>
       </c>
@@ -3306,7 +3301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -3320,7 +3315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -3334,7 +3329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>155</v>
       </c>
@@ -3348,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>156</v>
       </c>
@@ -3362,7 +3357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>157</v>
       </c>
@@ -3376,7 +3371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>158</v>
       </c>
@@ -3390,7 +3385,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>159</v>
       </c>
@@ -3404,7 +3399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -3418,7 +3413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>161</v>
       </c>
@@ -3432,7 +3427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -3446,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -3460,7 +3455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -3474,7 +3469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -3488,7 +3483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -3502,7 +3497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -3516,7 +3511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -3530,7 +3525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -3544,7 +3539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -3558,7 +3553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -3572,7 +3567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -3586,7 +3581,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -3600,7 +3595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -3614,7 +3609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -3628,7 +3623,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>176</v>
       </c>
@@ -3642,7 +3637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>177</v>
       </c>
@@ -3656,7 +3651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>178</v>
       </c>
@@ -3670,7 +3665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -3684,7 +3679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>180</v>
       </c>
@@ -3698,7 +3693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>181</v>
       </c>
@@ -3712,7 +3707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -3726,7 +3721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>183</v>
       </c>
@@ -3740,7 +3735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>184</v>
       </c>
@@ -3754,7 +3749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>185</v>
       </c>
@@ -3768,7 +3763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>186</v>
       </c>
@@ -3782,7 +3777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -3796,7 +3791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -3810,7 +3805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -3824,7 +3819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -3838,7 +3833,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -3852,7 +3847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -3866,7 +3861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -3880,7 +3875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>194</v>
       </c>
@@ -3894,7 +3889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>195</v>
       </c>
@@ -3928,19 +3923,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.5" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="48">
+    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>196</v>
       </c>
@@ -3975,7 +3970,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="63.95">
+    <row r="2" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>37</v>
       </c>
@@ -4005,7 +4000,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="32.1">
+    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -4035,7 +4030,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="32.1">
+    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -4065,7 +4060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="80.099999999999994">
+    <row r="5" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>41</v>
       </c>
@@ -4095,7 +4090,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15.95">
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -4125,7 +4120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="63.95">
+    <row r="7" spans="1:11" ht="96" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -4143,7 +4138,7 @@
         <v>222</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>223</v>
+        <v>287</v>
       </c>
       <c r="I7" t="s">
         <v>209</v>
@@ -4155,12 +4150,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.95">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C8" s="2">
         <v>11987</v>
@@ -4185,12 +4180,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="87">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>225</v>
+      <c r="B9" t="s">
+        <v>224</v>
       </c>
       <c r="C9" s="15">
         <v>9640</v>
@@ -4199,34 +4194,34 @@
         <f t="shared" si="0"/>
         <v>3.8801812897980216E-2</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9" t="s">
         <v>226</v>
       </c>
-      <c r="F9" s="17" t="s">
+      <c r="G9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="G9" s="17" t="s">
-        <v>212</v>
-      </c>
-      <c r="H9" s="18" t="s">
+      <c r="I9" t="s">
+        <v>209</v>
+      </c>
+      <c r="J9" t="s">
+        <v>213</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
         <v>228</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="62.25" customHeight="1">
-      <c r="A10" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>229</v>
       </c>
       <c r="C10" s="15">
         <v>9358</v>
@@ -4235,30 +4230,28 @@
         <f t="shared" si="0"/>
         <v>3.7666739118184529E-2</v>
       </c>
-      <c r="E10" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>216</v>
-      </c>
-      <c r="K10" s="17">
+      <c r="E10" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="I10" t="s">
+        <v>213</v>
+      </c>
+      <c r="J10" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="72.75">
+    <row r="11" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>56</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C11" s="15">
         <v>8939</v>
@@ -4268,10 +4261,10 @@
         <v>3.5980228785793066E-2</v>
       </c>
       <c r="E11" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>232</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>233</v>
       </c>
       <c r="I11" t="s">
         <v>213</v>
@@ -4283,7 +4276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="50.25" customHeight="1">
+    <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>65</v>
       </c>
@@ -4298,13 +4291,13 @@
         <v>3.1757915328326128E-2</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" t="s">
         <v>234</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="I12" t="s">
         <v>213</v>
@@ -4316,12 +4309,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15.95">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C13" s="2">
         <v>7765</v>
@@ -4331,10 +4324,10 @@
         <v>3.125477978763655E-2</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" t="s">
         <v>238</v>
-      </c>
-      <c r="F13" t="s">
-        <v>239</v>
       </c>
       <c r="I13" t="s">
         <v>213</v>
@@ -4346,12 +4339,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="15.95">
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C14" s="2">
         <v>6895</v>
@@ -4361,13 +4354,13 @@
         <v>2.7752956424437092E-2</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F14" t="s">
         <v>234</v>
       </c>
-      <c r="F14" t="s">
-        <v>235</v>
-      </c>
       <c r="H14" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I14" t="s">
         <v>213</v>
@@ -4379,12 +4372,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.95">
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C15" s="2">
         <v>6863</v>
@@ -4409,7 +4402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="32.1">
+    <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -4436,12 +4429,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.95">
+    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>76</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C17" s="2">
         <v>2545</v>
@@ -4451,13 +4444,13 @@
         <v>1.0243839608439796E-2</v>
       </c>
       <c r="E17" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F17" t="s">
+        <v>234</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="F17" t="s">
-        <v>235</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>244</v>
       </c>
       <c r="I17" t="s">
         <v>213</v>
@@ -4469,12 +4462,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.95">
+    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>50</v>
       </c>
       <c r="B18" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C18" s="2">
         <v>2394</v>
@@ -4499,12 +4492,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.95">
+    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2">
         <v>2267</v>
@@ -4514,10 +4507,10 @@
         <v>9.1248661659461758E-3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I19" t="s">
         <v>213</v>
@@ -4529,12 +4522,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.95">
+    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C20" s="2">
         <v>2136</v>
@@ -4559,12 +4552,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.95">
+    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>53</v>
       </c>
       <c r="B21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C21" s="2">
         <v>1462</v>
@@ -4589,12 +4582,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.95">
+    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2">
         <v>1287</v>
@@ -4619,12 +4612,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.95">
+    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2">
         <v>1267</v>
@@ -4649,12 +4642,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.95">
+    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C24" s="2">
         <v>1209</v>
@@ -4679,12 +4672,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.95">
+    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>71</v>
       </c>
       <c r="B25" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2">
         <v>870</v>
@@ -4694,7 +4687,7 @@
         <v>3.5018233631994591E-3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I25" t="s">
         <v>213</v>
@@ -4706,12 +4699,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.95">
+    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2">
         <v>837</v>
@@ -4736,12 +4729,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.95">
+    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2">
         <v>836</v>
@@ -4751,10 +4744,10 @@
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I27" t="s">
         <v>213</v>
@@ -4766,12 +4759,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.95">
+    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C28" s="2">
         <v>785</v>
@@ -4796,12 +4789,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.95">
+    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>82</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2">
         <v>771</v>
@@ -4826,12 +4819,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="72.75">
+    <row r="30" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C30" s="15">
         <v>694</v>
@@ -4841,10 +4834,10 @@
         <v>2.793408521908534E-3</v>
       </c>
       <c r="E30" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="H30" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="I30" t="s">
         <v>213</v>
@@ -4853,12 +4846,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="32.1">
+    <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C31" s="2">
         <v>672</v>
@@ -4868,10 +4861,10 @@
         <v>2.7048566667471682E-3</v>
       </c>
       <c r="E31" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="I31" t="s">
         <v>213</v>
@@ -4883,12 +4876,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.95">
+    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C32" s="2">
         <v>604</v>
@@ -4898,10 +4891,10 @@
         <v>2.4311509326120384E-3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F32" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H32" s="5"/>
       <c r="I32" t="s">
@@ -4914,12 +4907,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15.95">
+    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>42</v>
       </c>
       <c r="B33" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C33" s="2">
         <v>543</v>
@@ -4944,7 +4937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="15.95">
+    <row r="34" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>110</v>
       </c>
@@ -4959,13 +4952,13 @@
         <v>2.1775706201044914E-3</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F34" t="s">
         <v>234</v>
       </c>
-      <c r="F34" t="s">
-        <v>235</v>
-      </c>
       <c r="H34" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I34" t="s">
         <v>213</v>
@@ -4977,12 +4970,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="15.95">
+    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>80</v>
       </c>
       <c r="B35" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C35" s="2">
         <v>540</v>
@@ -4992,7 +4985,7 @@
         <v>2.1735455357789744E-3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I35" t="s">
         <v>213</v>
@@ -5004,12 +4997,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="15.95">
+    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>73</v>
       </c>
       <c r="B36" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C36" s="2">
         <v>527</v>
@@ -5034,12 +5027,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.95">
+    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>46</v>
       </c>
       <c r="B37" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C37" s="2">
         <v>502</v>
@@ -5064,12 +5057,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15.95">
+    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>83</v>
       </c>
       <c r="B38" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C38" s="2">
         <v>479</v>
@@ -5079,10 +5072,10 @@
         <v>1.9280153919224608E-3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I38" t="s">
         <v>213</v>
@@ -5094,12 +5087,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15.95">
+    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C39" s="2">
         <v>454</v>
@@ -5109,10 +5102,10 @@
         <v>1.8273882837845452E-3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I39" t="s">
         <v>213</v>
@@ -5124,12 +5117,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15.95">
+    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2">
         <v>444</v>
@@ -5142,7 +5135,7 @@
         <v>207</v>
       </c>
       <c r="F40" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I40" t="s">
         <v>213</v>
@@ -5154,12 +5147,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15.95">
+    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>64</v>
       </c>
       <c r="B41" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C41" s="2">
         <v>442</v>
@@ -5172,7 +5165,7 @@
         <v>207</v>
       </c>
       <c r="F41" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I41" t="s">
         <v>213</v>
@@ -5184,12 +5177,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>116</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C42" s="9">
         <v>412</v>
@@ -5206,12 +5199,12 @@
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" ht="15.95">
+    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>77</v>
       </c>
       <c r="B43" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C43" s="2">
         <v>353</v>
@@ -5221,10 +5214,10 @@
         <v>1.4208547669073666E-3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F43" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I43" t="s">
         <v>213</v>
@@ -5236,12 +5229,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="15.95">
+    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C44" s="2">
         <v>298</v>
@@ -5266,12 +5259,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="43.5">
+    <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>69</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C45" s="13">
         <v>278</v>
@@ -5281,13 +5274,13 @@
         <v>1.1189734424936202E-3</v>
       </c>
       <c r="E45" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F45" t="s">
+        <v>256</v>
+      </c>
+      <c r="H45" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="F45" t="s">
-        <v>257</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="I45" t="s">
         <v>213</v>
@@ -5299,12 +5292,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="32.1">
+    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>105</v>
       </c>
       <c r="B46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C46" s="2">
         <v>228</v>
@@ -5314,13 +5307,13 @@
         <v>9.1771922621778929E-4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F46" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I46" t="s">
         <v>213</v>
@@ -5332,12 +5325,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="32.1">
+    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C47" s="2">
         <v>219</v>
@@ -5347,13 +5340,13 @@
         <v>8.8149346728813973E-4</v>
       </c>
       <c r="E47" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F47" t="s">
+        <v>256</v>
+      </c>
+      <c r="H47" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="F47" t="s">
-        <v>257</v>
-      </c>
-      <c r="H47" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="I47" t="s">
         <v>213</v>
@@ -5365,12 +5358,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15.95">
+    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C48" s="2">
         <v>212</v>
@@ -5395,12 +5388,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15.95">
+    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>124</v>
       </c>
       <c r="B49" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C49" s="2">
         <v>185</v>
@@ -5410,10 +5403,10 @@
         <v>7.446406002205746E-4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F49" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I49" t="s">
         <v>213</v>
@@ -5425,12 +5418,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15.95">
+    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>70</v>
       </c>
       <c r="B50" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C50" s="2">
         <v>183</v>
@@ -5443,7 +5436,7 @@
         <v>207</v>
       </c>
       <c r="F50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I50" t="s">
         <v>213</v>
@@ -5455,9 +5448,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="9">
@@ -5475,12 +5468,12 @@
       <c r="J51" s="8"/>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="32.1">
+    <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C52" s="2">
         <v>158</v>
@@ -5490,13 +5483,13 @@
         <v>6.3596332343162591E-4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I52" t="s">
         <v>213</v>
@@ -5508,12 +5501,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15.95">
+    <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>132</v>
       </c>
       <c r="B53" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C53" s="2">
         <v>139</v>
@@ -5523,10 +5516,10 @@
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F53" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I53" t="s">
         <v>213</v>
@@ -5538,12 +5531,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15.95">
+    <row r="54" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C54" s="2">
         <v>138</v>
@@ -5568,12 +5561,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="15.95">
+    <row r="55" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>89</v>
       </c>
       <c r="B55" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C55" s="2">
         <v>127</v>
@@ -5583,10 +5576,10 @@
         <v>5.1118570934061071E-4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F55" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I55" t="s">
         <v>213</v>
@@ -5598,12 +5591,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="15.95">
+    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>96</v>
       </c>
       <c r="B56" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C56" s="2">
         <v>116</v>
@@ -5628,12 +5621,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="15.95">
+    <row r="57" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C57" s="2">
         <v>85</v>
@@ -5643,10 +5636,10 @@
         <v>3.4213216766891265E-4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F57" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I57" t="s">
         <v>213</v>
@@ -5658,7 +5651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="15.95">
+    <row r="58" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>142</v>
       </c>
@@ -5676,10 +5669,10 @@
         <v>207</v>
       </c>
       <c r="F58" t="s">
+        <v>273</v>
+      </c>
+      <c r="H58" s="5" t="s">
         <v>274</v>
-      </c>
-      <c r="H58" s="5" t="s">
-        <v>275</v>
       </c>
       <c r="I58" t="s">
         <v>213</v>
@@ -5691,12 +5684,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="32.1">
+    <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>144</v>
       </c>
       <c r="B59" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C59" s="2">
         <v>67</v>
@@ -5706,13 +5699,13 @@
         <v>2.6968064980961351E-4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F59" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I59" t="s">
         <v>213</v>
@@ -5724,12 +5717,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="32.1">
+    <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C60" s="2">
         <v>58</v>
@@ -5739,10 +5732,10 @@
         <v>2.3345489087996395E-4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H60" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I60" t="s">
         <v>213</v>
@@ -5754,12 +5747,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="15.95">
+    <row r="61" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>52</v>
       </c>
       <c r="B61" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C61" s="2">
         <v>37</v>
@@ -5772,7 +5765,7 @@
         <v>207</v>
       </c>
       <c r="F61" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I61" t="s">
         <v>213</v>
@@ -5784,12 +5777,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="15.95">
+    <row r="62" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>51</v>
       </c>
       <c r="B62" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C62" s="2">
         <v>34</v>
@@ -5802,7 +5795,7 @@
         <v>207</v>
       </c>
       <c r="F62" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I62" t="s">
         <v>213</v>
@@ -5814,7 +5807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="15.95">
+    <row r="63" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>57</v>
       </c>
@@ -5829,7 +5822,7 @@
         <v>207</v>
       </c>
       <c r="H63" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I63" t="s">
         <v>213</v>
@@ -5841,12 +5834,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="15.95">
+    <row r="64" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>126</v>
       </c>
       <c r="B64" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C64" s="2">
         <v>31</v>
@@ -5856,10 +5849,10 @@
         <v>1.247776140910152E-4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F64" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I64" t="s">
         <v>213</v>
@@ -5871,12 +5864,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="63.95">
+    <row r="65" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>98</v>
       </c>
       <c r="B65" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C65" s="2">
         <v>27</v>
@@ -5889,7 +5882,7 @@
         <v>207</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I65" t="s">
         <v>213</v>
@@ -5901,7 +5894,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="15.95">
+    <row r="66" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -5919,7 +5912,7 @@
         <v>207</v>
       </c>
       <c r="H66" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I66" t="s">
         <v>213</v>
@@ -5931,7 +5924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="48">
+    <row r="67" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>166</v>
       </c>
@@ -5949,10 +5942,10 @@
         <v>207</v>
       </c>
       <c r="F67" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H67" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I67" t="s">
         <v>213</v>
@@ -5964,7 +5957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="15.95">
+    <row r="68" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>87</v>
       </c>
@@ -5982,7 +5975,7 @@
         <v>207</v>
       </c>
       <c r="F68" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I68" t="s">
         <v>213</v>
@@ -5994,12 +5987,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="63.95">
+    <row r="69" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C69" s="2">
         <v>8</v>
@@ -6009,10 +6002,10 @@
         <v>3.2200674604132955E-5</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H69" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I69" t="s">
         <v>213</v>
@@ -6024,7 +6017,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="15.95">
+    <row r="70" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>94</v>
       </c>
@@ -6042,10 +6035,10 @@
         <v>207</v>
       </c>
       <c r="F70" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H70" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I70" t="s">
         <v>213</v>
@@ -6057,7 +6050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="15.95">
+    <row r="71" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>95</v>
       </c>
@@ -6075,10 +6068,10 @@
         <v>207</v>
       </c>
       <c r="F71" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H71" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I71" t="s">
         <v>213</v>
@@ -6090,12 +6083,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="12" t="s">
         <v>125</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C72" s="13">
         <v>4</v>
@@ -6108,7 +6101,7 @@
         <v>207</v>
       </c>
       <c r="F72" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I72" t="s">
         <v>213</v>
@@ -6120,12 +6113,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="63.95">
+    <row r="73" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>129</v>
       </c>
       <c r="B73" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C73" s="2">
         <v>2</v>
@@ -6138,7 +6131,7 @@
         <v>207</v>
       </c>
       <c r="H73" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I73" t="s">
         <v>213</v>
@@ -6150,12 +6143,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
@@ -6171,7 +6164,7 @@
         <v>215</v>
       </c>
       <c r="H74" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I74" t="s">
         <v>216</v>
@@ -6183,12 +6176,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>85</v>
       </c>
       <c r="B75" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C75" s="2">
         <v>1</v>
@@ -6201,24 +6194,24 @@
         <v>207</v>
       </c>
       <c r="H75" t="s">
+        <v>284</v>
+      </c>
+      <c r="I75" t="s">
+        <v>216</v>
+      </c>
+      <c r="J75" t="s">
         <v>285</v>
-      </c>
-      <c r="I75" t="s">
-        <v>216</v>
-      </c>
-      <c r="J75" t="s">
-        <v>286</v>
       </c>
       <c r="K75">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>127</v>
       </c>
       <c r="B76" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C76" s="2">
         <v>1</v>
@@ -6234,7 +6227,7 @@
         <v>215</v>
       </c>
       <c r="H76" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I76" t="s">
         <v>216</v>
@@ -6246,12 +6239,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>148</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C77" s="2">
         <v>1</v>
@@ -6264,7 +6257,7 @@
         <v>207</v>
       </c>
       <c r="H77" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I77" t="s">
         <v>216</v>
@@ -6276,12 +6269,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>103</v>
       </c>
       <c r="B78" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C78" s="2">
         <v>1</v>
@@ -6297,7 +6290,7 @@
         <v>215</v>
       </c>
       <c r="H78" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I78" t="s">
         <v>216</v>
@@ -6309,12 +6302,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>176</v>
       </c>
       <c r="B79" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C79" s="2">
         <v>1</v>
@@ -6324,13 +6317,13 @@
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F79" t="s">
         <v>215</v>
       </c>
       <c r="H79" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I79" t="s">
         <v>216</v>
@@ -6342,12 +6335,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>61</v>
       </c>
       <c r="B80" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C80" s="2">
         <v>1</v>
@@ -6357,10 +6350,10 @@
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H80" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I80" t="s">
         <v>216</v>
@@ -6372,12 +6365,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C81" s="2">
         <v>1</v>
@@ -6393,7 +6386,7 @@
         <v>215</v>
       </c>
       <c r="H81" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I81" t="s">
         <v>216</v>
@@ -6405,12 +6398,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C82" s="2">
         <v>1</v>
@@ -6426,7 +6419,7 @@
         <v>215</v>
       </c>
       <c r="H82" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I82" t="s">
         <v>216</v>
@@ -6438,12 +6431,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>153</v>
       </c>
       <c r="B83" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C83" s="2">
         <v>1</v>
@@ -6456,7 +6449,7 @@
         <v>207</v>
       </c>
       <c r="H83" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I83" t="s">
         <v>216</v>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD96ECA9-4CD7-0544-9753-3CC6E3DA31DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35F38AC-B6BE-9248-AB5A-BE8DB1A8DFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35F38AC-B6BE-9248-AB5A-BE8DB1A8DFDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2B46C83-FA7C-42F9-9F49-203FE4ADDC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -34,6 +34,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="706" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="296">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -707,189 +708,208 @@
     <t>Main Menu</t>
   </si>
   <si>
+    <t>Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu</t>
+  </si>
+  <si>
+    <t>Neutral / Negative</t>
+  </si>
+  <si>
+    <t>If EP name = Closed Hours-Holidays Menu Telephony EP	, then Neutral, type = "After hours call"
+If EP name = Closed Queue Menu Telephony EP, then Negative, type = "Closed Queue"</t>
+  </si>
+  <si>
+    <t>Legal Menu</t>
+  </si>
+  <si>
+    <t>Farmworker Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative </t>
+  </si>
+  <si>
+    <t>Abandoned (tenative)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on info from Mark, this reflects no activity at Farmworker Menu and cannot progress without a selection; either call disconnects after max number of repetitions or the caller hangs up; max step counter is unknown so believe calls should be considered abandoned </t>
+  </si>
+  <si>
+    <t>N/A - Ad Hoc Outbound Call</t>
+  </si>
+  <si>
+    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive / neutral (tenative) </t>
+  </si>
+  <si>
+    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect  to customer; uncertainty b/c there are not activity names that indicate connection in the data</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front Desk </t>
+  </si>
+  <si>
+    <t>No input for language selection;</t>
+  </si>
+  <si>
+    <t>Holiday &amp; Closed Menu</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Appointment Menu</t>
+  </si>
+  <si>
+    <t>Caller has an appointment scheduled</t>
+  </si>
+  <si>
+    <t>Other Legal Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive </t>
+  </si>
+  <si>
+    <t>Caller requests an interpreter</t>
+  </si>
+  <si>
+    <t>Housing menu</t>
+  </si>
+  <si>
+    <t>Voicemail Transfer</t>
+  </si>
+  <si>
+    <t>Family menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legal Menu </t>
+  </si>
+  <si>
+    <t>Pre-legal seniors menu</t>
+  </si>
+  <si>
+    <t>HIV Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive / Neutral (tenative) </t>
+  </si>
+  <si>
+    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect; uncertainty b/c there are not activity names that indicate connection in the data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Menu </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Positive (tenative) </t>
+  </si>
+  <si>
+    <t>Caller listens to message; no option given to return to previous menus</t>
+  </si>
+  <si>
+    <t>Issue not handled by LAC</t>
+  </si>
+  <si>
+    <t>No input</t>
+  </si>
+  <si>
+    <t>Immigration menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abandoned </t>
+  </si>
+  <si>
+    <t>Family Menu</t>
+  </si>
+  <si>
+    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action</t>
+  </si>
+  <si>
+    <t>Benefits Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neutral </t>
+  </si>
+  <si>
+    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
+  </si>
+  <si>
+    <t>Caller is non-Cook County Senior and did not make a selection after message</t>
+  </si>
+  <si>
+    <t>Employment menu</t>
+  </si>
+  <si>
+    <t>No activity</t>
+  </si>
+  <si>
+    <t>Caller selected Other Legal option (8) in Suburban Seniors Menu</t>
+  </si>
+  <si>
+    <t>Immigration Menu</t>
+  </si>
+  <si>
+    <t>Voice Mail Transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closed </t>
+  </si>
+  <si>
+    <t>Unsuccessful Courtesy Callback</t>
+  </si>
+  <si>
+    <t>No Agent Name for attempted courtesy callback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assuming this corresponds to Farm Worker Voicemail transfer on flow charts </t>
+  </si>
+  <si>
+    <t>Verbiage tells callers that they can leave comments online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
+  </si>
+  <si>
+    <t>Outbound call failed to connect; system error</t>
+  </si>
+  <si>
+    <t>Employment Menu</t>
+  </si>
+  <si>
+    <t>Pre-Legal Seniors</t>
+  </si>
+  <si>
+    <t>Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
+  </si>
+  <si>
     <t>Courtesy Callback</t>
   </si>
   <si>
-    <t>Neutral / Negative</t>
-  </si>
-  <si>
-    <t>Legal Menu</t>
-  </si>
-  <si>
-    <t>Farmworker Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative </t>
-  </si>
-  <si>
-    <t>Abandoned (tenative)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Based on info from Mark, this reflects no activity at Farmworker Menu and cannot progress without a selection; either call disconnects after max number of repetitions or the caller hangs up; max step counter is unknown so believe calls should be considered abandoned </t>
-  </si>
-  <si>
-    <t>N/A - Ad Hoc Outbound Call</t>
-  </si>
-  <si>
-    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up</t>
-  </si>
-  <si>
-    <t>Courtesy Callback, Queues</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive / neutral (tenative) </t>
-  </si>
-  <si>
-    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect  to customer; uncertainty b/c there are not activity names that indicate connection in the data</t>
-  </si>
-  <si>
-    <t>Positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front Desk </t>
-  </si>
-  <si>
-    <t>No input for language selection;</t>
-  </si>
-  <si>
-    <t>Holiday &amp; Closed Menu</t>
-  </si>
-  <si>
-    <t>Neutral</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>Appointment Menu</t>
-  </si>
-  <si>
-    <t>Caller has an appointment scheduled</t>
-  </si>
-  <si>
-    <t>Other Legal Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive </t>
-  </si>
-  <si>
-    <t>Caller requests an interpreter</t>
-  </si>
-  <si>
-    <t>Housing menu</t>
-  </si>
-  <si>
-    <t>Voicemail Transfer</t>
-  </si>
-  <si>
-    <t>Family menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Queues </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Legal Menu </t>
-  </si>
-  <si>
-    <t>Pre-legal seniors menu</t>
-  </si>
-  <si>
-    <t>HIV Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive / Neutral (tenative) </t>
-  </si>
-  <si>
-    <t>If there is an Agent Name and time difference between activity &amp; end of call, it is positive. Otherwise, the call could not connect; uncertainty b/c there are not activity names that indicate connection in the data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Menu </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Positive (tenative) </t>
-  </si>
-  <si>
-    <t>Caller listens to message; no option given to return to previous menus</t>
-  </si>
-  <si>
-    <t>Issue not handled by LAC</t>
-  </si>
-  <si>
-    <t>No input</t>
-  </si>
-  <si>
-    <t>Immigration menu</t>
-  </si>
-  <si>
-    <t>Pre-Legal Seniors Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abandoned </t>
-  </si>
-  <si>
-    <t>Family Menu</t>
-  </si>
-  <si>
-    <t>Benefits Menu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neutral </t>
-  </si>
-  <si>
-    <t>Callers outside Cook County or calling on someone else's behalf  (without POA) should abandon</t>
-  </si>
-  <si>
-    <t>Caller is non-Cook County Senior and did not make a selection after message</t>
-  </si>
-  <si>
-    <t>Queues</t>
-  </si>
-  <si>
-    <t>Employment menu</t>
-  </si>
-  <si>
-    <t>No activity</t>
-  </si>
-  <si>
-    <t>Caller selected Other Legal option (8) in Suburban Seniors Menu</t>
-  </si>
-  <si>
-    <t>Immigration Menu</t>
-  </si>
-  <si>
-    <t>Voice Mail Transfer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Closed </t>
-  </si>
-  <si>
-    <t>Unsuccessful Courtesy Callback</t>
-  </si>
-  <si>
-    <t>No Agent Name for attempted courtesy callback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assuming this corresponds to Farm Worker Voicemail transfer on flow charts </t>
-  </si>
-  <si>
-    <t>Verbiage tells callers that they can leave comments online</t>
-  </si>
-  <si>
-    <t>Outbound call failed to connect; system error</t>
-  </si>
-  <si>
-    <t>Employment Menu</t>
-  </si>
-  <si>
-    <t>Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
-  </si>
-  <si>
     <t>System failure in courtesy callback attempt</t>
   </si>
   <si>
     <t xml:space="preserve">Caller hangs up before being connected with an agent, system tries to progress but gives error since there's no caller </t>
   </si>
   <si>
+    <t xml:space="preserve">Pre-Legal Seniors </t>
+  </si>
+  <si>
     <t>Caller did not finish confirming callback</t>
   </si>
   <si>
@@ -902,11 +922,16 @@
     <t>VIvi</t>
   </si>
   <si>
+    <t>Pre-Legal Menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Queues Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu, </t>
+  </si>
+  <si>
     <t xml:space="preserve">"Play Courtesy CallBack Confirmation" . This is typically played right before the contact is disconnected from the system. The consumer selected a courtesy callback but hung up before the system could disconnect so this is neutral. </t>
   </si>
   <si>
-    <t>If EP name = Closed Hours-Holidays Menu Telephony EP	, then Neutral, type = "After hours call"
-If EP name = Closed Queue Menu Telephony EP, then Negative, type = "Closed Queue", if EP Name = "Pre-Legal Menu Seniors Menu Telephony EP", then neutral, type = "issue not handled by LAC"</t>
+    <t xml:space="preserve">Pre-Legal Menu </t>
   </si>
 </sst>
 </file>
@@ -917,7 +942,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -939,6 +964,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -990,7 +1027,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1001,21 +1038,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1353,13 +1414,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1367,7 +1428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1375,7 +1436,7 @@
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1383,7 +1444,7 @@
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1391,7 +1452,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1399,7 +1460,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1407,7 +1468,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1415,7 +1476,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1423,7 +1484,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1431,7 +1492,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1439,7 +1500,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1447,7 +1508,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1455,7 +1516,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1463,7 +1524,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1471,7 +1532,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1479,7 +1540,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1487,7 +1548,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1495,7 +1556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1503,7 +1564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1511,7 +1572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1519,7 +1580,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1527,7 +1588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1535,7 +1596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1543,7 +1604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1551,7 +1612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1559,7 +1620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1567,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1583,17 +1644,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="32.1">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1607,7 +1668,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1621,7 +1682,7 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1635,7 +1696,7 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1649,7 +1710,7 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1663,7 +1724,7 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1677,7 +1738,7 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1691,7 +1752,7 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1705,7 +1766,7 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1719,7 +1780,7 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1733,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1747,7 +1808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1761,7 +1822,7 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1775,7 +1836,7 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1789,7 +1850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1803,7 +1864,7 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1817,7 +1878,7 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1831,7 +1892,7 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1845,7 +1906,7 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1859,7 +1920,7 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1873,7 +1934,7 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1887,7 +1948,7 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1901,7 +1962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1915,7 +1976,7 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1929,7 +1990,7 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -1943,7 +2004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -1957,7 +2018,7 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -1971,7 +2032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -1985,7 +2046,7 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1999,7 +2060,7 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -2013,7 +2074,7 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2027,7 +2088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -2041,7 +2102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -2055,7 +2116,7 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -2069,7 +2130,7 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2083,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2097,7 +2158,7 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -2111,7 +2172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -2125,7 +2186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -2139,7 +2200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2153,7 +2214,7 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2167,7 +2228,7 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -2181,7 +2242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2195,7 +2256,7 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2209,7 +2270,7 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2223,7 +2284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -2237,7 +2298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2251,7 +2312,7 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2265,7 +2326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -2279,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -2293,7 +2354,7 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -2307,7 +2368,7 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -2321,7 +2382,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2335,7 +2396,7 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -2349,7 +2410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2363,7 +2424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -2377,7 +2438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -2391,7 +2452,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2405,7 +2466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -2419,7 +2480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2433,7 +2494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2447,7 +2508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -2461,7 +2522,7 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -2475,7 +2536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -2489,7 +2550,7 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -2503,7 +2564,7 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -2517,7 +2578,7 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2531,7 +2592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -2545,7 +2606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>99</v>
       </c>
@@ -2559,7 +2620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -2573,7 +2634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -2587,7 +2648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -2601,7 +2662,7 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -2615,7 +2676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -2629,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -2643,7 +2704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -2657,7 +2718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -2671,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -2685,7 +2746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -2699,7 +2760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -2713,7 +2774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>111</v>
       </c>
@@ -2727,7 +2788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -2741,7 +2802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -2755,7 +2816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>114</v>
       </c>
@@ -2769,7 +2830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -2783,7 +2844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -2797,7 +2858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -2811,7 +2872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -2825,7 +2886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>119</v>
       </c>
@@ -2839,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -2853,7 +2914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -2867,7 +2928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -2881,7 +2942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -2895,7 +2956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -2909,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -2923,7 +2984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -2937,7 +2998,7 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -2951,7 +3012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -2965,7 +3026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -2979,7 +3040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -2993,7 +3054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -3007,7 +3068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -3021,7 +3082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -3035,7 +3096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -3049,7 +3110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -3063,7 +3124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -3077,7 +3138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -3091,7 +3152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -3105,7 +3166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3119,7 +3180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -3133,7 +3194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
         <v>141</v>
       </c>
@@ -3147,7 +3208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
         <v>142</v>
       </c>
@@ -3161,7 +3222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
         <v>143</v>
       </c>
@@ -3175,7 +3236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
         <v>144</v>
       </c>
@@ -3189,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
         <v>145</v>
       </c>
@@ -3203,7 +3264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3217,7 +3278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
         <v>147</v>
       </c>
@@ -3231,7 +3292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -3245,7 +3306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
         <v>149</v>
       </c>
@@ -3259,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
         <v>150</v>
       </c>
@@ -3273,7 +3334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
         <v>151</v>
       </c>
@@ -3287,7 +3348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
         <v>152</v>
       </c>
@@ -3301,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -3315,7 +3376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -3329,7 +3390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
         <v>155</v>
       </c>
@@ -3343,7 +3404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
         <v>156</v>
       </c>
@@ -3357,7 +3418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
         <v>157</v>
       </c>
@@ -3371,7 +3432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
         <v>158</v>
       </c>
@@ -3385,7 +3446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
         <v>159</v>
       </c>
@@ -3399,7 +3460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -3413,7 +3474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
         <v>161</v>
       </c>
@@ -3427,7 +3488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -3441,7 +3502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -3455,7 +3516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -3469,7 +3530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -3483,7 +3544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -3497,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -3511,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -3525,7 +3586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -3539,7 +3600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -3553,7 +3614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -3567,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -3581,7 +3642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -3595,7 +3656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -3609,7 +3670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -3623,7 +3684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
         <v>176</v>
       </c>
@@ -3637,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
         <v>177</v>
       </c>
@@ -3651,7 +3712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
         <v>178</v>
       </c>
@@ -3665,7 +3726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -3679,7 +3740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
         <v>180</v>
       </c>
@@ -3693,7 +3754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
         <v>181</v>
       </c>
@@ -3707,7 +3768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -3721,7 +3782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
         <v>183</v>
       </c>
@@ -3735,7 +3796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
         <v>184</v>
       </c>
@@ -3749,7 +3810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
         <v>185</v>
       </c>
@@ -3763,7 +3824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
         <v>186</v>
       </c>
@@ -3777,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -3791,7 +3852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -3805,7 +3866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -3819,7 +3880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -3833,7 +3894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -3847,7 +3908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -3861,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -3875,7 +3936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
         <v>194</v>
       </c>
@@ -3889,7 +3950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
         <v>195</v>
       </c>
@@ -3923,2541 +3984,2688 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.5" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:11" ht="48">
+      <c r="A1" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+    <row r="2" spans="1:11" ht="72.75">
+      <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="9">
         <v>39892</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="10">
         <f>C2/SUM(($C$2:$C$83))</f>
         <v>0.16056866391350899</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="I2" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:11" ht="29.25">
+      <c r="A3" s="5" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="9">
         <v>28035</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="10">
         <f t="shared" ref="D3:D66" si="0">C3/SUM(($C$2:$C$83))</f>
         <v>0.11284323906585843</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="G3" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="I3" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J3" t="s">
-        <v>213</v>
-      </c>
-      <c r="K3">
+      <c r="J3" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K3" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+    <row r="4" spans="1:11" ht="29.25">
+      <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="9">
         <v>27545</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="10">
         <f t="shared" si="0"/>
         <v>0.11087094774635528</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J4" t="s">
-        <v>216</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="80" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="J4" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="87">
+      <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="9">
         <v>25721</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="10">
         <f t="shared" si="0"/>
         <v>0.10352919393661297</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>218</v>
       </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J5" t="s">
-        <v>216</v>
-      </c>
-      <c r="K5">
+      <c r="J5" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K5" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="9">
         <v>13075</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="10">
         <f t="shared" si="0"/>
         <v>5.2627977556129801E-2</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I6" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="J6" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K6" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="87">
+      <c r="A7" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="9">
         <v>12010</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="10">
         <f t="shared" si="0"/>
         <v>4.8341262749454599E-2</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>222</v>
       </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="I7" t="s">
+        <v>223</v>
+      </c>
+      <c r="I7" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K7">
+      <c r="J7" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B8" t="s">
-        <v>223</v>
-      </c>
-      <c r="C8" s="2">
+      <c r="B8" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C8" s="9">
         <v>11987</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="10">
         <f t="shared" si="0"/>
         <v>4.8248685809967717E-2</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I8" t="s">
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J8" t="s">
-        <v>216</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="96" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="J8" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K8" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="87">
+      <c r="A9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B9" t="s">
-        <v>224</v>
-      </c>
-      <c r="C9" s="15">
+      <c r="B9" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C9" s="11">
         <v>9640</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="12">
         <f t="shared" si="0"/>
         <v>3.8801812897980216E-2</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F9" t="s">
         <v>226</v>
       </c>
-      <c r="G9" t="s">
+      <c r="F9" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>212</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="I9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="J9" t="s">
-        <v>213</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="J9" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K9" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="62.25" customHeight="1">
+      <c r="A10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B10" t="s">
-        <v>228</v>
-      </c>
-      <c r="C10" s="15">
+      <c r="B10" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="11">
         <v>9358</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="12">
         <f t="shared" si="0"/>
         <v>3.7666739118184529E-2</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>225</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="I10" t="s">
-        <v>213</v>
-      </c>
-      <c r="J10" t="s">
-        <v>216</v>
-      </c>
-      <c r="K10">
+        <v>230</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="80" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="11" spans="1:11" ht="87">
+      <c r="A11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B11" t="s">
-        <v>230</v>
-      </c>
-      <c r="C11" s="15">
+      <c r="B11" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="11">
         <v>8939</v>
       </c>
-      <c r="D11" s="16">
+      <c r="D11" s="12">
         <f t="shared" si="0"/>
         <v>3.5980228785793066E-2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>231</v>
-      </c>
+        <v>232</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="I11" t="s">
-        <v>213</v>
-      </c>
-      <c r="J11" t="s">
-        <v>216</v>
-      </c>
-      <c r="K11">
+        <v>233</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K11" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:11" ht="50.25" customHeight="1">
+      <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="9">
         <v>7890</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="10">
         <f t="shared" si="0"/>
         <v>3.1757915328326128E-2</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F12" t="s">
         <v>234</v>
       </c>
+      <c r="F12" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="I12" t="s">
-        <v>213</v>
-      </c>
-      <c r="J12" t="s">
-        <v>216</v>
-      </c>
-      <c r="K12">
+        <v>236</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="13" spans="1:11">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="B13" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C13" s="9">
         <v>7765</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="10">
         <f t="shared" si="0"/>
         <v>3.125477978763655E-2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F13" t="s">
         <v>238</v>
       </c>
-      <c r="I13" t="s">
-        <v>213</v>
-      </c>
-      <c r="J13" t="s">
-        <v>216</v>
-      </c>
-      <c r="K13">
+      <c r="F13" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K13" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+    <row r="14" spans="1:11">
+      <c r="A14" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B14" t="s">
-        <v>239</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="B14" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="9">
         <v>6895</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="10">
         <f t="shared" si="0"/>
         <v>2.7752956424437092E-2</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F14" t="s">
         <v>234</v>
       </c>
+      <c r="F14" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="I14" t="s">
-        <v>213</v>
-      </c>
-      <c r="J14" t="s">
-        <v>216</v>
-      </c>
-      <c r="K14">
+        <v>241</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K14" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
+    <row r="15" spans="1:11">
+      <c r="A15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B15" t="s">
-        <v>241</v>
-      </c>
-      <c r="C15" s="2">
+      <c r="B15" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="9">
         <v>6863</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="10">
         <f t="shared" si="0"/>
         <v>2.7624153726020562E-2</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I15" t="s">
-        <v>213</v>
-      </c>
-      <c r="J15" t="s">
-        <v>216</v>
-      </c>
-      <c r="K15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="29.25">
+      <c r="A16" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16" s="9">
         <v>3959</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="10">
         <f t="shared" si="0"/>
         <v>1.5935308844720296E-2</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="I16" t="s">
-        <v>213</v>
-      </c>
-      <c r="J16" t="s">
-        <v>216</v>
-      </c>
-      <c r="K16">
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K16" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+    <row r="17" spans="1:11">
+      <c r="A17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B17" t="s">
-        <v>223</v>
-      </c>
-      <c r="C17" s="2">
+      <c r="B17" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C17" s="9">
         <v>2545</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="10">
         <f t="shared" si="0"/>
         <v>1.0243839608439796E-2</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F17" t="s">
-        <v>234</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="I17" t="s">
-        <v>213</v>
-      </c>
-      <c r="J17" t="s">
-        <v>216</v>
-      </c>
-      <c r="K17">
+        <v>244</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K17" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+    <row r="18" spans="1:11">
+      <c r="A18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B18" t="s">
-        <v>244</v>
-      </c>
-      <c r="C18" s="2">
+      <c r="B18" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C18" s="9">
         <v>2394</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="10">
         <f t="shared" si="0"/>
         <v>9.6360518752867871E-3</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I18" t="s">
-        <v>213</v>
-      </c>
-      <c r="J18" t="s">
-        <v>216</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B19" t="s">
-        <v>223</v>
-      </c>
-      <c r="C19" s="2">
+      <c r="B19" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="C19" s="9">
         <v>2267</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="10">
         <f t="shared" si="0"/>
         <v>9.1248661659461758E-3</v>
       </c>
       <c r="E19" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K19" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="F19" t="s">
-        <v>245</v>
-      </c>
-      <c r="I19" t="s">
-        <v>213</v>
-      </c>
-      <c r="J19" t="s">
-        <v>216</v>
-      </c>
-      <c r="K19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B20" t="s">
-        <v>241</v>
-      </c>
-      <c r="C20" s="2">
+      <c r="C20" s="9">
         <v>2136</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="10">
         <f t="shared" si="0"/>
         <v>8.5975801193034999E-3</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I20" t="s">
-        <v>213</v>
-      </c>
-      <c r="J20" t="s">
-        <v>216</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="B21" t="s">
-        <v>246</v>
-      </c>
-      <c r="C21" s="2">
+      <c r="B21" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C21" s="9">
         <v>1462</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="10">
         <f t="shared" si="0"/>
         <v>5.8846732839052977E-3</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I21" t="s">
-        <v>213</v>
-      </c>
-      <c r="J21" t="s">
-        <v>216</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="68.25">
+      <c r="A22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
-        <v>247</v>
-      </c>
-      <c r="C22" s="2">
+      <c r="B22" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C22" s="9">
         <v>1287</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="10">
         <f t="shared" si="0"/>
         <v>5.1802835269398892E-3</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I22" t="s">
-        <v>213</v>
-      </c>
-      <c r="J22" t="s">
-        <v>216</v>
-      </c>
-      <c r="K22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B23" t="s">
-        <v>248</v>
-      </c>
-      <c r="C23" s="2">
+      <c r="B23" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="9">
         <v>1267</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="10">
         <f t="shared" si="0"/>
         <v>5.099781840429557E-3</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I23" t="s">
-        <v>213</v>
-      </c>
-      <c r="J23" t="s">
-        <v>216</v>
-      </c>
-      <c r="K23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B24" t="s">
-        <v>249</v>
-      </c>
-      <c r="C24" s="2">
+      <c r="B24" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C24" s="9">
         <v>1209</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="10">
         <f t="shared" si="0"/>
         <v>4.8663269495495933E-3</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I24" t="s">
-        <v>213</v>
-      </c>
-      <c r="J24" t="s">
-        <v>216</v>
-      </c>
-      <c r="K24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J24" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="B25" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C25" s="9">
         <v>870</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="10">
         <f t="shared" si="0"/>
         <v>3.5018233631994591E-3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I25" t="s">
-        <v>213</v>
-      </c>
-      <c r="J25" t="s">
-        <v>216</v>
-      </c>
-      <c r="K25">
+        <v>238</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J25" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K25" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="26" spans="1:11">
+      <c r="A26" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B26" t="s">
-        <v>244</v>
-      </c>
-      <c r="C26" s="2">
+      <c r="B26" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26" s="9">
         <v>837</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="10">
         <f t="shared" si="0"/>
         <v>3.3689955804574105E-3</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I26" t="s">
-        <v>213</v>
-      </c>
-      <c r="J26" t="s">
-        <v>216</v>
-      </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B27" t="s">
-        <v>250</v>
-      </c>
-      <c r="C27" s="2">
+      <c r="B27" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C27" s="9">
         <v>836</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="10">
         <f t="shared" si="0"/>
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F27" t="s">
-        <v>245</v>
-      </c>
-      <c r="I27" t="s">
-        <v>213</v>
-      </c>
-      <c r="J27" t="s">
-        <v>216</v>
-      </c>
-      <c r="K27">
+        <v>234</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K27" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+    <row r="28" spans="1:11" ht="68.25">
+      <c r="A28" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B28" t="s">
-        <v>247</v>
-      </c>
-      <c r="C28" s="2">
+      <c r="B28" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C28" s="9">
         <v>785</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="10">
         <f t="shared" si="0"/>
         <v>3.1596911955305462E-3</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F28" t="s">
+      <c r="F28" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I28" t="s">
-        <v>213</v>
-      </c>
-      <c r="J28" t="s">
-        <v>216</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="B29" t="s">
-        <v>250</v>
-      </c>
-      <c r="C29" s="2">
+      <c r="B29" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C29" s="9">
         <v>771</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="10">
         <f t="shared" si="0"/>
         <v>3.1033400149733138E-3</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F29" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I29" t="s">
-        <v>213</v>
-      </c>
-      <c r="J29" t="s">
-        <v>216</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A30" s="12" t="s">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="87">
+      <c r="A30" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="B30" t="s">
-        <v>230</v>
-      </c>
-      <c r="C30" s="15">
+      <c r="B30" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C30" s="11">
         <v>694</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="12">
         <f t="shared" si="0"/>
         <v>2.793408521908534E-3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>251</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="I30" t="s">
-        <v>213</v>
-      </c>
-      <c r="K30">
+        <v>254</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+    <row r="31" spans="1:11" ht="29.25">
+      <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C31" s="2">
+        <v>255</v>
+      </c>
+      <c r="C31" s="9">
         <v>672</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="10">
         <f t="shared" si="0"/>
         <v>2.7048566667471682E-3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>254</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="I31" t="s">
-        <v>213</v>
-      </c>
-      <c r="J31" t="s">
-        <v>216</v>
-      </c>
-      <c r="K31">
+        <v>257</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J31" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K31" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+    <row r="32" spans="1:11">
+      <c r="A32" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B32" t="s">
-        <v>244</v>
-      </c>
-      <c r="C32" s="2">
+      <c r="B32" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="C32" s="9">
         <v>604</v>
       </c>
-      <c r="D32" s="6">
+      <c r="D32" s="10">
         <f t="shared" si="0"/>
         <v>2.4311509326120384E-3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F32" t="s">
-        <v>256</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-      <c r="I32" t="s">
-        <v>213</v>
-      </c>
-      <c r="J32" t="s">
-        <v>216</v>
-      </c>
-      <c r="K32">
+      <c r="I32" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K32" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+    <row r="33" spans="1:11">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" t="s">
-        <v>246</v>
-      </c>
-      <c r="C33" s="2">
+      <c r="B33" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C33" s="9">
         <v>543</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="10">
         <f t="shared" si="0"/>
         <v>2.1856207887555245E-3</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I33" t="s">
-        <v>213</v>
-      </c>
-      <c r="J33" t="s">
-        <v>216</v>
-      </c>
-      <c r="K33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K33" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B34" s="5" t="s">
         <v>220</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="9">
         <v>541</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="10">
         <f t="shared" si="0"/>
         <v>2.1775706201044914E-3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F34" t="s">
         <v>234</v>
       </c>
+      <c r="F34" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="I34" t="s">
-        <v>213</v>
-      </c>
-      <c r="J34" t="s">
-        <v>216</v>
-      </c>
-      <c r="K34">
+        <v>259</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
+    <row r="35" spans="1:11">
+      <c r="A35" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B35" t="s">
-        <v>246</v>
-      </c>
-      <c r="C35" s="2">
+      <c r="B35" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C35" s="9">
         <v>540</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="10">
         <f t="shared" si="0"/>
         <v>2.1735455357789744E-3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="I35" t="s">
-        <v>213</v>
-      </c>
-      <c r="J35" t="s">
-        <v>216</v>
-      </c>
-      <c r="K35">
+        <v>238</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K35" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
+    <row r="36" spans="1:11">
+      <c r="A36" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B36" t="s">
-        <v>258</v>
-      </c>
-      <c r="C36" s="2">
+      <c r="B36" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C36" s="9">
         <v>527</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="10">
         <f t="shared" si="0"/>
         <v>2.1212194395472585E-3</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F36" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I36" t="s">
-        <v>213</v>
-      </c>
-      <c r="J36" t="s">
-        <v>216</v>
-      </c>
-      <c r="K36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B37" t="s">
-        <v>259</v>
-      </c>
-      <c r="C37" s="2">
+      <c r="B37" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C37" s="9">
         <v>502</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="10">
         <f t="shared" si="0"/>
         <v>2.020592331409343E-3</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F37" t="s">
+      <c r="F37" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I37" t="s">
-        <v>213</v>
-      </c>
-      <c r="J37" t="s">
-        <v>216</v>
-      </c>
-      <c r="K37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K37" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B38" t="s">
-        <v>241</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="B38" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="9">
         <v>479</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="10">
         <f t="shared" si="0"/>
         <v>1.9280153919224608E-3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F38" t="s">
-        <v>256</v>
-      </c>
-      <c r="I38" t="s">
-        <v>213</v>
-      </c>
-      <c r="J38" t="s">
-        <v>216</v>
-      </c>
-      <c r="K38">
+        <v>238</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K38" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
+    <row r="39" spans="1:11">
+      <c r="A39" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="B39" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="2">
+      <c r="B39" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" s="9">
         <v>454</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="10">
         <f t="shared" si="0"/>
         <v>1.8273882837845452E-3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F39" t="s">
-        <v>256</v>
-      </c>
-      <c r="I39" t="s">
-        <v>213</v>
-      </c>
-      <c r="J39" t="s">
-        <v>216</v>
-      </c>
-      <c r="K39">
+        <v>238</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K39" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
+    <row r="40" spans="1:11">
+      <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>249</v>
-      </c>
-      <c r="C40" s="2">
+      <c r="B40" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C40" s="9">
         <v>444</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="10">
         <f t="shared" si="0"/>
         <v>1.7871374405293791E-3</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F40" t="s">
-        <v>260</v>
-      </c>
-      <c r="I40" t="s">
-        <v>213</v>
-      </c>
-      <c r="J40" t="s">
-        <v>216</v>
-      </c>
-      <c r="K40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
+      <c r="F40" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J40" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K40" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B41" t="s">
-        <v>249</v>
-      </c>
-      <c r="C41" s="2">
+      <c r="B41" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C41" s="9">
         <v>442</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="10">
         <f t="shared" si="0"/>
         <v>1.779087271878346E-3</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F41" t="s">
-        <v>260</v>
-      </c>
-      <c r="I41" t="s">
-        <v>213</v>
-      </c>
-      <c r="J41" t="s">
-        <v>216</v>
-      </c>
-      <c r="K41">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
+      <c r="F41" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J41" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K41" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="29.25">
+      <c r="A42" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B42" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="C42" s="9">
+      <c r="B42" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C42" s="14">
         <v>412</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42" s="15">
         <f t="shared" si="0"/>
         <v>1.6583347421128473E-3</v>
       </c>
-      <c r="E42" s="11"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="8"/>
-      <c r="J42" s="8"/>
-      <c r="K42" s="8"/>
-    </row>
-    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B43" t="s">
-        <v>261</v>
-      </c>
-      <c r="C43" s="2">
+      <c r="B43" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C43" s="9">
         <v>353</v>
       </c>
-      <c r="D43" s="6">
+      <c r="D43" s="10">
         <f t="shared" si="0"/>
         <v>1.4208547669073666E-3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F43" t="s">
-        <v>256</v>
-      </c>
-      <c r="I43" t="s">
-        <v>213</v>
-      </c>
-      <c r="J43" t="s">
-        <v>216</v>
-      </c>
-      <c r="K43">
+        <v>238</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K43" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
+    <row r="44" spans="1:11">
+      <c r="A44" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="B44" t="s">
-        <v>262</v>
-      </c>
-      <c r="C44" s="2">
+      <c r="B44" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" s="9">
         <v>298</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="10">
         <f t="shared" si="0"/>
         <v>1.1994751290039527E-3</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F44" t="s">
+      <c r="F44" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I44" t="s">
-        <v>213</v>
-      </c>
-      <c r="J44" t="s">
-        <v>216</v>
-      </c>
-      <c r="K44">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A45" s="12" t="s">
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J44" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K44" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="43.5">
+      <c r="A45" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="C45" s="13">
+      <c r="B45" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C45" s="16">
         <v>278</v>
       </c>
-      <c r="D45" s="14">
+      <c r="D45" s="17">
         <f t="shared" si="0"/>
         <v>1.1189734424936202E-3</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="F45" t="s">
-        <v>256</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I45" t="s">
-        <v>213</v>
-      </c>
-      <c r="J45" t="s">
-        <v>216</v>
-      </c>
-      <c r="K45">
+        <v>267</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J45" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K45" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="46" spans="1:11" ht="29.25">
+      <c r="A46" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="B46" t="s">
-        <v>259</v>
-      </c>
-      <c r="C46" s="2">
+      <c r="B46" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C46" s="9">
         <v>228</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="10">
         <f t="shared" si="0"/>
         <v>9.1771922621778929E-4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F46" t="s">
-        <v>256</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="I46" t="s">
-        <v>213</v>
-      </c>
-      <c r="J46" t="s">
-        <v>216</v>
-      </c>
-      <c r="K46">
+        <v>268</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K46" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+    <row r="47" spans="1:11" ht="68.25">
+      <c r="A47" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C47" s="2">
+      <c r="B47" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C47" s="9">
         <v>219</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="10">
         <f t="shared" si="0"/>
         <v>8.8149346728813973E-4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="F47" t="s">
-        <v>256</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="I47" t="s">
-        <v>213</v>
-      </c>
-      <c r="J47" t="s">
-        <v>216</v>
-      </c>
-      <c r="K47">
+        <v>267</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K47" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
+    <row r="48" spans="1:11">
+      <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B48" t="s">
-        <v>259</v>
-      </c>
-      <c r="C48" s="2">
+      <c r="B48" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C48" s="9">
         <v>212</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="10">
         <f t="shared" si="0"/>
         <v>8.533178770095233E-4</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F48" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I48" t="s">
-        <v>213</v>
-      </c>
-      <c r="J48" t="s">
-        <v>216</v>
-      </c>
-      <c r="K48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K48" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B49" t="s">
-        <v>262</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="B49" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C49" s="9">
         <v>185</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="10">
         <f t="shared" si="0"/>
         <v>7.446406002205746E-4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F49" t="s">
-        <v>245</v>
-      </c>
-      <c r="I49" t="s">
-        <v>213</v>
-      </c>
-      <c r="J49" t="s">
-        <v>216</v>
-      </c>
-      <c r="K49">
+        <v>234</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K49" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    <row r="50" spans="1:11">
+      <c r="A50" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B50" t="s">
-        <v>267</v>
-      </c>
-      <c r="C50" s="2">
+      <c r="B50" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C50" s="9">
         <v>183</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="10">
         <f t="shared" si="0"/>
         <v>7.3659043156954135E-4</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F50" t="s">
-        <v>260</v>
-      </c>
-      <c r="I50" t="s">
-        <v>213</v>
-      </c>
-      <c r="J50" t="s">
-        <v>216</v>
-      </c>
-      <c r="K50">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A51" s="8" t="s">
-        <v>268</v>
-      </c>
-      <c r="B51" s="8"/>
-      <c r="C51" s="9">
+      <c r="F50" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K50" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B51" s="7"/>
+      <c r="C51" s="14">
         <v>177</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51" s="15">
         <f t="shared" si="0"/>
         <v>7.1243992561644172E-4</v>
       </c>
-      <c r="E51" s="11"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-    </row>
-    <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
+      <c r="K51" s="7"/>
+    </row>
+    <row r="52" spans="1:11" ht="29.25">
+      <c r="A52" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B52" t="s">
-        <v>259</v>
-      </c>
-      <c r="C52" s="2">
+      <c r="B52" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C52" s="9">
         <v>158</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="10">
         <f t="shared" si="0"/>
         <v>6.3596332343162591E-4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F52" t="s">
-        <v>256</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G52" s="5"/>
       <c r="H52" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="I52" t="s">
-        <v>213</v>
-      </c>
-      <c r="J52" t="s">
-        <v>216</v>
-      </c>
-      <c r="K52">
+        <v>271</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K52" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="53" spans="1:11">
+      <c r="A53" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B53" t="s">
-        <v>270</v>
-      </c>
-      <c r="C53" s="2">
+      <c r="B53" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C53" s="9">
         <v>139</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="10">
         <f t="shared" si="0"/>
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F53" t="s">
-        <v>271</v>
-      </c>
-      <c r="I53" t="s">
-        <v>213</v>
-      </c>
-      <c r="J53" t="s">
-        <v>216</v>
-      </c>
-      <c r="K53">
+        <v>234</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K53" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="54" spans="1:11">
+      <c r="A54" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B54" t="s">
-        <v>239</v>
-      </c>
-      <c r="C54" s="2">
+      <c r="B54" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C54" s="9">
         <v>138</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="10">
         <f t="shared" si="0"/>
         <v>5.5546163692129352E-4</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F54" t="s">
+      <c r="F54" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I54" t="s">
-        <v>213</v>
-      </c>
-      <c r="J54" t="s">
-        <v>216</v>
-      </c>
-      <c r="K54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K54" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
+      <c r="A55" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B55" t="s">
-        <v>259</v>
-      </c>
-      <c r="C55" s="2">
+      <c r="B55" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C55" s="9">
         <v>127</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="10">
         <f t="shared" si="0"/>
         <v>5.1118570934061071E-4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F55" t="s">
-        <v>256</v>
-      </c>
-      <c r="I55" t="s">
-        <v>213</v>
-      </c>
-      <c r="J55" t="s">
-        <v>216</v>
-      </c>
-      <c r="K55">
+        <v>238</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K55" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="56" spans="1:11">
+      <c r="A56" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B56" t="s">
-        <v>270</v>
-      </c>
-      <c r="C56" s="2">
+      <c r="B56" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C56" s="9">
         <v>116</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="10">
         <f t="shared" si="0"/>
         <v>4.669097817599279E-4</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F56" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="I56" t="s">
-        <v>213</v>
-      </c>
-      <c r="J56" t="s">
-        <v>216</v>
-      </c>
-      <c r="K56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K56" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="B57" t="s">
-        <v>236</v>
-      </c>
-      <c r="C57" s="2">
+      <c r="B57" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="C57" s="9">
         <v>85</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="10">
         <f t="shared" si="0"/>
         <v>3.4213216766891265E-4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F57" t="s">
-        <v>272</v>
-      </c>
-      <c r="I57" t="s">
-        <v>213</v>
-      </c>
-      <c r="J57" t="s">
-        <v>216</v>
-      </c>
-      <c r="K57">
+        <v>238</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K57" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+    <row r="58" spans="1:11" ht="87">
+      <c r="A58" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="B58" t="s">
-        <v>221</v>
-      </c>
-      <c r="C58" s="2">
+      <c r="B58" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C58" s="9">
         <v>70</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="10">
         <f t="shared" si="0"/>
         <v>2.8175590278616339E-4</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F58" t="s">
-        <v>273</v>
-      </c>
+      <c r="F58" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G58" s="5"/>
       <c r="H58" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="I58" t="s">
-        <v>213</v>
-      </c>
-      <c r="J58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K58">
+        <v>276</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K58" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="59" spans="1:11" ht="29.25">
+      <c r="A59" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B59" t="s">
-        <v>224</v>
-      </c>
-      <c r="C59" s="2">
+      <c r="B59" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C59" s="9">
         <v>67</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="10">
         <f t="shared" si="0"/>
         <v>2.6968064980961351E-4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="F59" t="s">
-        <v>245</v>
-      </c>
+        <v>234</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="G59" s="5"/>
       <c r="H59" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="I59" t="s">
-        <v>213</v>
-      </c>
-      <c r="J59" t="s">
-        <v>216</v>
-      </c>
-      <c r="K59">
+        <v>277</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K59" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
+    <row r="60" spans="1:11" ht="29.25">
+      <c r="A60" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B60" t="s">
-        <v>253</v>
-      </c>
-      <c r="C60" s="2">
+      <c r="B60" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C60" s="9">
         <v>58</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="10">
         <f t="shared" si="0"/>
         <v>2.3345489087996395E-4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>254</v>
-      </c>
+        <v>256</v>
+      </c>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
       <c r="H60" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="I60" t="s">
-        <v>213</v>
-      </c>
-      <c r="J60" t="s">
-        <v>216</v>
-      </c>
-      <c r="K60">
+        <v>278</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K60" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="61" spans="1:11" ht="87">
+      <c r="A61" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B61" t="s">
-        <v>266</v>
-      </c>
-      <c r="C61" s="2">
+      <c r="B61" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="C61" s="9">
         <v>37</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="10">
         <f t="shared" si="0"/>
         <v>1.4892812004411492E-4</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F61" t="s">
-        <v>260</v>
-      </c>
-      <c r="I61" t="s">
-        <v>213</v>
-      </c>
-      <c r="J61" t="s">
-        <v>216</v>
-      </c>
-      <c r="K61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+      <c r="F61" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K61" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
+      <c r="A62" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B62" t="s">
-        <v>253</v>
-      </c>
-      <c r="C62" s="2">
+      <c r="B62" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="C62" s="9">
         <v>34</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="10">
         <f t="shared" si="0"/>
         <v>1.3685286706756507E-4</v>
       </c>
       <c r="E62" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F62" t="s">
-        <v>260</v>
-      </c>
-      <c r="I62" t="s">
-        <v>213</v>
-      </c>
-      <c r="J62" t="s">
-        <v>216</v>
-      </c>
-      <c r="K62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+      <c r="F62" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K62" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C63" s="2">
+      <c r="B63" s="5"/>
+      <c r="C63" s="9">
         <v>32</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="10">
         <f t="shared" si="0"/>
         <v>1.2880269841653182E-4</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H63" t="s">
-        <v>277</v>
-      </c>
-      <c r="I63" t="s">
-        <v>213</v>
-      </c>
-      <c r="J63" t="s">
-        <v>216</v>
-      </c>
-      <c r="K63">
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K63" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+    <row r="64" spans="1:11">
+      <c r="A64" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B64" t="s">
-        <v>278</v>
-      </c>
-      <c r="C64" s="2">
+      <c r="B64" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="C64" s="9">
         <v>31</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="10">
         <f t="shared" si="0"/>
         <v>1.247776140910152E-4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F64" t="s">
-        <v>256</v>
-      </c>
-      <c r="I64" t="s">
-        <v>213</v>
-      </c>
-      <c r="J64" t="s">
-        <v>216</v>
-      </c>
-      <c r="K64">
+        <v>238</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K64" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+    <row r="65" spans="1:11" ht="57.75">
+      <c r="A65" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="B65" t="s">
-        <v>266</v>
-      </c>
-      <c r="C65" s="2">
+      <c r="B65" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="C65" s="9">
         <v>27</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="10">
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
       <c r="E65" s="5" t="s">
         <v>207</v>
       </c>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
       <c r="H65" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="I65" t="s">
-        <v>213</v>
-      </c>
-      <c r="J65" t="s">
-        <v>216</v>
-      </c>
-      <c r="K65">
+        <v>283</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K65" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+    <row r="66" spans="1:11">
+      <c r="A66" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B66" t="s">
-        <v>221</v>
-      </c>
-      <c r="C66" s="2">
+      <c r="B66" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C66" s="9">
         <v>27</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="10">
         <f t="shared" si="0"/>
         <v>1.0867727678894872E-4</v>
       </c>
       <c r="E66" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H66" t="s">
-        <v>280</v>
-      </c>
-      <c r="I66" t="s">
-        <v>213</v>
-      </c>
-      <c r="J66" t="s">
-        <v>216</v>
-      </c>
-      <c r="K66">
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K66" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="48" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+    <row r="67" spans="1:11" ht="43.5">
+      <c r="A67" s="5" t="s">
         <v>166</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C67" s="2">
+      <c r="C67" s="9">
         <v>22</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="10">
         <f t="shared" ref="D67:D83" si="1">C67/SUM(($C$2:$C$83))</f>
         <v>8.855185516136563E-5</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F67" t="s">
-        <v>260</v>
-      </c>
+      <c r="F67" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="I67" t="s">
-        <v>213</v>
-      </c>
-      <c r="J67" t="s">
-        <v>216</v>
-      </c>
-      <c r="K67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+        <v>286</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K67" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" ht="29.25">
+      <c r="A68" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B68" t="s">
-        <v>221</v>
-      </c>
-      <c r="C68" s="2">
+      <c r="B68" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C68" s="9">
         <v>13</v>
       </c>
-      <c r="D68" s="6">
+      <c r="D68" s="10">
         <f t="shared" si="1"/>
         <v>5.2326096231716057E-5</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F68" t="s">
-        <v>273</v>
-      </c>
-      <c r="I68" t="s">
-        <v>213</v>
-      </c>
-      <c r="J68" t="s">
-        <v>216</v>
-      </c>
-      <c r="K68">
+      <c r="F68" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K68" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+    <row r="69" spans="1:11" ht="57.75">
+      <c r="A69" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B69" t="s">
-        <v>247</v>
-      </c>
-      <c r="C69" s="2">
+      <c r="B69" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C69" s="9">
         <v>8</v>
       </c>
-      <c r="D69" s="6">
+      <c r="D69" s="10">
         <f t="shared" si="1"/>
         <v>3.2200674604132955E-5</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>225</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="I69" t="s">
-        <v>213</v>
-      </c>
-      <c r="J69" t="s">
-        <v>216</v>
-      </c>
-      <c r="K69">
+        <v>283</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K69" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+    <row r="70" spans="1:11">
+      <c r="A70" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="B70" t="s">
-        <v>221</v>
-      </c>
-      <c r="C70" s="2">
+      <c r="B70" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C70" s="9">
         <v>5</v>
       </c>
-      <c r="D70" s="6">
+      <c r="D70" s="10">
         <f t="shared" si="1"/>
         <v>2.0125421627583099E-5</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F70" t="s">
-        <v>260</v>
-      </c>
-      <c r="H70" t="s">
-        <v>282</v>
-      </c>
-      <c r="I70" t="s">
-        <v>213</v>
-      </c>
-      <c r="J70" t="s">
-        <v>216</v>
-      </c>
-      <c r="K70">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+      <c r="F70" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K70" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
+      <c r="A71" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B71" t="s">
-        <v>221</v>
-      </c>
-      <c r="C71" s="2">
+      <c r="B71" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="C71" s="9">
         <v>4</v>
       </c>
-      <c r="D71" s="6">
+      <c r="D71" s="10">
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
       <c r="E71" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F71" t="s">
-        <v>260</v>
-      </c>
-      <c r="H71" t="s">
-        <v>282</v>
-      </c>
-      <c r="I71" t="s">
-        <v>213</v>
-      </c>
-      <c r="J71" t="s">
-        <v>216</v>
-      </c>
-      <c r="K71">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="12" t="s">
+      <c r="F71" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K71" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="B72" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="C72" s="13">
+      <c r="B72" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" s="16">
         <v>4</v>
       </c>
-      <c r="D72" s="14">
+      <c r="D72" s="17">
         <f t="shared" si="1"/>
         <v>1.6100337302066478E-5</v>
       </c>
       <c r="E72" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F72" t="s">
-        <v>260</v>
-      </c>
-      <c r="I72" t="s">
-        <v>213</v>
-      </c>
-      <c r="J72" t="s">
-        <v>216</v>
-      </c>
-      <c r="K72">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="64" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+      <c r="F72" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K72" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="57.75">
+      <c r="A73" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="B73" t="s">
-        <v>247</v>
-      </c>
-      <c r="C73" s="2">
+      <c r="B73" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C73" s="9">
         <v>2</v>
       </c>
-      <c r="D73" s="6">
+      <c r="D73" s="10">
         <f t="shared" si="1"/>
         <v>8.0501686510332388E-6</v>
       </c>
       <c r="E73" s="5" t="s">
         <v>207</v>
       </c>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
       <c r="H73" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="I73" t="s">
-        <v>213</v>
-      </c>
-      <c r="J73" t="s">
-        <v>216</v>
-      </c>
-      <c r="K73">
+        <v>283</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K73" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+    <row r="74" spans="1:11" ht="57.75">
+      <c r="A74" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B74" t="s">
-        <v>247</v>
-      </c>
-      <c r="C74" s="2">
+      <c r="B74" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" s="9">
         <v>2</v>
       </c>
-      <c r="D74" s="6">
+      <c r="D74" s="10">
         <f t="shared" si="1"/>
         <v>8.0501686510332388E-6</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F74" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H74" t="s">
-        <v>283</v>
-      </c>
-      <c r="I74" t="s">
-        <v>216</v>
-      </c>
-      <c r="J74" t="s">
-        <v>213</v>
-      </c>
-      <c r="K74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+      <c r="G74" s="5"/>
+      <c r="H74" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K74" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="57.75">
+      <c r="A75" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="B75" t="s">
-        <v>248</v>
-      </c>
-      <c r="C75" s="2">
-        <v>1</v>
-      </c>
-      <c r="D75" s="6">
+      <c r="B75" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C75" s="9">
+        <v>1</v>
+      </c>
+      <c r="D75" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E75" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H75" t="s">
-        <v>284</v>
-      </c>
-      <c r="I75" t="s">
-        <v>216</v>
-      </c>
-      <c r="J75" t="s">
-        <v>285</v>
-      </c>
-      <c r="K75">
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="K75" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+    <row r="76" spans="1:11" ht="57.75">
+      <c r="A76" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B76" t="s">
-        <v>270</v>
-      </c>
-      <c r="C76" s="2">
-        <v>1</v>
-      </c>
-      <c r="D76" s="6">
+      <c r="B76" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="C76" s="9">
+        <v>1</v>
+      </c>
+      <c r="D76" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E76" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F76" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H76" t="s">
-        <v>283</v>
-      </c>
-      <c r="I76" t="s">
-        <v>216</v>
-      </c>
-      <c r="J76" t="s">
-        <v>213</v>
-      </c>
-      <c r="K76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+      <c r="G76" s="5"/>
+      <c r="H76" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K76" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="57.75">
+      <c r="A77" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B77" t="s">
-        <v>247</v>
-      </c>
-      <c r="C77" s="2">
-        <v>1</v>
-      </c>
-      <c r="D77" s="6">
+      <c r="B77" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C77" s="9">
+        <v>1</v>
+      </c>
+      <c r="D77" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E77" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H77" t="s">
-        <v>284</v>
-      </c>
-      <c r="I77" t="s">
-        <v>216</v>
-      </c>
-      <c r="J77" t="s">
-        <v>213</v>
-      </c>
-      <c r="K77">
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K77" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+    <row r="78" spans="1:11" ht="57.75">
+      <c r="A78" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B78" t="s">
-        <v>247</v>
-      </c>
-      <c r="C78" s="2">
-        <v>1</v>
-      </c>
-      <c r="D78" s="6">
+      <c r="B78" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C78" s="9">
+        <v>1</v>
+      </c>
+      <c r="D78" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F78" t="s">
+      <c r="F78" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H78" t="s">
-        <v>283</v>
-      </c>
-      <c r="I78" t="s">
-        <v>216</v>
-      </c>
-      <c r="J78" t="s">
-        <v>213</v>
-      </c>
-      <c r="K78">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+      <c r="G78" s="5"/>
+      <c r="H78" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K78" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="57.75">
+      <c r="A79" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B79" t="s">
-        <v>247</v>
-      </c>
-      <c r="C79" s="2">
-        <v>1</v>
-      </c>
-      <c r="D79" s="6">
+      <c r="B79" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C79" s="9">
+        <v>1</v>
+      </c>
+      <c r="D79" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="F79" t="s">
+        <v>226</v>
+      </c>
+      <c r="F79" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H79" t="s">
-        <v>283</v>
-      </c>
-      <c r="I79" t="s">
-        <v>216</v>
-      </c>
-      <c r="J79" t="s">
-        <v>213</v>
-      </c>
-      <c r="K79">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+      <c r="G79" s="5"/>
+      <c r="H79" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K79" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="101.25">
+      <c r="A80" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B80" t="s">
-        <v>247</v>
-      </c>
-      <c r="C80" s="2">
-        <v>1</v>
-      </c>
-      <c r="D80" s="6">
+      <c r="B80" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C80" s="9">
+        <v>1</v>
+      </c>
+      <c r="D80" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="H80" t="s">
-        <v>286</v>
-      </c>
-      <c r="I80" t="s">
-        <v>216</v>
-      </c>
-      <c r="J80" t="s">
-        <v>213</v>
-      </c>
-      <c r="K80">
+        <v>238</v>
+      </c>
+      <c r="F80" s="5"/>
+      <c r="G80" s="5"/>
+      <c r="H80" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K80" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+    <row r="81" spans="1:11" ht="57.75">
+      <c r="A81" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B81" t="s">
-        <v>247</v>
-      </c>
-      <c r="C81" s="2">
-        <v>1</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="B81" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="C81" s="9">
+        <v>1</v>
+      </c>
+      <c r="D81" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E81" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F81" t="s">
+      <c r="F81" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H81" t="s">
-        <v>283</v>
-      </c>
-      <c r="I81" t="s">
-        <v>216</v>
-      </c>
-      <c r="J81" t="s">
-        <v>213</v>
-      </c>
-      <c r="K81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+      <c r="G81" s="5"/>
+      <c r="H81" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K81" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" ht="57.75">
+      <c r="A82" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B82" t="s">
-        <v>247</v>
-      </c>
-      <c r="C82" s="2">
-        <v>1</v>
-      </c>
-      <c r="D82" s="6">
+      <c r="B82" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C82" s="9">
+        <v>1</v>
+      </c>
+      <c r="D82" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E82" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F82" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="H82" t="s">
-        <v>283</v>
-      </c>
-      <c r="I82" t="s">
-        <v>216</v>
-      </c>
-      <c r="J82" t="s">
-        <v>213</v>
-      </c>
-      <c r="K82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+      <c r="G82" s="5"/>
+      <c r="H82" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K82" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="57.75">
+      <c r="A83" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="B83" t="s">
-        <v>247</v>
-      </c>
-      <c r="C83" s="2">
-        <v>1</v>
-      </c>
-      <c r="D83" s="6">
+      <c r="B83" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C83" s="9">
+        <v>1</v>
+      </c>
+      <c r="D83" s="10">
         <f t="shared" si="1"/>
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E83" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="H83" t="s">
-        <v>284</v>
-      </c>
-      <c r="I83" t="s">
-        <v>216</v>
-      </c>
-      <c r="J83" t="s">
-        <v>213</v>
-      </c>
-      <c r="K83">
+      <c r="F83" s="5"/>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="K83" s="5">
         <v>2</v>
       </c>
     </row>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2B46C83-FA7C-42F9-9F49-203FE4ADDC2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5ACA85-C950-2E49-BA93-E89181EEE1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -34,7 +34,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -736,9 +735,6 @@
     <t>N/A - Ad Hoc Outbound Call</t>
   </si>
   <si>
-    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu</t>
   </si>
   <si>
@@ -932,6 +928,9 @@
   </si>
   <si>
     <t xml:space="preserve">Pre-Legal Menu </t>
+  </si>
+  <si>
+    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up, these calls are not to customers so should not be included in analysis</t>
   </si>
 </sst>
 </file>
@@ -942,7 +941,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1414,13 +1413,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1428,7 +1427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1436,7 +1435,7 @@
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1444,7 +1443,7 @@
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1452,7 +1451,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1460,7 +1459,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1468,7 +1467,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1476,7 +1475,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1484,7 +1483,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1492,7 +1491,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1500,7 +1499,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1508,7 +1507,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1516,7 +1515,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1524,7 +1523,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1532,7 +1531,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1540,7 +1539,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1548,7 +1547,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1556,7 +1555,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1564,7 +1563,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1572,7 +1571,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1580,7 +1579,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1588,7 +1587,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1596,7 +1595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1604,7 +1603,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1612,7 +1611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1620,7 +1619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1628,7 +1627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1644,17 +1643,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" customWidth="1"/>
+    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="32.1">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1668,7 +1667,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1682,7 +1681,7 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1696,7 +1695,7 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1710,7 +1709,7 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1724,7 +1723,7 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1738,7 +1737,7 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1752,7 +1751,7 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1766,7 +1765,7 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1780,7 +1779,7 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1794,7 +1793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1808,7 +1807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1822,7 +1821,7 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1836,7 +1835,7 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1850,7 +1849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1864,7 +1863,7 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1878,7 +1877,7 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1892,7 +1891,7 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1906,7 +1905,7 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1920,7 +1919,7 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1934,7 +1933,7 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1948,7 +1947,7 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1962,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1976,7 +1975,7 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1990,7 +1989,7 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -2004,7 +2003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -2018,7 +2017,7 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -2032,7 +2031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -2046,7 +2045,7 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2060,7 +2059,7 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -2074,7 +2073,7 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2088,7 +2087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -2116,7 +2115,7 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -2130,7 +2129,7 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2144,7 +2143,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2158,7 +2157,7 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -2172,7 +2171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -2186,7 +2185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -2200,7 +2199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2214,7 +2213,7 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2228,7 +2227,7 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -2242,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2256,7 +2255,7 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2270,7 +2269,7 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2284,7 +2283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -2298,7 +2297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2326,7 +2325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -2340,7 +2339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -2354,7 +2353,7 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -2368,7 +2367,7 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -2382,7 +2381,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2396,7 +2395,7 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -2410,7 +2409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2424,7 +2423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -2438,7 +2437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -2452,7 +2451,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2466,7 +2465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -2480,7 +2479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2494,7 +2493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2508,7 +2507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -2522,7 +2521,7 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -2536,7 +2535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -2550,7 +2549,7 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -2564,7 +2563,7 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -2578,7 +2577,7 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2592,7 +2591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>99</v>
       </c>
@@ -2620,7 +2619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -2634,7 +2633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -2648,7 +2647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -2662,7 +2661,7 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -2676,7 +2675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -2690,7 +2689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -2704,7 +2703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -2718,7 +2717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -2732,7 +2731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -2746,7 +2745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -2760,7 +2759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -2774,7 +2773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>111</v>
       </c>
@@ -2788,7 +2787,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -2802,7 +2801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -2816,7 +2815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>114</v>
       </c>
@@ -2830,7 +2829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -2844,7 +2843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -2858,7 +2857,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -2872,7 +2871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -2886,7 +2885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>119</v>
       </c>
@@ -2900,7 +2899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -2914,7 +2913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -2928,7 +2927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -2942,7 +2941,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -2956,7 +2955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -2970,7 +2969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -2984,7 +2983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -2998,7 +2997,7 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -3012,7 +3011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -3026,7 +3025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -3040,7 +3039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -3068,7 +3067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -3082,7 +3081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -3096,7 +3095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -3124,7 +3123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -3138,7 +3137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -3152,7 +3151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -3166,7 +3165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3180,7 +3179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -3194,7 +3193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>141</v>
       </c>
@@ -3208,7 +3207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>142</v>
       </c>
@@ -3222,7 +3221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>143</v>
       </c>
@@ -3236,7 +3235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>144</v>
       </c>
@@ -3250,7 +3249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>145</v>
       </c>
@@ -3264,7 +3263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3278,7 +3277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>147</v>
       </c>
@@ -3292,7 +3291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -3306,7 +3305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>149</v>
       </c>
@@ -3320,7 +3319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>150</v>
       </c>
@@ -3334,7 +3333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>151</v>
       </c>
@@ -3348,7 +3347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>152</v>
       </c>
@@ -3362,7 +3361,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -3376,7 +3375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -3390,7 +3389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>155</v>
       </c>
@@ -3404,7 +3403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>156</v>
       </c>
@@ -3418,7 +3417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>157</v>
       </c>
@@ -3432,7 +3431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>158</v>
       </c>
@@ -3446,7 +3445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>159</v>
       </c>
@@ -3460,7 +3459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -3474,7 +3473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>161</v>
       </c>
@@ -3488,7 +3487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -3502,7 +3501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -3516,7 +3515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -3530,7 +3529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -3544,7 +3543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -3558,7 +3557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -3586,7 +3585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -3600,7 +3599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -3628,7 +3627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -3642,7 +3641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -3656,7 +3655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -3670,7 +3669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -3684,7 +3683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>176</v>
       </c>
@@ -3698,7 +3697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>177</v>
       </c>
@@ -3712,7 +3711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>178</v>
       </c>
@@ -3726,7 +3725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -3740,7 +3739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>180</v>
       </c>
@@ -3754,7 +3753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>181</v>
       </c>
@@ -3768,7 +3767,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -3782,7 +3781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>183</v>
       </c>
@@ -3796,7 +3795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>184</v>
       </c>
@@ -3810,7 +3809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>185</v>
       </c>
@@ -3824,7 +3823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>186</v>
       </c>
@@ -3838,7 +3837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -3852,7 +3851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -3866,7 +3865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -3880,7 +3879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -3894,7 +3893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -3908,7 +3907,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -3922,7 +3921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -3936,7 +3935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>194</v>
       </c>
@@ -3950,7 +3949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>195</v>
       </c>
@@ -3984,19 +3983,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.5" customWidth="1"/>
+    <col min="2" max="2" width="22.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.28515625" customWidth="1"/>
+    <col min="5" max="5" width="11.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="48">
+    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>196</v>
       </c>
@@ -4031,7 +4030,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="72.75">
+    <row r="2" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
@@ -4063,7 +4062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="29.25">
+    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>40</v>
       </c>
@@ -4095,7 +4094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="29.25">
+    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
@@ -4127,7 +4126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="87">
+    <row r="5" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
@@ -4159,7 +4158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>33</v>
       </c>
@@ -4191,7 +4190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="87">
+    <row r="7" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>44</v>
       </c>
@@ -4223,7 +4222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>36</v>
       </c>
@@ -4255,7 +4254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="87">
+    <row r="9" spans="1:11" ht="96" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>55</v>
       </c>
@@ -4291,7 +4290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="62.25" customHeight="1">
+    <row r="10" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>58</v>
       </c>
@@ -4311,7 +4310,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>230</v>
+        <v>295</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>213</v>
@@ -4323,12 +4322,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="87">
+    <row r="11" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C11" s="11">
         <v>8939</v>
@@ -4338,12 +4337,12 @@
         <v>3.5980228785793066E-2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>213</v>
@@ -4355,7 +4354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="50.25" customHeight="1">
+    <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
@@ -4370,14 +4369,14 @@
         <v>3.1757915328326128E-2</v>
       </c>
       <c r="E12" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>213</v>
@@ -4389,12 +4388,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C13" s="9">
         <v>7765</v>
@@ -4404,10 +4403,10 @@
         <v>3.125477978763655E-2</v>
       </c>
       <c r="E13" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>238</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>239</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -4421,12 +4420,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C14" s="9">
         <v>6895</v>
@@ -4436,14 +4435,14 @@
         <v>2.7752956424437092E-2</v>
       </c>
       <c r="E14" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>213</v>
@@ -4455,12 +4454,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C15" s="9">
         <v>6863</v>
@@ -4487,7 +4486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="29.25">
+    <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>72</v>
       </c>
@@ -4517,7 +4516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>76</v>
       </c>
@@ -4532,14 +4531,14 @@
         <v>1.0243839608439796E-2</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>213</v>
@@ -4551,12 +4550,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C18" s="9">
         <v>2394</v>
@@ -4583,7 +4582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>79</v>
       </c>
@@ -4598,10 +4597,10 @@
         <v>9.1248661659461758E-3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -4615,12 +4614,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C20" s="9">
         <v>2136</v>
@@ -4647,12 +4646,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C21" s="9">
         <v>1462</v>
@@ -4679,12 +4678,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="68.25">
+    <row r="22" spans="1:11" ht="71" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C22" s="9">
         <v>1287</v>
@@ -4711,12 +4710,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C23" s="9">
         <v>1267</v>
@@ -4743,12 +4742,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C24" s="9">
         <v>1209</v>
@@ -4775,12 +4774,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="9">
         <v>870</v>
@@ -4790,7 +4789,7 @@
         <v>3.5018233631994591E-3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -4805,12 +4804,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C26" s="9">
         <v>837</v>
@@ -4837,12 +4836,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C27" s="9">
         <v>836</v>
@@ -4852,10 +4851,10 @@
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -4869,12 +4868,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="68.25">
+    <row r="28" spans="1:11" ht="71" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C28" s="9">
         <v>785</v>
@@ -4901,12 +4900,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C29" s="9">
         <v>771</v>
@@ -4933,12 +4932,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="87">
+    <row r="30" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A30" s="13" t="s">
         <v>102</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C30" s="11">
         <v>694</v>
@@ -4948,12 +4947,12 @@
         <v>2.793408521908534E-3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>213</v>
@@ -4963,12 +4962,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="29.25">
+    <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C31" s="9">
         <v>672</v>
@@ -4978,12 +4977,12 @@
         <v>2.7048566667471682E-3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>213</v>
@@ -4995,12 +4994,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C32" s="9">
         <v>604</v>
@@ -5010,10 +5009,10 @@
         <v>2.4311509326120384E-3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -5027,12 +5026,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C33" s="9">
         <v>543</v>
@@ -5059,7 +5058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>110</v>
       </c>
@@ -5074,14 +5073,14 @@
         <v>2.1775706201044914E-3</v>
       </c>
       <c r="E34" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>235</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>213</v>
@@ -5093,12 +5092,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C35" s="9">
         <v>540</v>
@@ -5108,10 +5107,10 @@
         <v>2.1735455357789744E-3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -5125,12 +5124,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C36" s="9">
         <v>527</v>
@@ -5157,12 +5156,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C37" s="9">
         <v>502</v>
@@ -5189,12 +5188,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C38" s="9">
         <v>479</v>
@@ -5204,10 +5203,10 @@
         <v>1.9280153919224608E-3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -5221,12 +5220,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C39" s="9">
         <v>454</v>
@@ -5236,10 +5235,10 @@
         <v>1.8273882837845452E-3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -5253,12 +5252,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C40" s="9">
         <v>444</v>
@@ -5271,7 +5270,7 @@
         <v>207</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -5285,12 +5284,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C41" s="9">
         <v>442</v>
@@ -5303,7 +5302,7 @@
         <v>207</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
@@ -5317,12 +5316,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="29.25">
+    <row r="42" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
         <v>116</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C42" s="14">
         <v>412</v>
@@ -5335,18 +5334,18 @@
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C43" s="9">
         <v>353</v>
@@ -5356,10 +5355,10 @@
         <v>1.4208547669073666E-3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -5373,12 +5372,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C44" s="9">
         <v>298</v>
@@ -5405,12 +5404,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="43.5">
+    <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C45" s="16">
         <v>278</v>
@@ -5420,14 +5419,14 @@
         <v>1.1189734424936202E-3</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>213</v>
@@ -5439,12 +5438,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="29.25">
+    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>105</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C46" s="9">
         <v>228</v>
@@ -5454,14 +5453,14 @@
         <v>9.1771922621778929E-4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>213</v>
@@ -5473,12 +5472,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="68.25">
+    <row r="47" spans="1:11" ht="71" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C47" s="9">
         <v>219</v>
@@ -5488,14 +5487,14 @@
         <v>8.8149346728813973E-4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>213</v>
@@ -5507,12 +5506,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C48" s="9">
         <v>212</v>
@@ -5539,12 +5538,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>124</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C49" s="9">
         <v>185</v>
@@ -5554,10 +5553,10 @@
         <v>7.446406002205746E-4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -5571,12 +5570,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C50" s="9">
         <v>183</v>
@@ -5589,7 +5588,7 @@
         <v>207</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -5603,9 +5602,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="14">
@@ -5623,12 +5622,12 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
     </row>
-    <row r="52" spans="1:11" ht="29.25">
+    <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>128</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C52" s="9">
         <v>158</v>
@@ -5638,14 +5637,14 @@
         <v>6.3596332343162591E-4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>213</v>
@@ -5657,12 +5656,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>132</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C53" s="9">
         <v>139</v>
@@ -5672,10 +5671,10 @@
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -5689,12 +5688,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C54" s="9">
         <v>138</v>
@@ -5721,12 +5720,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C55" s="9">
         <v>127</v>
@@ -5736,10 +5735,10 @@
         <v>5.1118570934061071E-4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -5753,12 +5752,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="9">
         <v>116</v>
@@ -5785,12 +5784,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C57" s="9">
         <v>85</v>
@@ -5800,10 +5799,10 @@
         <v>3.4213216766891265E-4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -5817,12 +5816,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="87">
+    <row r="58" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C58" s="9">
         <v>70</v>
@@ -5835,11 +5834,11 @@
         <v>207</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>213</v>
@@ -5851,7 +5850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="29.25">
+    <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>144</v>
       </c>
@@ -5866,14 +5865,14 @@
         <v>2.6968064980961351E-4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>213</v>
@@ -5885,12 +5884,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="29.25">
+    <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C60" s="9">
         <v>58</v>
@@ -5900,12 +5899,12 @@
         <v>2.3345489087996395E-4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>213</v>
@@ -5917,12 +5916,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="87">
+    <row r="61" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C61" s="9">
         <v>37</v>
@@ -5935,7 +5934,7 @@
         <v>207</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5949,12 +5948,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C62" s="9">
         <v>34</v>
@@ -5967,7 +5966,7 @@
         <v>207</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5981,7 +5980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>57</v>
       </c>
@@ -5999,7 +5998,7 @@
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>213</v>
@@ -6011,12 +6010,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C64" s="9">
         <v>31</v>
@@ -6026,10 +6025,10 @@
         <v>1.247776140910152E-4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -6043,12 +6042,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="57.75">
+    <row r="65" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>98</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C65" s="9">
         <v>27</v>
@@ -6063,7 +6062,7 @@
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>213</v>
@@ -6075,12 +6074,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C66" s="9">
         <v>27</v>
@@ -6095,7 +6094,7 @@
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>213</v>
@@ -6107,7 +6106,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="43.5">
+    <row r="67" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>166</v>
       </c>
@@ -6125,11 +6124,11 @@
         <v>207</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>213</v>
@@ -6141,12 +6140,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="29.25">
+    <row r="68" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C68" s="9">
         <v>13</v>
@@ -6159,7 +6158,7 @@
         <v>207</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -6173,12 +6172,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="57.75">
+    <row r="69" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C69" s="9">
         <v>8</v>
@@ -6193,7 +6192,7 @@
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>213</v>
@@ -6205,12 +6204,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C70" s="9">
         <v>5</v>
@@ -6223,11 +6222,11 @@
         <v>207</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>213</v>
@@ -6239,12 +6238,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C71" s="9">
         <v>4</v>
@@ -6257,11 +6256,11 @@
         <v>207</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>213</v>
@@ -6273,12 +6272,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="13" t="s">
         <v>125</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C72" s="16">
         <v>4</v>
@@ -6291,7 +6290,7 @@
         <v>207</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -6305,12 +6304,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="57.75">
+    <row r="73" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C73" s="9">
         <v>2</v>
@@ -6325,7 +6324,7 @@
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I73" s="5" t="s">
         <v>213</v>
@@ -6337,12 +6336,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="57.75">
+    <row r="74" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C74" s="9">
         <v>2</v>
@@ -6359,7 +6358,7 @@
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>216</v>
@@ -6371,12 +6370,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="57.75">
+    <row r="75" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -6391,24 +6390,24 @@
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J75" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>291</v>
       </c>
       <c r="K75" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="57.75">
+    <row r="76" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>127</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C76" s="9">
         <v>1</v>
@@ -6425,7 +6424,7 @@
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>216</v>
@@ -6437,12 +6436,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="57.75">
+    <row r="77" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>148</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C77" s="9">
         <v>1</v>
@@ -6457,7 +6456,7 @@
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>216</v>
@@ -6469,12 +6468,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="57.75">
+    <row r="78" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C78" s="9">
         <v>1</v>
@@ -6491,7 +6490,7 @@
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>216</v>
@@ -6503,12 +6502,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="57.75">
+    <row r="79" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>176</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C79" s="9">
         <v>1</v>
@@ -6525,7 +6524,7 @@
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>216</v>
@@ -6537,12 +6536,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="101.25">
+    <row r="80" spans="1:11" ht="80" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C80" s="9">
         <v>1</v>
@@ -6552,12 +6551,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>216</v>
@@ -6569,12 +6568,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="57.75">
+    <row r="81" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>115</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C81" s="9">
         <v>1</v>
@@ -6591,7 +6590,7 @@
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>216</v>
@@ -6603,12 +6602,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="57.75">
+    <row r="82" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>112</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C82" s="9">
         <v>1</v>
@@ -6625,7 +6624,7 @@
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>216</v>
@@ -6637,12 +6636,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="57.75">
+    <row r="83" spans="1:11" ht="64" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>153</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C83" s="9">
         <v>1</v>
@@ -6657,7 +6656,7 @@
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I83" s="5" t="s">
         <v>216</v>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C5ACA85-C950-2E49-BA93-E89181EEE1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30215CD9-49D9-5249-84D4-344B8F597655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -834,9 +834,6 @@
     <t>Family Menu</t>
   </si>
   <si>
-    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action</t>
-  </si>
-  <si>
     <t>Benefits Menu</t>
   </si>
   <si>
@@ -931,6 +928,9 @@
   </si>
   <si>
     <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up, these calls are not to customers so should not be included in analysis</t>
+  </si>
+  <si>
+    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action, always then transferred to CBT Agent</t>
   </si>
 </sst>
 </file>
@@ -4310,7 +4310,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>213</v>
@@ -5316,7 +5316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="48" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="s">
         <v>116</v>
       </c>
@@ -5334,7 +5334,7 @@
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="I42" s="7"/>
       <c r="J42" s="7"/>
@@ -5377,7 +5377,7 @@
         <v>66</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C44" s="9">
         <v>298</v>
@@ -5419,14 +5419,14 @@
         <v>1.1189734424936202E-3</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>257</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>213</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>213</v>
@@ -5487,14 +5487,14 @@
         <v>8.8149346728813973E-4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>257</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>213</v>
@@ -5543,7 +5543,7 @@
         <v>124</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C49" s="9">
         <v>185</v>
@@ -5575,7 +5575,7 @@
         <v>70</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C50" s="9">
         <v>183</v>
@@ -5604,7 +5604,7 @@
     </row>
     <row r="51" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="14">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>213</v>
@@ -5661,7 +5661,7 @@
         <v>132</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C53" s="9">
         <v>139</v>
@@ -5674,7 +5674,7 @@
         <v>233</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -5757,7 +5757,7 @@
         <v>96</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C56" s="9">
         <v>116</v>
@@ -5802,7 +5802,7 @@
         <v>237</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -5834,11 +5834,11 @@
         <v>207</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>213</v>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>213</v>
@@ -5904,7 +5904,7 @@
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>213</v>
@@ -5921,7 +5921,7 @@
         <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C61" s="9">
         <v>37</v>
@@ -5998,7 +5998,7 @@
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>213</v>
@@ -6015,7 +6015,7 @@
         <v>126</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C64" s="9">
         <v>31</v>
@@ -6047,7 +6047,7 @@
         <v>98</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C65" s="9">
         <v>27</v>
@@ -6062,7 +6062,7 @@
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>213</v>
@@ -6079,7 +6079,7 @@
         <v>59</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C66" s="9">
         <v>27</v>
@@ -6094,7 +6094,7 @@
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>213</v>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>213</v>
@@ -6145,7 +6145,7 @@
         <v>87</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C68" s="9">
         <v>13</v>
@@ -6158,7 +6158,7 @@
         <v>207</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -6177,7 +6177,7 @@
         <v>86</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C69" s="9">
         <v>8</v>
@@ -6192,7 +6192,7 @@
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>213</v>
@@ -6209,7 +6209,7 @@
         <v>94</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C70" s="9">
         <v>5</v>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>213</v>
@@ -6243,7 +6243,7 @@
         <v>95</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C71" s="9">
         <v>4</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>213</v>
@@ -6324,7 +6324,7 @@
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I73" s="5" t="s">
         <v>213</v>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>216</v>
@@ -6390,13 +6390,13 @@
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J75" s="5" t="s">
         <v>289</v>
-      </c>
-      <c r="I75" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>290</v>
       </c>
       <c r="K75" s="5">
         <v>2</v>
@@ -6407,7 +6407,7 @@
         <v>127</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C76" s="9">
         <v>1</v>
@@ -6424,7 +6424,7 @@
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>216</v>
@@ -6441,7 +6441,7 @@
         <v>148</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C77" s="9">
         <v>1</v>
@@ -6456,7 +6456,7 @@
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>216</v>
@@ -6473,7 +6473,7 @@
         <v>103</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C78" s="9">
         <v>1</v>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>216</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>216</v>
@@ -6541,7 +6541,7 @@
         <v>61</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C80" s="9">
         <v>1</v>
@@ -6556,7 +6556,7 @@
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>216</v>
@@ -6573,7 +6573,7 @@
         <v>115</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C81" s="9">
         <v>1</v>
@@ -6590,7 +6590,7 @@
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>216</v>
@@ -6607,7 +6607,7 @@
         <v>112</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C82" s="9">
         <v>1</v>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>216</v>
@@ -6641,7 +6641,7 @@
         <v>153</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C83" s="9">
         <v>1</v>
@@ -6656,7 +6656,7 @@
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I83" s="5" t="s">
         <v>216</v>

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30215CD9-49D9-5249-84D4-344B8F597655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB79698-6052-BF4F-86D1-8460E5C663A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="297">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -931,6 +931,9 @@
   </si>
   <si>
     <t>Based on verbiage, unsure of what selection at Family Menu leads to this action, always then transferred to CBT Agent</t>
+  </si>
+  <si>
+    <t>Positive (tentative)</t>
   </si>
 </sst>
 </file>
@@ -5330,7 +5333,9 @@
         <f t="shared" si="0"/>
         <v>1.6583347421128473E-3</v>
       </c>
-      <c r="E42" s="7"/>
+      <c r="E42" s="7" t="s">
+        <v>296</v>
+      </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7" t="s">

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACB79698-6052-BF4F-86D1-8460E5C663A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DECE64-0B27-6440-8020-F95AF46C1ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="297">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -930,10 +930,10 @@
     <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up, these calls are not to customers so should not be included in analysis</t>
   </si>
   <si>
-    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action, always then transferred to CBT Agent</t>
-  </si>
-  <si>
     <t>Positive (tentative)</t>
+  </si>
+  <si>
+    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action, always then transferred to CBT Agent (thus assumed to be a positive outcome)</t>
   </si>
 </sst>
 </file>
@@ -5334,16 +5334,20 @@
         <v>1.6583347421128473E-3</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="I42" s="7"/>
+        <v>296</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>216</v>
+      </c>
       <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
+      <c r="K42" s="7">
+        <v>2</v>
+      </c>
     </row>
     <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">

--- a/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
+++ b/Clarifications/CAR_data_Activity_name_tagging_10Nov.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29512"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabrinaderwent/Documents/GitHub/STAT390_LegalAid_Fall2025/Clarifications/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DECE64-0B27-6440-8020-F95AF46C1ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{44A1AFB0-5236-4709-8236-E64A84D8A60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="1" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="6380" yWindow="760" windowWidth="22580" windowHeight="17820" tabRatio="799" firstSheet="2" activeTab="2" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -34,6 +34,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="296">
   <si>
     <t>Termination Reason</t>
   </si>
@@ -735,6 +736,9 @@
     <t>N/A - Ad Hoc Outbound Call</t>
   </si>
   <si>
+    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up, these calls are not to customers so should not be included in analysis</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Pre-Legal Seniors Menu, Legal Menu, Family Menu, Housing Menu, Benefits Menu, Employment Menu, Immigration Menu</t>
   </si>
   <si>
@@ -834,6 +838,12 @@
     <t>Family Menu</t>
   </si>
   <si>
+    <t>Positive (tentative)</t>
+  </si>
+  <si>
+    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action, always then transferred to CBT Agent (thus assumed to be a positive outcome)</t>
+  </si>
+  <si>
     <t>Benefits Menu</t>
   </si>
   <si>
@@ -891,9 +901,6 @@
     <t>Should check if agents are logged into queue; if last activity, call never entered queue -&gt; system error, customer may end call after waiting (not considering it abandonment)</t>
   </si>
   <si>
-    <t>Courtesy Callback</t>
-  </si>
-  <si>
     <t>System failure in courtesy callback attempt</t>
   </si>
   <si>
@@ -925,15 +932,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pre-Legal Menu </t>
-  </si>
-  <si>
-    <t>Based on info from Mark, system sets caller ID for outbound call, but there is no activity suggesting the call is picked up, these calls are not to customers so should not be included in analysis</t>
-  </si>
-  <si>
-    <t>Positive (tentative)</t>
-  </si>
-  <si>
-    <t>Based on verbiage, unsure of what selection at Family Menu leads to this action, always then transferred to CBT Agent (thus assumed to be a positive outcome)</t>
   </si>
 </sst>
 </file>
@@ -944,7 +942,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1416,13 +1414,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981D87C8-B39B-4C38-8BFC-6165BBCFDE55}">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1430,7 +1428,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1438,7 +1436,7 @@
         <v>79194</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1446,7 +1444,7 @@
         <v>12154</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -1454,7 +1452,7 @@
         <v>4541</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1462,7 +1460,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1470,7 +1468,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1478,7 +1476,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1486,7 +1484,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1494,7 +1492,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1502,7 +1500,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -1510,7 +1508,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1518,7 +1516,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1526,7 +1524,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1534,7 +1532,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -1542,7 +1540,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
@@ -1550,7 +1548,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1558,7 +1556,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1566,7 +1564,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1574,7 +1572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -1582,7 +1580,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1590,7 +1588,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -1598,7 +1596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1606,7 +1604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -1614,7 +1612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1622,7 +1620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1630,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1646,17 +1644,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
   <dimension ref="A3:D167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.1640625" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="31.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" s="5" customFormat="1" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="5" customFormat="1" ht="32.1">
       <c r="A3" s="4" t="s">
         <v>28</v>
       </c>
@@ -1670,7 +1668,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -1684,7 +1682,7 @@
         <v>1.164283632535702</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1698,7 +1696,7 @@
         <v>1.1234789956542732</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1712,7 +1710,7 @@
         <v>1.1517072098475967</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -1726,7 +1724,7 @@
         <v>1.0016428727397502</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -1740,7 +1738,7 @@
         <v>1.1962759989643565</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1754,7 +1752,7 @@
         <v>1.760418961408287</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1768,7 +1766,7 @@
         <v>1.0020809935918611</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1782,7 +1780,7 @@
         <v>1.0070813465233792</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1796,7 +1794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
         <v>41</v>
       </c>
@@ -1810,7 +1808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1824,7 +1822,7 @@
         <v>1.1057110591272081</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1838,7 +1836,7 @@
         <v>1.09186266808373</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1852,7 +1850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -1866,7 +1864,7 @@
         <v>1.2464993537268418</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4">
       <c r="A18" t="s">
         <v>46</v>
       </c>
@@ -1880,7 +1878,7 @@
         <v>1.2055463117027176</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4">
       <c r="A19" t="s">
         <v>47</v>
       </c>
@@ -1894,7 +1892,7 @@
         <v>1.112073745494871</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4">
       <c r="A20" t="s">
         <v>48</v>
       </c>
@@ -1908,7 +1906,7 @@
         <v>2.2501056189269115</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -1922,7 +1920,7 @@
         <v>1.0569956040624526</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4">
       <c r="A22" t="s">
         <v>50</v>
       </c>
@@ -1936,7 +1934,7 @@
         <v>1.3492672988010344</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -1950,7 +1948,7 @@
         <v>1.0407039786470931</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -1964,7 +1962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
         <v>53</v>
       </c>
@@ -1978,7 +1976,7 @@
         <v>1.3119709794437726</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
         <v>54</v>
       </c>
@@ -1992,7 +1990,7 @@
         <v>1.1961218346024438</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
         <v>55</v>
       </c>
@@ -2006,7 +2004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
         <v>56</v>
       </c>
@@ -2020,7 +2018,7 @@
         <v>1.2148247699782901</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
         <v>57</v>
       </c>
@@ -2034,7 +2032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -2048,7 +2046,7 @@
         <v>2.0004271222637482</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2062,7 +2060,7 @@
         <v>1.0457948040510787</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4">
       <c r="A32" t="s">
         <v>60</v>
       </c>
@@ -2076,7 +2074,7 @@
         <v>2.8494102083563004</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4">
       <c r="A33" t="s">
         <v>61</v>
       </c>
@@ -2090,7 +2088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4">
       <c r="A34" t="s">
         <v>62</v>
       </c>
@@ -2104,7 +2102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -2118,7 +2116,7 @@
         <v>2.8681539187913128</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4">
       <c r="A36" t="s">
         <v>64</v>
       </c>
@@ -2132,7 +2130,7 @@
         <v>1.0709219858156029</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4">
       <c r="A37" t="s">
         <v>65</v>
       </c>
@@ -2146,7 +2144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4">
       <c r="A38" t="s">
         <v>66</v>
       </c>
@@ -2160,7 +2158,7 @@
         <v>1.0844024307900066</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -2174,7 +2172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -2188,7 +2186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4">
       <c r="A41" t="s">
         <v>69</v>
       </c>
@@ -2202,7 +2200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4">
       <c r="A42" t="s">
         <v>70</v>
       </c>
@@ -2216,7 +2214,7 @@
         <v>1.1186081052408232</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4">
       <c r="A43" t="s">
         <v>71</v>
       </c>
@@ -2230,7 +2228,7 @@
         <v>1.0735778091208275</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4">
       <c r="A44" t="s">
         <v>72</v>
       </c>
@@ -2244,7 +2242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4">
       <c r="A45" t="s">
         <v>73</v>
       </c>
@@ -2258,7 +2256,7 @@
         <v>1.4581728123280131</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4">
       <c r="A46" t="s">
         <v>74</v>
       </c>
@@ -2272,7 +2270,7 @@
         <v>1.1370056497175141</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4">
       <c r="A47" t="s">
         <v>75</v>
       </c>
@@ -2286,7 +2284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4">
       <c r="A48" t="s">
         <v>76</v>
       </c>
@@ -2300,7 +2298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4">
       <c r="A49" t="s">
         <v>77</v>
       </c>
@@ -2314,7 +2312,7 @@
         <v>1.0387380191693292</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4">
       <c r="A50" t="s">
         <v>78</v>
       </c>
@@ -2328,7 +2326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4">
       <c r="A51" t="s">
         <v>79</v>
       </c>
@@ -2342,7 +2340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4">
       <c r="A52" t="s">
         <v>80</v>
       </c>
@@ -2356,7 +2354,7 @@
         <v>1.0768890852850199</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -2370,7 +2368,7 @@
         <v>1.1437472185135737</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4">
       <c r="A54" t="s">
         <v>82</v>
       </c>
@@ -2384,7 +2382,7 @@
         <v>1.6628787878787878</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -2398,7 +2396,7 @@
         <v>1.1380455407969639</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4">
       <c r="A56" t="s">
         <v>84</v>
       </c>
@@ -2412,7 +2410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4">
       <c r="A57" t="s">
         <v>85</v>
       </c>
@@ -2426,7 +2424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4">
       <c r="A58" t="s">
         <v>86</v>
       </c>
@@ -2440,7 +2438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4">
       <c r="A59" t="s">
         <v>87</v>
       </c>
@@ -2454,7 +2452,7 @@
         <v>2.0524880708929789</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4">
       <c r="A60" t="s">
         <v>88</v>
       </c>
@@ -2468,7 +2466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -2482,7 +2480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4">
       <c r="A62" t="s">
         <v>90</v>
       </c>
@@ -2496,7 +2494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -2510,7 +2508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4">
       <c r="A64" t="s">
         <v>92</v>
       </c>
@@ -2524,7 +2522,7 @@
         <v>1.0892547660311958</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4">
       <c r="A65" t="s">
         <v>93</v>
       </c>
@@ -2538,7 +2536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -2552,7 +2550,7 @@
         <v>1.5662535748331745</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4">
       <c r="A67" t="s">
         <v>95</v>
       </c>
@@ -2566,7 +2564,7 @@
         <v>1.1737804878048781</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4">
       <c r="A68" t="s">
         <v>96</v>
       </c>
@@ -2580,7 +2578,7 @@
         <v>1.2172131147540983</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4">
       <c r="A69" t="s">
         <v>97</v>
       </c>
@@ -2594,7 +2592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4">
       <c r="A70" t="s">
         <v>98</v>
       </c>
@@ -2608,7 +2606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4">
       <c r="A71" t="s">
         <v>99</v>
       </c>
@@ -2622,7 +2620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4">
       <c r="A72" t="s">
         <v>100</v>
       </c>
@@ -2636,7 +2634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -2650,7 +2648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4">
       <c r="A74" t="s">
         <v>102</v>
       </c>
@@ -2664,7 +2662,7 @@
         <v>1.1807387862796834</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4">
       <c r="A75" t="s">
         <v>103</v>
       </c>
@@ -2678,7 +2676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -2692,7 +2690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -2706,7 +2704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -2720,7 +2718,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4">
       <c r="A79" t="s">
         <v>107</v>
       </c>
@@ -2734,7 +2732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4">
       <c r="A80" t="s">
         <v>108</v>
       </c>
@@ -2748,7 +2746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4">
       <c r="A81" t="s">
         <v>109</v>
       </c>
@@ -2762,7 +2760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4">
       <c r="A82" t="s">
         <v>110</v>
       </c>
@@ -2776,7 +2774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4">
       <c r="A83" t="s">
         <v>111</v>
       </c>
@@ -2790,7 +2788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4">
       <c r="A84" t="s">
         <v>112</v>
       </c>
@@ -2804,7 +2802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4">
       <c r="A85" t="s">
         <v>113</v>
       </c>
@@ -2818,7 +2816,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4">
       <c r="A86" t="s">
         <v>114</v>
       </c>
@@ -2832,7 +2830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4">
       <c r="A87" t="s">
         <v>115</v>
       </c>
@@ -2846,7 +2844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4">
       <c r="A88" t="s">
         <v>116</v>
       </c>
@@ -2860,7 +2858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4">
       <c r="A89" t="s">
         <v>117</v>
       </c>
@@ -2874,7 +2872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4">
       <c r="A90" t="s">
         <v>118</v>
       </c>
@@ -2888,7 +2886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4">
       <c r="A91" t="s">
         <v>119</v>
       </c>
@@ -2902,7 +2900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4">
       <c r="A92" t="s">
         <v>120</v>
       </c>
@@ -2916,7 +2914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4">
       <c r="A93" t="s">
         <v>121</v>
       </c>
@@ -2930,7 +2928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4">
       <c r="A94" t="s">
         <v>122</v>
       </c>
@@ -2944,7 +2942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4">
       <c r="A95" t="s">
         <v>123</v>
       </c>
@@ -2958,7 +2956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4">
       <c r="A96" t="s">
         <v>124</v>
       </c>
@@ -2972,7 +2970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4">
       <c r="A97" t="s">
         <v>125</v>
       </c>
@@ -2986,7 +2984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4">
       <c r="A98" t="s">
         <v>126</v>
       </c>
@@ -3000,7 +2998,7 @@
         <v>1.1213872832369942</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4">
       <c r="A99" t="s">
         <v>127</v>
       </c>
@@ -3014,7 +3012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4">
       <c r="A100" t="s">
         <v>128</v>
       </c>
@@ -3028,7 +3026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4">
       <c r="A101" t="s">
         <v>129</v>
       </c>
@@ -3042,7 +3040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4">
       <c r="A102" t="s">
         <v>130</v>
       </c>
@@ -3056,7 +3054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4">
       <c r="A103" t="s">
         <v>131</v>
       </c>
@@ -3070,7 +3068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4">
       <c r="A104" t="s">
         <v>132</v>
       </c>
@@ -3084,7 +3082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4">
       <c r="A105" t="s">
         <v>133</v>
       </c>
@@ -3098,7 +3096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4">
       <c r="A106" t="s">
         <v>134</v>
       </c>
@@ -3112,7 +3110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4">
       <c r="A107" t="s">
         <v>135</v>
       </c>
@@ -3126,7 +3124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4">
       <c r="A108" t="s">
         <v>136</v>
       </c>
@@ -3140,7 +3138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4">
       <c r="A109" t="s">
         <v>137</v>
       </c>
@@ -3154,7 +3152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4">
       <c r="A110" t="s">
         <v>138</v>
       </c>
@@ -3168,7 +3166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4">
       <c r="A111" t="s">
         <v>139</v>
       </c>
@@ -3182,7 +3180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4">
       <c r="A112" t="s">
         <v>140</v>
       </c>
@@ -3196,7 +3194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4">
       <c r="A113" t="s">
         <v>141</v>
       </c>
@@ -3210,7 +3208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4">
       <c r="A114" t="s">
         <v>142</v>
       </c>
@@ -3224,7 +3222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4">
       <c r="A115" t="s">
         <v>143</v>
       </c>
@@ -3238,7 +3236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4">
       <c r="A116" t="s">
         <v>144</v>
       </c>
@@ -3252,7 +3250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4">
       <c r="A117" t="s">
         <v>145</v>
       </c>
@@ -3266,7 +3264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4">
       <c r="A118" t="s">
         <v>146</v>
       </c>
@@ -3280,7 +3278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4">
       <c r="A119" t="s">
         <v>147</v>
       </c>
@@ -3294,7 +3292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4">
       <c r="A120" t="s">
         <v>148</v>
       </c>
@@ -3308,7 +3306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4">
       <c r="A121" t="s">
         <v>149</v>
       </c>
@@ -3322,7 +3320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4">
       <c r="A122" t="s">
         <v>150</v>
       </c>
@@ -3336,7 +3334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4">
       <c r="A123" t="s">
         <v>151</v>
       </c>
@@ -3350,7 +3348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4">
       <c r="A124" t="s">
         <v>152</v>
       </c>
@@ -3364,7 +3362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4">
       <c r="A125" t="s">
         <v>153</v>
       </c>
@@ -3378,7 +3376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4">
       <c r="A126" t="s">
         <v>154</v>
       </c>
@@ -3392,7 +3390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4">
       <c r="A127" t="s">
         <v>155</v>
       </c>
@@ -3406,7 +3404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4">
       <c r="A128" t="s">
         <v>156</v>
       </c>
@@ -3420,7 +3418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4">
       <c r="A129" t="s">
         <v>157</v>
       </c>
@@ -3434,7 +3432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4">
       <c r="A130" t="s">
         <v>158</v>
       </c>
@@ -3448,7 +3446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4">
       <c r="A131" t="s">
         <v>159</v>
       </c>
@@ -3462,7 +3460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4">
       <c r="A132" t="s">
         <v>160</v>
       </c>
@@ -3476,7 +3474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4">
       <c r="A133" t="s">
         <v>161</v>
       </c>
@@ -3490,7 +3488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4">
       <c r="A134" t="s">
         <v>162</v>
       </c>
@@ -3504,7 +3502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4">
       <c r="A135" t="s">
         <v>163</v>
       </c>
@@ -3518,7 +3516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4">
       <c r="A136" t="s">
         <v>164</v>
       </c>
@@ -3532,7 +3530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4">
       <c r="A137" t="s">
         <v>165</v>
       </c>
@@ -3546,7 +3544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4">
       <c r="A138" t="s">
         <v>166</v>
       </c>
@@ -3560,7 +3558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4">
       <c r="A139" t="s">
         <v>167</v>
       </c>
@@ -3574,7 +3572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4">
       <c r="A140" t="s">
         <v>168</v>
       </c>
@@ -3588,7 +3586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4">
       <c r="A141" t="s">
         <v>169</v>
       </c>
@@ -3602,7 +3600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4">
       <c r="A142" t="s">
         <v>170</v>
       </c>
@@ -3616,7 +3614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4">
       <c r="A143" t="s">
         <v>171</v>
       </c>
@@ -3630,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4">
       <c r="A144" t="s">
         <v>172</v>
       </c>
@@ -3644,7 +3642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4">
       <c r="A145" t="s">
         <v>173</v>
       </c>
@@ -3658,7 +3656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4">
       <c r="A146" t="s">
         <v>174</v>
       </c>
@@ -3672,7 +3670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4">
       <c r="A147" t="s">
         <v>175</v>
       </c>
@@ -3686,7 +3684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4">
       <c r="A148" t="s">
         <v>176</v>
       </c>
@@ -3700,7 +3698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4">
       <c r="A149" t="s">
         <v>177</v>
       </c>
@@ -3714,7 +3712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4">
       <c r="A150" t="s">
         <v>178</v>
       </c>
@@ -3728,7 +3726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4">
       <c r="A151" t="s">
         <v>179</v>
       </c>
@@ -3742,7 +3740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4">
       <c r="A152" t="s">
         <v>180</v>
       </c>
@@ -3756,7 +3754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4">
       <c r="A153" t="s">
         <v>181</v>
       </c>
@@ -3770,7 +3768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4">
       <c r="A154" t="s">
         <v>182</v>
       </c>
@@ -3784,7 +3782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4">
       <c r="A155" t="s">
         <v>183</v>
       </c>
@@ -3798,7 +3796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4">
       <c r="A156" t="s">
         <v>184</v>
       </c>
@@ -3812,7 +3810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4">
       <c r="A157" t="s">
         <v>185</v>
       </c>
@@ -3826,7 +3824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4">
       <c r="A158" t="s">
         <v>186</v>
       </c>
@@ -3840,7 +3838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4">
       <c r="A159" t="s">
         <v>187</v>
       </c>
@@ -3854,7 +3852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4">
       <c r="A160" t="s">
         <v>188</v>
       </c>
@@ -3868,7 +3866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4">
       <c r="A161" t="s">
         <v>189</v>
       </c>
@@ -3882,7 +3880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4">
       <c r="A162" t="s">
         <v>190</v>
       </c>
@@ -3896,7 +3894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4">
       <c r="A163" t="s">
         <v>191</v>
       </c>
@@ -3910,7 +3908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4">
       <c r="A164" t="s">
         <v>192</v>
       </c>
@@ -3924,7 +3922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4">
       <c r="A165" t="s">
         <v>193</v>
       </c>
@@ -3938,7 +3936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4">
       <c r="A166" t="s">
         <v>194</v>
       </c>
@@ -3952,7 +3950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4">
       <c r="A167" t="s">
         <v>195</v>
       </c>
@@ -3986,19 +3984,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7750F3-75BB-482E-9AD7-33391182A4F5}">
   <dimension ref="A1:K83"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="33.5" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" customWidth="1"/>
-    <col min="3" max="3" width="17.1640625" customWidth="1"/>
+    <col min="1" max="1" width="33.42578125" customWidth="1"/>
+    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="28.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="28.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="48">
       <c r="A1" s="6" t="s">
         <v>196</v>
       </c>
@@ -4033,7 +4031,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="63.95">
       <c r="A2" s="5" t="s">
         <v>37</v>
       </c>
@@ -4065,7 +4063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="32.1">
       <c r="A3" s="5" t="s">
         <v>40</v>
       </c>
@@ -4097,7 +4095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" ht="32.1">
       <c r="A4" s="5" t="s">
         <v>32</v>
       </c>
@@ -4129,7 +4127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="80.099999999999994">
       <c r="A5" s="5" t="s">
         <v>41</v>
       </c>
@@ -4161,7 +4159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="15.95">
       <c r="A6" s="5" t="s">
         <v>33</v>
       </c>
@@ -4193,7 +4191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="80.099999999999994">
       <c r="A7" s="5" t="s">
         <v>44</v>
       </c>
@@ -4225,7 +4223,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="15.95">
       <c r="A8" s="5" t="s">
         <v>36</v>
       </c>
@@ -4257,7 +4255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="96" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="96">
       <c r="A9" s="5" t="s">
         <v>55</v>
       </c>
@@ -4293,7 +4291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="62.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="62.25" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>58</v>
       </c>
@@ -4313,7 +4311,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>294</v>
+        <v>230</v>
       </c>
       <c r="I10" s="5" t="s">
         <v>213</v>
@@ -4325,12 +4323,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="80.099999999999994">
       <c r="A11" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C11" s="11">
         <v>8939</v>
@@ -4340,12 +4338,12 @@
         <v>3.5980228785793066E-2</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>213</v>
@@ -4357,7 +4355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="50.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="50.25" customHeight="1">
       <c r="A12" s="5" t="s">
         <v>65</v>
       </c>
@@ -4372,14 +4370,14 @@
         <v>3.1757915328326128E-2</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>213</v>
@@ -4391,12 +4389,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="15.95">
       <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C13" s="9">
         <v>7765</v>
@@ -4406,10 +4404,10 @@
         <v>3.125477978763655E-2</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
@@ -4423,12 +4421,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="15.95">
       <c r="A14" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C14" s="9">
         <v>6895</v>
@@ -4438,14 +4436,14 @@
         <v>2.7752956424437092E-2</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>213</v>
@@ -4457,12 +4455,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="15.95">
       <c r="A15" s="5" t="s">
         <v>48</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C15" s="9">
         <v>6863</v>
@@ -4489,7 +4487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="32.1">
       <c r="A16" s="5" t="s">
         <v>72</v>
       </c>
@@ -4519,7 +4517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="15.95">
       <c r="A17" s="5" t="s">
         <v>76</v>
       </c>
@@ -4534,14 +4532,14 @@
         <v>1.0243839608439796E-2</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>213</v>
@@ -4553,12 +4551,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="15.95">
       <c r="A18" s="5" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C18" s="9">
         <v>2394</v>
@@ -4585,7 +4583,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="15.95">
       <c r="A19" s="5" t="s">
         <v>79</v>
       </c>
@@ -4600,10 +4598,10 @@
         <v>9.1248661659461758E-3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
@@ -4617,12 +4615,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="15.95">
       <c r="A20" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C20" s="9">
         <v>2136</v>
@@ -4649,12 +4647,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="15.95">
       <c r="A21" s="5" t="s">
         <v>53</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C21" s="9">
         <v>1462</v>
@@ -4681,12 +4679,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="71" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="71.099999999999994">
       <c r="A22" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C22" s="9">
         <v>1287</v>
@@ -4713,12 +4711,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="15.95">
       <c r="A23" s="5" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C23" s="9">
         <v>1267</v>
@@ -4745,12 +4743,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="15.95">
       <c r="A24" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C24" s="9">
         <v>1209</v>
@@ -4777,12 +4775,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="15.95">
       <c r="A25" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C25" s="9">
         <v>870</v>
@@ -4792,7 +4790,7 @@
         <v>3.5018233631994591E-3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -4807,12 +4805,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="15.95">
       <c r="A26" s="5" t="s">
         <v>45</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C26" s="9">
         <v>837</v>
@@ -4839,12 +4837,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="15.95">
       <c r="A27" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C27" s="9">
         <v>836</v>
@@ -4854,10 +4852,10 @@
         <v>3.3649704961318939E-3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
@@ -4871,12 +4869,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="71" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="71.099999999999994">
       <c r="A28" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C28" s="9">
         <v>785</v>
@@ -4903,12 +4901,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" ht="15.95">
       <c r="A29" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C29" s="9">
         <v>771</v>
@@ -4935,12 +4933,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:11" ht="80.099999999999994">
       <c r="A30" s="13" t="s">
         <v>102</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C30" s="11">
         <v>694</v>
@@ -4950,12 +4948,12 @@
         <v>2.793408521908534E-3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>213</v>
@@ -4965,12 +4963,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:11" ht="32.1">
       <c r="A31" s="5" t="s">
         <v>74</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C31" s="9">
         <v>672</v>
@@ -4980,12 +4978,12 @@
         <v>2.7048566667471682E-3</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>213</v>
@@ -4997,12 +4995,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:11" ht="15.95">
       <c r="A32" s="5" t="s">
         <v>47</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C32" s="9">
         <v>604</v>
@@ -5012,10 +5010,10 @@
         <v>2.4311509326120384E-3</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
@@ -5029,12 +5027,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:11" ht="15.95">
       <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C33" s="9">
         <v>543</v>
@@ -5061,7 +5059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:11" ht="15.95">
       <c r="A34" s="5" t="s">
         <v>110</v>
       </c>
@@ -5076,14 +5074,14 @@
         <v>2.1775706201044914E-3</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>213</v>
@@ -5095,12 +5093,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:11" ht="15.95">
       <c r="A35" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C35" s="9">
         <v>540</v>
@@ -5110,10 +5108,10 @@
         <v>2.1735455357789744E-3</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
@@ -5127,12 +5125,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="15.95">
       <c r="A36" s="5" t="s">
         <v>73</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C36" s="9">
         <v>527</v>
@@ -5159,12 +5157,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="15.95">
       <c r="A37" s="5" t="s">
         <v>46</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C37" s="9">
         <v>502</v>
@@ -5191,12 +5189,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="15.95">
       <c r="A38" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C38" s="9">
         <v>479</v>
@@ -5206,10 +5204,10 @@
         <v>1.9280153919224608E-3</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
@@ -5223,12 +5221,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="15.95">
       <c r="A39" s="5" t="s">
         <v>81</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C39" s="9">
         <v>454</v>
@@ -5238,10 +5236,10 @@
         <v>1.8273882837845452E-3</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
@@ -5255,12 +5253,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="15.95">
       <c r="A40" s="5" t="s">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C40" s="9">
         <v>444</v>
@@ -5273,7 +5271,7 @@
         <v>207</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
@@ -5287,12 +5285,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="15.95">
       <c r="A41" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C41" s="9">
         <v>442</v>
@@ -5305,7 +5303,7 @@
         <v>207</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
@@ -5319,12 +5317,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="48">
       <c r="A42" s="7" t="s">
         <v>116</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C42" s="14">
         <v>412</v>
@@ -5334,12 +5332,12 @@
         <v>1.6583347421128473E-3</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>216</v>
@@ -5349,12 +5347,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" ht="15.95">
       <c r="A43" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C43" s="9">
         <v>353</v>
@@ -5364,10 +5362,10 @@
         <v>1.4208547669073666E-3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
@@ -5381,12 +5379,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" ht="15.95">
       <c r="A44" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C44" s="9">
         <v>298</v>
@@ -5413,12 +5411,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" ht="32.1">
       <c r="A45" s="13" t="s">
         <v>69</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C45" s="16">
         <v>278</v>
@@ -5428,14 +5426,14 @@
         <v>1.1189734424936202E-3</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>213</v>
@@ -5447,12 +5445,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" ht="32.1">
       <c r="A46" s="5" t="s">
         <v>105</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C46" s="9">
         <v>228</v>
@@ -5462,14 +5460,14 @@
         <v>9.1771922621778929E-4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="I46" s="5" t="s">
         <v>213</v>
@@ -5481,12 +5479,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="71" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" ht="71.099999999999994">
       <c r="A47" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C47" s="9">
         <v>219</v>
@@ -5496,14 +5494,14 @@
         <v>8.8149346728813973E-4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>213</v>
@@ -5515,12 +5513,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="15.95">
       <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C48" s="9">
         <v>212</v>
@@ -5547,12 +5545,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="15.95">
       <c r="A49" s="5" t="s">
         <v>124</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C49" s="9">
         <v>185</v>
@@ -5562,10 +5560,10 @@
         <v>7.446406002205746E-4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
@@ -5579,12 +5577,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="15.95">
       <c r="A50" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C50" s="9">
         <v>183</v>
@@ -5597,7 +5595,7 @@
         <v>207</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
@@ -5611,9 +5609,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" ht="15.95">
       <c r="A51" s="7" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B51" s="7"/>
       <c r="C51" s="14">
@@ -5631,12 +5629,12 @@
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
     </row>
-    <row r="52" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="32.1">
       <c r="A52" s="5" t="s">
         <v>128</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C52" s="9">
         <v>158</v>
@@ -5646,14 +5644,14 @@
         <v>6.3596332343162591E-4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="I52" s="5" t="s">
         <v>213</v>
@@ -5665,12 +5663,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="15.95">
       <c r="A53" s="5" t="s">
         <v>132</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C53" s="9">
         <v>139</v>
@@ -5680,10 +5678,10 @@
         <v>5.594867212468101E-4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
@@ -5697,12 +5695,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="15.95">
       <c r="A54" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C54" s="9">
         <v>138</v>
@@ -5729,12 +5727,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="15.95">
       <c r="A55" s="5" t="s">
         <v>89</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C55" s="9">
         <v>127</v>
@@ -5744,10 +5742,10 @@
         <v>5.1118570934061071E-4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
@@ -5761,12 +5759,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="15.95">
       <c r="A56" s="5" t="s">
         <v>96</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C56" s="9">
         <v>116</v>
@@ -5793,12 +5791,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="15.95">
       <c r="A57" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C57" s="9">
         <v>85</v>
@@ -5808,10 +5806,10 @@
         <v>3.4213216766891265E-4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
@@ -5825,12 +5823,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="80.099999999999994">
       <c r="A58" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C58" s="9">
         <v>70</v>
@@ -5843,11 +5841,11 @@
         <v>207</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="I58" s="5" t="s">
         <v>213</v>
@@ -5859,7 +5857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" ht="32.1">
       <c r="A59" s="5" t="s">
         <v>144</v>
       </c>
@@ -5874,14 +5872,14 @@
         <v>2.6968064980961351E-4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>213</v>
@@ -5893,12 +5891,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="32" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" ht="32.1">
       <c r="A60" s="5" t="s">
         <v>92</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C60" s="9">
         <v>58</v>
@@ -5908,12 +5906,12 @@
         <v>2.3345489087996395E-4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="I60" s="5" t="s">
         <v>213</v>
@@ -5925,12 +5923,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" ht="80.099999999999994">
       <c r="A61" s="5" t="s">
         <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C61" s="9">
         <v>37</v>
@@ -5943,7 +5941,7 @@
         <v>207</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
@@ -5957,12 +5955,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="15.95">
       <c r="A62" s="5" t="s">
         <v>51</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C62" s="9">
         <v>34</v>
@@ -5975,7 +5973,7 @@
         <v>207</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
@@ -5989,7 +5987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="15.95">
       <c r="A63" s="5" t="s">
         <v>57</v>
       </c>
@@ -6007,7 +6005,7 @@
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>213</v>
@@ -6019,12 +6017,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="15.95">
       <c r="A64" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C64" s="9">
         <v>31</v>
@@ -6034,10 +6032,10 @@
         <v>1.247776140910152E-4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
@@ -6051,12 +6049,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="63.95">
       <c r="A65" s="5" t="s">
         <v>98</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C65" s="9">
         <v>27</v>
@@ -6071,7 +6069,7 @@
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>213</v>
@@ -6083,12 +6081,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="87">
       <c r="A66" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C66" s="9">
         <v>27</v>
@@ -6103,7 +6101,7 @@
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I66" s="5" t="s">
         <v>213</v>
@@ -6115,7 +6113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" ht="48">
       <c r="A67" s="5" t="s">
         <v>166</v>
       </c>
@@ -6133,11 +6131,11 @@
         <v>207</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="I67" s="5" t="s">
         <v>213</v>
@@ -6149,12 +6147,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" ht="87">
       <c r="A68" s="5" t="s">
         <v>87</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C68" s="9">
         <v>13</v>
@@ -6167,7 +6165,7 @@
         <v>207</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
@@ -6181,12 +6179,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:11" ht="63.95">
       <c r="A69" s="5" t="s">
         <v>86</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C69" s="9">
         <v>8</v>
@@ -6201,7 +6199,7 @@
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I69" s="5" t="s">
         <v>213</v>
@@ -6213,12 +6211,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:11" ht="87">
       <c r="A70" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C70" s="9">
         <v>5</v>
@@ -6231,11 +6229,11 @@
         <v>207</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I70" s="5" t="s">
         <v>213</v>
@@ -6247,12 +6245,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="87">
       <c r="A71" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C71" s="9">
         <v>4</v>
@@ -6265,11 +6263,11 @@
         <v>207</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>213</v>
@@ -6281,12 +6279,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" ht="15.95">
       <c r="A72" s="13" t="s">
         <v>125</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C72" s="16">
         <v>4</v>
@@ -6299,7 +6297,7 @@
         <v>207</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
@@ -6313,12 +6311,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="63.95">
       <c r="A73" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C73" s="9">
         <v>2</v>
@@ -6333,7 +6331,7 @@
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
       <c r="H73" s="5" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I73" s="5" t="s">
         <v>213</v>
@@ -6345,12 +6343,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="48">
       <c r="A74" s="5" t="s">
         <v>91</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C74" s="9">
         <v>2</v>
@@ -6367,7 +6365,7 @@
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I74" s="5" t="s">
         <v>216</v>
@@ -6379,12 +6377,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" ht="63.95">
       <c r="A75" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C75" s="9">
         <v>1</v>
@@ -6399,24 +6397,24 @@
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
       <c r="H75" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I75" s="5" t="s">
         <v>216</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K75" s="5">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" ht="48">
       <c r="A76" s="5" t="s">
         <v>127</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C76" s="9">
         <v>1</v>
@@ -6433,7 +6431,7 @@
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I76" s="5" t="s">
         <v>216</v>
@@ -6445,12 +6443,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" ht="63.95">
       <c r="A77" s="5" t="s">
         <v>148</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C77" s="9">
         <v>1</v>
@@ -6465,7 +6463,7 @@
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
       <c r="H77" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>216</v>
@@ -6477,12 +6475,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" ht="48">
       <c r="A78" s="5" t="s">
         <v>103</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C78" s="9">
         <v>1</v>
@@ -6499,7 +6497,7 @@
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I78" s="5" t="s">
         <v>216</v>
@@ -6511,12 +6509,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" ht="48">
       <c r="A79" s="5" t="s">
         <v>176</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C79" s="9">
         <v>1</v>
@@ -6533,7 +6531,7 @@
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>216</v>
@@ -6545,12 +6543,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="80" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="80.099999999999994">
       <c r="A80" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C80" s="9">
         <v>1</v>
@@ -6560,12 +6558,12 @@
         <v>4.0250843255166194E-6</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
       <c r="H80" s="5" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="I80" s="5" t="s">
         <v>216</v>
@@ -6577,12 +6575,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" ht="48">
       <c r="A81" s="5" t="s">
         <v>115</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C81" s="9">
         <v>1</v>
@@ -6599,7 +6597,7 @@
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>216</v>
@@ -6611,12 +6609,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="48" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" ht="48">
       <c r="A82" s="5" t="s">
         <v>112</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C82" s="9">
         <v>1</v>
@@ -6633,7 +6631,7 @@
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="I82" s="5" t="s">
         <v>216</v>
@@ -6645,12 +6643,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="64" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" ht="63.95">
       <c r="A83" s="5" t="s">
         <v>153</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C83" s="9">
         <v>1</v>
@@ -6665,7 +6663,7 @@
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
       <c r="H83" s="5" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I83" s="5" t="s">
         <v>216</v>
